--- a/backend/ctee_analyzed.xlsx
+++ b/backend/ctee_analyzed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M500"/>
+  <dimension ref="A1:N500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>All_Scores</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>News_Event</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -561,6 +566,11 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.7003 | 大盤指數、期貨與總體經濟: 0.0698 | 通訊網路與軟體服務: 0.0501 | 航運與物流: 0.048 | 再生能源與永續發展: 0.0432 | 電子科技與半導體: 0.0318 | 其他產業或綜合新聞: 0.0169 | 傳統製造與原物料: 0.014 | 生技與醫療: 0.0127 | 營建與房地產: 0.0083 | 金融與保險業: 0.0049</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -632,6 +642,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -699,6 +714,11 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.7559 | 電子科技與半導體: 0.1127 | 金融與保險業: 0.0207 | 民生消費與零售: 0.0183 | 其他產業或綜合新聞: 0.0176 | 再生能源與永續發展: 0.0169 | 通訊網路與軟體服務: 0.015 | 生技與醫療: 0.0139 | 航運與物流: 0.0106 | 營建與房地產: 0.0104 | 傳統製造與原物料: 0.008</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -770,6 +790,11 @@
           <t>通訊網路與軟體服務: 0.3936 | 其他產業或綜合新聞: 0.0928 | 電子科技與半導體: 0.0898 | 民生消費與零售: 0.0797 | 再生能源與永續發展: 0.0729 | 大盤指數、期貨與總體經濟: 0.0614 | 傳統製造與原物料: 0.0566 | 金融與保險業: 0.0555 | 生技與醫療: 0.0342 | 航運與物流: 0.0333 | 營建與房地產: 0.0301</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -837,6 +862,11 @@
           <t>生技與醫療: 0.8535 | 大盤指數、期貨與總體經濟: 0.023 | 其他產業或綜合新聞: 0.0226 | 民生消費與零售: 0.0186 | 航運與物流: 0.0149 | 金融與保險業: 0.0141 | 再生能源與永續發展: 0.0123 | 通訊網路與軟體服務: 0.0113 | 營建與房地產: 0.0112 | 電子科技與半導體: 0.0097 | 傳統製造與原物料: 0.0087</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -894,6 +924,11 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.2855 | 金融與保險業: 0.2564 | 電子科技與半導體: 0.0765 | 營建與房地產: 0.0718 | 民生消費與零售: 0.0579 | 其他產業或綜合新聞: 0.0569 | 生技與醫療: 0.052 | 再生能源與永續發展: 0.0441 | 通訊網路與軟體服務: 0.0356 | 航運與物流: 0.0318 | 傳統製造與原物料: 0.0314</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -967,6 +1002,11 @@
           <t>金融與保險業: 0.956 | 大盤指數、期貨與總體經濟: 0.0103 | 通訊網路與軟體服務: 0.0069 | 電子科技與半導體: 0.0053 | 其他產業或綜合新聞: 0.0045 | 再生能源與永續發展: 0.0037 | 生技與醫療: 0.0031 | 傳統製造與原物料: 0.0027 | 民生消費與零售: 0.0026 | 航運與物流: 0.0026 | 營建與房地產: 0.0023</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1036,6 +1076,11 @@
           <t>再生能源與永續發展: 0.2367 | 電子科技與半導體: 0.2355 | 其他產業或綜合新聞: 0.1825 | 通訊網路與軟體服務: 0.1303 | 大盤指數、期貨與總體經濟: 0.0778 | 生技與醫療: 0.0315 | 民生消費與零售: 0.0302 | 傳統製造與原物料: 0.0212 | 航運與物流: 0.0195 | 營建與房地產: 0.0185 | 金融與保險業: 0.0162</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1105,6 +1150,11 @@
           <t>電子科技與半導體: 0.8808 | 通訊網路與軟體服務: 0.0587 | 民生消費與零售: 0.0129 | 其他產業或綜合新聞: 0.0088 | 再生能源與永續發展: 0.0084 | 大盤指數、期貨與總體經濟: 0.0084 | 航運與物流: 0.0068 | 營建與房地產: 0.0043 | 生技與醫療: 0.004 | 傳統製造與原物料: 0.0039 | 金融與保險業: 0.003</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1168,6 +1218,11 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.9792 | 通訊網路與軟體服務: 0.0038 | 航運與物流: 0.0024 | 營建與房地產: 0.0024 | 生技與醫療: 0.0022 | 傳統製造與原物料: 0.0021 | 其他產業或綜合新聞: 0.0019 | 大盤指數、期貨與總體經濟: 0.0017 | 民生消費與零售: 0.0017 | 金融與保險業: 0.0014 | 再生能源與永續發展: 0.0012</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -1237,6 +1292,11 @@
           <t>電子科技與半導體: 0.6251 | 其他產業或綜合新聞: 0.1456 | 民生消費與零售: 0.0491 | 再生能源與永續發展: 0.0354 | 通訊網路與軟體服務: 0.0336 | 大盤指數、期貨與總體經濟: 0.0279 | 金融與保險業: 0.027 | 傳統製造與原物料: 0.0187 | 營建與房地產: 0.0166 | 航運與物流: 0.0111 | 生技與醫療: 0.01</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1304,6 +1364,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1363,6 +1428,11 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.7869 | 大盤指數、期貨與總體經濟: 0.0687 | 通訊網路與軟體服務: 0.0636 | 再生能源與永續發展: 0.0209 | 金融與保險業: 0.0169 | 民生消費與零售: 0.0129 | 傳統製造與原物料: 0.0089 | 航運與物流: 0.0087 | 其他產業或綜合新聞: 0.0058 | 生技與醫療: 0.0042 | 營建與房地產: 0.0026</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -1436,6 +1506,11 @@
           <t>通訊網路與軟體服務: 0.2565 | 電子科技與半導體: 0.2429 | 大盤指數、期貨與總體經濟: 0.0981 | 金融與保險業: 0.0849 | 其他產業或綜合新聞: 0.0818 | 再生能源與永續發展: 0.0652 | 民生消費與零售: 0.0495 | 生技與醫療: 0.0406 | 航運與物流: 0.0282 | 營建與房地產: 0.0266 | 傳統製造與原物料: 0.0255</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1501,6 +1576,11 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2237 | 再生能源與永續發展: 0.1275 | 通訊網路與軟體服務: 0.0994 | 民生消費與零售: 0.0843 | 大盤指數、期貨與總體經濟: 0.0838 | 其他產業或綜合新聞: 0.0798 | 金融與保險業: 0.078 | 營建與房地產: 0.0634 | 生技與醫療: 0.0586 | 傳統製造與原物料: 0.0532 | 航運與物流: 0.0481</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -1592,6 +1672,11 @@
           <t>電子科技與半導體: 0.2218 | 大盤指數、期貨與總體經濟: 0.1712 | 通訊網路與軟體服務: 0.096 | 金融與保險業: 0.0907 | 其他產業或綜合新聞: 0.08 | 再生能源與永續發展: 0.0694 | 生技與醫療: 0.0662 | 航運與物流: 0.0618 | 營建與房地產: 0.0584 | 民生消費與零售: 0.0526 | 傳統製造與原物料: 0.0318</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1661,6 +1746,11 @@
           <t>大盤指數、期貨與總體經濟: 0.1478 | 其他產業或綜合新聞: 0.1367 | 電子科技與半導體: 0.1254 | 通訊網路與軟體服務: 0.1042 | 金融與保險業: 0.0859 | 航運與物流: 0.0847 | 再生能源與永續發展: 0.084 | 民生消費與零售: 0.0734 | 傳統製造與原物料: 0.0626 | 生技與醫療: 0.0612 | 營建與房地產: 0.0342</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1722,6 +1812,11 @@
           <t>電子科技與半導體: 0.991 | 再生能源與永續發展: 0.0014 | 傳統製造與原物料: 0.0014 | 大盤指數、期貨與總體經濟: 0.0013 | 航運與物流: 0.001 | 民生消費與零售: 0.0009 | 營建與房地產: 0.0007 | 其他產業或綜合新聞: 0.0006 | 生技與醫療: 0.0006 | 金融與保險業: 0.0005 | 通訊網路與軟體服務: 0.0005</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1779,6 +1874,11 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.9001 | 大盤指數、期貨與總體經濟: 0.0382 | 傳統製造與原物料: 0.0132 | 其他產業或綜合新聞: 0.0084 | 民生消費與零售: 0.0069 | 航運與物流: 0.0068 | 通訊網路與軟體服務: 0.0067 | 營建與房地產: 0.0052 | 生技與醫療: 0.0052 | 再生能源與永續發展: 0.005 | 金融與保險業: 0.0042</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -1854,6 +1954,11 @@
           <t>傳統製造與原物料: 0.488 | 再生能源與永續發展: 0.1497 | 大盤指數、期貨與總體經濟: 0.1327 | 民生消費與零售: 0.0657 | 其他產業或綜合新聞: 0.0604 | 生技與醫療: 0.026 | 航運與物流: 0.0227 | 金融與保險業: 0.0221 | 營建與房地產: 0.0176 | 通訊網路與軟體服務: 0.009 | 電子科技與半導體: 0.006</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1925,6 +2030,11 @@
           <t>大盤指數、期貨與總體經濟: 0.7188 | 再生能源與永續發展: 0.0384 | 通訊網路與軟體服務: 0.0367 | 電子科技與半導體: 0.0362 | 民生消費與零售: 0.0343 | 金融與保險業: 0.034 | 其他產業或綜合新聞: 0.0325 | 傳統製造與原物料: 0.0279 | 航運與物流: 0.0158 | 生技與醫療: 0.0147 | 營建與房地產: 0.0107</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>總經與政策</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1988,6 +2098,11 @@
           <t>電子科技與半導體: 0.7492 | 金融與保險業: 0.0753 | 傳統製造與原物料: 0.0558 | 其他產業或綜合新聞: 0.0286 | 再生能源與永續發展: 0.0164 | 大盤指數、期貨與總體經濟: 0.0158 | 民生消費與零售: 0.015 | 通訊網路與軟體服務: 0.0126 | 航運與物流: 0.0111 | 生技與醫療: 0.0106 | 營建與房地產: 0.0097</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2047,6 +2162,11 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.2167 | 金融與保險業: 0.1697 | 民生消費與零售: 0.1044 | 傳統製造與原物料: 0.0975 | 電子科技與半導體: 0.095 | 營建與房地產: 0.0747 | 再生能源與永續發展: 0.0688 | 通訊網路與軟體服務: 0.0513 | 航運與物流: 0.0443 | 其他產業或綜合新聞: 0.044 | 生技與醫療: 0.0336</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -2118,6 +2238,11 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2247 | 通訊網路與軟體服務: 0.2119 | 再生能源與永續發展: 0.1637 | 大盤指數、期貨與總體經濟: 0.0982 | 其他產業或綜合新聞: 0.0668 | 營建與房地產: 0.0543 | 航運與物流: 0.0416 | 民生消費與零售: 0.0395 | 傳統製造與原物料: 0.0389 | 生技與醫療: 0.0316 | 金融與保險業: 0.0288</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -2225,6 +2350,11 @@
           <t>電子科技與半導體: 0.5779 | 大盤指數、期貨與總體經濟: 0.1458 | 金融與保險業: 0.1345 | 民生消費與零售: 0.0243 | 通訊網路與軟體服務: 0.0232 | 航運與物流: 0.0199 | 傳統製造與原物料: 0.0165 | 生技與醫療: 0.0163 | 再生能源與永續發展: 0.0154 | 營建與房地產: 0.0136 | 其他產業或綜合新聞: 0.0126</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2284,6 +2414,11 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>金融與保險業: 0.351 | 大盤指數、期貨與總體經濟: 0.2054 | 通訊網路與軟體服務: 0.0871 | 傳統製造與原物料: 0.077 | 其他產業或綜合新聞: 0.0744 | 再生能源與永續發展: 0.0566 | 電子科技與半導體: 0.0464 | 民生消費與零售: 0.041 | 航運與物流: 0.0239 | 生技與醫療: 0.019 | 營建與房地產: 0.0183</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -2357,6 +2492,11 @@
           <t>電子科技與半導體: 0.1663 | 民生消費與零售: 0.1137 | 通訊網路與軟體服務: 0.0963 | 再生能源與永續發展: 0.0959 | 生技與醫療: 0.0906 | 航運與物流: 0.0851 | 大盤指數、期貨與總體經濟: 0.0823 | 金融與保險業: 0.0765 | 營建與房地產: 0.0685 | 其他產業或綜合新聞: 0.0653 | 傳統製造與原物料: 0.0595</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2428,6 +2568,11 @@
           <t>電子科技與半導體: 0.2754 | 民生消費與零售: 0.1187 | 金融與保險業: 0.0896 | 大盤指數、期貨與總體經濟: 0.0891 | 傳統製造與原物料: 0.0853 | 其他產業或綜合新聞: 0.0824 | 再生能源與永續發展: 0.0824 | 生技與醫療: 0.069 | 通訊網路與軟體服務: 0.0552 | 航運與物流: 0.0296 | 營建與房地產: 0.0234</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2495,6 +2640,11 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -2564,6 +2714,11 @@
           <t>民生消費與零售: 0.5661 | 再生能源與永續發展: 0.2222 | 大盤指數、期貨與總體經濟: 0.0712 | 電子科技與半導體: 0.0368 | 其他產業或綜合新聞: 0.028 | 航運與物流: 0.0199 | 金融與保險業: 0.0176 | 通訊網路與軟體服務: 0.0127 | 生技與醫療: 0.0113 | 傳統製造與原物料: 0.0077 | 營建與房地產: 0.0065</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2633,6 +2788,11 @@
           <t>再生能源與永續發展: 0.138 | 電子科技與半導體: 0.1271 | 大盤指數、期貨與總體經濟: 0.1151 | 民生消費與零售: 0.1146 | 通訊網路與軟體服務: 0.109 | 其他產業或綜合新聞: 0.1079 | 金融與保險業: 0.104 | 航運與物流: 0.0792 | 生技與醫療: 0.0437 | 傳統製造與原物料: 0.0369 | 營建與房地產: 0.0246</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2700,6 +2860,11 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>其他產業或綜合新聞: 0.1349 | 電子科技與半導體: 0.1317 | 民生消費與零售: 0.1084 | 大盤指數、期貨與總體經濟: 0.1004 | 通訊網路與軟體服務: 0.0898 | 再生能源與永續發展: 0.0866 | 生技與醫療: 0.0802 | 航運與物流: 0.0754 | 金融與保險業: 0.0749 | 傳統製造與原物料: 0.0589 | 營建與房地產: 0.0588</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
         </is>
       </c>
     </row>
@@ -2783,6 +2948,11 @@
           <t>電子科技與半導體: 0.1285 | 民生消費與零售: 0.1246 | 其他產業或綜合新聞: 0.1093 | 再生能源與永續發展: 0.0939 | 傳統製造與原物料: 0.0873 | 大盤指數、期貨與總體經濟: 0.0861 | 航運與物流: 0.083 | 金融與保險業: 0.0777 | 通訊網路與軟體服務: 0.0774 | 生技與醫療: 0.0708 | 營建與房地產: 0.0614</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2850,6 +3020,11 @@
           <t>電子科技與半導體: 0.2288 | 其他產業或綜合新聞: 0.135 | 通訊網路與軟體服務: 0.0971 | 民生消費與零售: 0.0778 | 傳統製造與原物料: 0.0772 | 金融與保險業: 0.076 | 再生能源與永續發展: 0.0754 | 生技與醫療: 0.0737 | 航運與物流: 0.0633 | 營建與房地產: 0.0479 | 大盤指數、期貨與總體經濟: 0.0478</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2913,6 +3088,11 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -2978,6 +3158,11 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.4526 | 其他產業或綜合新聞: 0.2024 | 航運與物流: 0.0613 | 傳統製造與原物料: 0.0579 | 電子科技與半導體: 0.0548 | 通訊網路與軟體服務: 0.0466 | 民生消費與零售: 0.0446 | 再生能源與永續發展: 0.0257 | 營建與房地產: 0.0188 | 金融與保險業: 0.018 | 生技與醫療: 0.0174</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -3061,6 +3246,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3132,6 +3322,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3203,6 +3398,11 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.8596 | 通訊網路與軟體服務: 0.031 | 電子科技與半導體: 0.0237 | 金融與保險業: 0.0184 | 再生能源與永續發展: 0.0149 | 民生消費與零售: 0.0129 | 其他產業或綜合新聞: 0.0109 | 航運與物流: 0.0106 | 傳統製造與原物料: 0.0075 | 營建與房地產: 0.0055 | 生技與醫療: 0.0051</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -3282,6 +3482,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3355,6 +3560,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3420,6 +3630,11 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.4393 | 金融與保險業: 0.1637 | 再生能源與永續發展: 0.1134 | 其他產業或綜合新聞: 0.0434 | 傳統製造與原物料: 0.04 | 大盤指數、期貨與總體經濟: 0.039 | 通訊網路與軟體服務: 0.0386 | 航運與物流: 0.0353 | 民生消費與零售: 0.0334 | 營建與房地產: 0.027 | 生技與醫療: 0.027</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -3495,6 +3710,11 @@
           <t>電子科技與半導體: 0.4258 | 通訊網路與軟體服務: 0.1613 | 再生能源與永續發展: 0.0935 | 其他產業或綜合新聞: 0.0815 | 營建與房地產: 0.0564 | 民生消費與零售: 0.0392 | 金融與保險業: 0.0387 | 大盤指數、期貨與總體經濟: 0.0348 | 航運與物流: 0.0303 | 生技與醫療: 0.0234 | 傳統製造與原物料: 0.0151</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3560,6 +3780,11 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>其他產業或綜合新聞: 0.4365 | 電子科技與半導體: 0.1754 | 再生能源與永續發展: 0.0691 | 大盤指數、期貨與總體經濟: 0.0675 | 民生消費與零售: 0.0649 | 傳統製造與原物料: 0.0571 | 通訊網路與軟體服務: 0.0396 | 金融與保險業: 0.0324 | 航運與物流: 0.0256 | 營建與房地產: 0.017 | 生技與醫療: 0.0149</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -3631,6 +3856,11 @@
           <t>民生消費與零售: 0.1725 | 電子科技與半導體: 0.1174 | 通訊網路與軟體服務: 0.1172 | 其他產業或綜合新聞: 0.1049 | 生技與醫療: 0.0951 | 再生能源與永續發展: 0.0925 | 金融與保險業: 0.081 | 航運與物流: 0.0712 | 大盤指數、期貨與總體經濟: 0.0567 | 營建與房地產: 0.0536 | 傳統製造與原物料: 0.0379</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -3700,6 +3930,11 @@
           <t>電子科技與半導體: 0.2623 | 再生能源與永續發展: 0.1564 | 其他產業或綜合新聞: 0.1132 | 大盤指數、期貨與總體經濟: 0.1098 | 民生消費與零售: 0.1078 | 航運與物流: 0.0653 | 傳統製造與原物料: 0.0631 | 通訊網路與軟體服務: 0.0538 | 生技與醫療: 0.0266 | 營建與房地產: 0.0213 | 金融與保險業: 0.0204</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -3769,6 +4004,11 @@
           <t>通訊網路與軟體服務: 0.2701 | 其他產業或綜合新聞: 0.152 | 電子科技與半導體: 0.1382 | 大盤指數、期貨與總體經濟: 0.1038 | 再生能源與永續發展: 0.0745 | 民生消費與零售: 0.0656 | 航運與物流: 0.0599 | 傳統製造與原物料: 0.0544 | 營建與房地產: 0.0332 | 金融與保險業: 0.0244 | 生技與醫療: 0.0239</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3828,6 +4068,11 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2704 | 再生能源與永續發展: 0.2005 | 金融與保險業: 0.1003 | 民生消費與零售: 0.0788 | 大盤指數、期貨與總體經濟: 0.0712 | 其他產業或綜合新聞: 0.0546 | 通訊網路與軟體服務: 0.0524 | 航運與物流: 0.0508 | 傳統製造與原物料: 0.0483 | 生技與醫療: 0.0408 | 營建與房地產: 0.0318</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -3901,6 +4146,11 @@
           <t>通訊網路與軟體服務: 0.7641 | 大盤指數、期貨與總體經濟: 0.1149 | 電子科技與半導體: 0.0599 | 再生能源與永續發展: 0.022 | 其他產業或綜合新聞: 0.015 | 民生消費與零售: 0.0059 | 航運與物流: 0.0051 | 金融與保險業: 0.0043 | 生技與醫療: 0.0036 | 營建與房地產: 0.0033 | 傳統製造與原物料: 0.0019</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3966,6 +4216,11 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>營建與房地產: 0.8346 | 民生消費與零售: 0.1591 | 航運與物流: 0.0029 | 其他產業或綜合新聞: 0.0007 | 大盤指數、期貨與總體經濟: 0.0005 | 再生能源與永續發展: 0.0005 | 電子科技與半導體: 0.0004 | 傳統製造與原物料: 0.0003 | 通訊網路與軟體服務: 0.0003 | 生技與醫療: 0.0003 | 金融與保險業: 0.0002</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -4043,6 +4298,11 @@
           <t>大盤指數、期貨與總體經濟: 0.4216 | 其他產業或綜合新聞: 0.1499 | 民生消費與零售: 0.0981 | 再生能源與永續發展: 0.0909 | 金融與保險業: 0.0594 | 傳統製造與原物料: 0.0378 | 電子科技與半導體: 0.032 | 營建與房地產: 0.0315 | 航運與物流: 0.0314 | 生技與醫療: 0.0256 | 通訊網路與軟體服務: 0.0217</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4116,6 +4376,11 @@
           <t>大盤指數、期貨與總體經濟: 0.2059 | 金融與保險業: 0.1295 | 再生能源與永續發展: 0.1032 | 其他產業或綜合新聞: 0.0897 | 民生消費與零售: 0.0807 | 傳統製造與原物料: 0.0781 | 生技與醫療: 0.0665 | 通訊網路與軟體服務: 0.0665 | 營建與房地產: 0.0656 | 電子科技與半導體: 0.0632 | 航運與物流: 0.0512</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4185,6 +4450,11 @@
           <t>金融與保險業: 0.7391 | 大盤指數、期貨與總體經濟: 0.0521 | 其他產業或綜合新聞: 0.043 | 民生消費與零售: 0.0425 | 傳統製造與原物料: 0.0245 | 再生能源與永續發展: 0.0208 | 營建與房地產: 0.0201 | 航運與物流: 0.0193 | 電子科技與半導體: 0.0178 | 通訊網路與軟體服務: 0.0104 | 生技與醫療: 0.0103</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -4246,6 +4516,11 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>金融與保險業: 0.3045 | 大盤指數、期貨與總體經濟: 0.1233 | 民生消費與零售: 0.0975 | 再生能源與永續發展: 0.0938 | 傳統製造與原物料: 0.0874 | 通訊網路與軟體服務: 0.0678 | 其他產業或綜合新聞: 0.0623 | 航運與物流: 0.0545 | 電子科技與半導體: 0.0438 | 生技與醫療: 0.0335 | 營建與房地產: 0.0316</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>人事異動</t>
         </is>
       </c>
     </row>
@@ -4315,6 +4590,11 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>生技與醫療: 0.187 | 再生能源與永續發展: 0.1504 | 通訊網路與軟體服務: 0.1413 | 電子科技與半導體: 0.1321 | 傳統製造與原物料: 0.113 | 大盤指數、期貨與總體經濟: 0.0983 | 其他產業或綜合新聞: 0.0891 | 航運與物流: 0.0429 | 民生消費與零售: 0.0331 | 營建與房地產: 0.0073 | 金融與保險業: 0.0056</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -4388,6 +4668,11 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.192 | 其他產業或綜合新聞: 0.1652 | 通訊網路與軟體服務: 0.0936 | 金融與保險業: 0.0926 | 再生能源與永續發展: 0.0912 | 電子科技與半導體: 0.0891 | 民生消費與零售: 0.0742 | 營建與房地產: 0.0702 | 傳統製造與原物料: 0.0598 | 生技與醫療: 0.0378 | 航運與物流: 0.0344</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -4467,6 +4752,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -4536,6 +4826,11 @@
           <t>其他產業或綜合新聞: 0.1188 | 電子科技與半導體: 0.1109 | 大盤指數、期貨與總體經濟: 0.1099 | 民生消費與零售: 0.1054 | 再生能源與永續發展: 0.1024 | 金融與保險業: 0.1004 | 傳統製造與原物料: 0.0981 | 通訊網路與軟體服務: 0.0765 | 生技與醫療: 0.0715 | 營建與房地產: 0.0603 | 航運與物流: 0.0457</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -4605,6 +4900,11 @@
           <t>通訊網路與軟體服務: 0.2264 | 其他產業或綜合新聞: 0.1736 | 電子科技與半導體: 0.1485 | 大盤指數、期貨與總體經濟: 0.1068 | 再生能源與永續發展: 0.0989 | 民生消費與零售: 0.0755 | 航運與物流: 0.0585 | 傳統製造與原物料: 0.037 | 生技與醫療: 0.0279 | 營建與房地產: 0.0274 | 金融與保險業: 0.0196</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -4670,6 +4970,11 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.4564 | 電子科技與半導體: 0.2619 | 民生消費與零售: 0.153 | 航運與物流: 0.053 | 其他產業或綜合新聞: 0.0223 | 大盤指數、期貨與總體經濟: 0.0211 | 再生能源與永續發展: 0.0126 | 金融與保險業: 0.0076 | 生技與醫療: 0.0052 | 營建與房地產: 0.004 | 傳統製造與原物料: 0.003</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -4739,6 +5044,11 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.2166 | 其他產業或綜合新聞: 0.1309 | 民生消費與零售: 0.1219 | 航運與物流: 0.101 | 再生能源與永續發展: 0.0823 | 電子科技與半導體: 0.0818 | 金融與保險業: 0.0754 | 生技與醫療: 0.0613 | 營建與房地產: 0.0521 | 大盤指數、期貨與總體經濟: 0.0452 | 傳統製造與原物料: 0.0314</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -4814,6 +5124,11 @@
           <t>大盤指數、期貨與總體經濟: 0.1746 | 電子科技與半導體: 0.1308 | 再生能源與永續發展: 0.1224 | 通訊網路與軟體服務: 0.1061 | 金融與保險業: 0.1021 | 其他產業或綜合新聞: 0.0761 | 民生消費與零售: 0.0751 | 營建與房地產: 0.0608 | 航運與物流: 0.059 | 生技與醫療: 0.0524 | 傳統製造與原物料: 0.0404</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -4879,6 +5194,11 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.6092 | 通訊網路與軟體服務: 0.3582 | 大盤指數、期貨與總體經濟: 0.0199 | 再生能源與永續發展: 0.006 | 其他產業或綜合新聞: 0.0019 | 金融與保險業: 0.001 | 傳統製造與原物料: 0.001 | 航運與物流: 0.0009 | 民生消費與零售: 0.0008 | 營建與房地產: 0.0006 | 生技與醫療: 0.0006</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -4952,6 +5272,11 @@
           <t>電子科技與半導體: 0.1678 | 大盤指數、期貨與總體經濟: 0.1447 | 通訊網路與軟體服務: 0.1422 | 民生消費與零售: 0.0888 | 航運與物流: 0.0813 | 再生能源與永續發展: 0.0754 | 金融與保險業: 0.0738 | 生技與醫療: 0.0692 | 其他產業或綜合新聞: 0.0657 | 營建與房地產: 0.052 | 傳統製造與原物料: 0.0392</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -5019,6 +5344,11 @@
           <t>電子科技與半導體: 0.3164 | 金融與保險業: 0.0984 | 再生能源與永續發展: 0.0825 | 通訊網路與軟體服務: 0.0783 | 其他產業或綜合新聞: 0.0768 | 大盤指數、期貨與總體經濟: 0.0734 | 傳統製造與原物料: 0.0644 | 營建與房地產: 0.0612 | 民生消費與零售: 0.0555 | 生技與醫療: 0.0469 | 航運與物流: 0.046</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -5084,6 +5414,11 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>生技與醫療: 0.3007 | 其他產業或綜合新聞: 0.1728 | 大盤指數、期貨與總體經濟: 0.1287 | 金融與保險業: 0.0754 | 民生消費與零售: 0.0712 | 再生能源與永續發展: 0.0697 | 傳統製造與原物料: 0.0469 | 航運與物流: 0.0459 | 營建與房地產: 0.0318 | 通訊網路與軟體服務: 0.0293 | 電子科技與半導體: 0.0277</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -5155,6 +5490,11 @@
           <t>民生消費與零售: 0.9037 | 大盤指數、期貨與總體經濟: 0.0163 | 再生能源與永續發展: 0.0143 | 其他產業或綜合新聞: 0.0123 | 通訊網路與軟體服務: 0.0118 | 電子科技與半導體: 0.0087 | 生技與醫療: 0.0075 | 營建與房地產: 0.0074 | 航運與物流: 0.0067 | 金融與保險業: 0.0059 | 傳統製造與原物料: 0.0054</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -5218,6 +5558,11 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>航運與物流: 0.3954 | 大盤指數、期貨與總體經濟: 0.1903 | 再生能源與永續發展: 0.1126 | 其他產業或綜合新聞: 0.1092 | 電子科技與半導體: 0.0726 | 生技與醫療: 0.0293 | 傳統製造與原物料: 0.0279 | 民生消費與零售: 0.0183 | 通訊網路與軟體服務: 0.0163 | 金融與保險業: 0.0148 | 營建與房地產: 0.0135</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -5295,6 +5640,11 @@
           <t>通訊網路與軟體服務: 0.3542 | 電子科技與半導體: 0.1841 | 民生消費與零售: 0.1339 | 再生能源與永續發展: 0.0546 | 航運與物流: 0.054 | 其他產業或綜合新聞: 0.0496 | 金融與保險業: 0.0412 | 傳統製造與原物料: 0.0389 | 大盤指數、期貨與總體經濟: 0.0368 | 生技與醫療: 0.0298 | 營建與房地產: 0.0229</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -5360,6 +5710,11 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>金融與保險業: 0.1727 | 電子科技與半導體: 0.1443 | 民生消費與零售: 0.1251 | 其他產業或綜合新聞: 0.0986 | 通訊網路與軟體服務: 0.0874 | 大盤指數、期貨與總體經濟: 0.0797 | 再生能源與永續發展: 0.0779 | 傳統製造與原物料: 0.0676 | 營建與房地產: 0.0568 | 航運與物流: 0.0515 | 生技與醫療: 0.0384</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -5437,6 +5792,11 @@
           <t>電子科技與半導體: 0.9444 | 通訊網路與軟體服務: 0.0181 | 再生能源與永續發展: 0.0081 | 其他產業或綜合新聞: 0.0056 | 航運與物流: 0.005 | 民生消費與零售: 0.0048 | 生技與醫療: 0.0032 | 金融與保險業: 0.0029 | 傳統製造與原物料: 0.0028 | 大盤指數、期貨與總體經濟: 0.0027 | 營建與房地產: 0.0024</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -5504,6 +5864,11 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.4391 | 通訊網路與軟體服務: 0.2536 | 航運與物流: 0.0777 | 電子科技與半導體: 0.0498 | 再生能源與永續發展: 0.0475 | 大盤指數、期貨與總體經濟: 0.0468 | 其他產業或綜合新聞: 0.0337 | 金融與保險業: 0.0194 | 生技與醫療: 0.0158 | 營建與房地產: 0.0092 | 傳統製造與原物料: 0.0073</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -5573,6 +5938,11 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.4521 | 再生能源與永續發展: 0.154 | 其他產業或綜合新聞: 0.065 | 傳統製造與原物料: 0.0592 | 民生消費與零售: 0.0554 | 生技與醫療: 0.0517 | 航運與物流: 0.0459 | 通訊網路與軟體服務: 0.0365 | 金融與保險業: 0.03 | 電子科技與半導體: 0.0267 | 營建與房地產: 0.0235</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -5766,6 +6136,11 @@
           <t>大盤指數、期貨與總體經濟: 0.2718 | 其他產業或綜合新聞: 0.1201 | 民生消費與零售: 0.0993 | 再生能源與永續發展: 0.0937 | 傳統製造與原物料: 0.0839 | 營建與房地產: 0.0627 | 生技與醫療: 0.0592 | 金融與保險業: 0.0564 | 航運與物流: 0.0551 | 通訊網路與軟體服務: 0.0515 | 電子科技與半導體: 0.0464</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -5833,6 +6208,11 @@
           <t>電子科技與半導體: 0.1562 | 大盤指數、期貨與總體經濟: 0.1121 | 其他產業或綜合新聞: 0.1119 | 再生能源與永續發展: 0.1106 | 民生消費與零售: 0.1013 | 通訊網路與軟體服務: 0.0991 | 航運與物流: 0.0754 | 金融與保險業: 0.0715 | 生技與醫療: 0.0621 | 傳統製造與原物料: 0.0611 | 營建與房地產: 0.0387</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -5894,6 +6274,11 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -5959,6 +6344,11 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.2895 | 電子科技與半導體: 0.2644 | 大盤指數、期貨與總體經濟: 0.1672 | 其他產業或綜合新聞: 0.0527 | 金融與保險業: 0.0405 | 航運與物流: 0.0364 | 生技與醫療: 0.0359 | 再生能源與永續發展: 0.0332 | 營建與房地產: 0.0308 | 民生消費與零售: 0.026 | 傳統製造與原物料: 0.0232</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -6026,6 +6416,11 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.3029 | 通訊網路與軟體服務: 0.1552 | 再生能源與永續發展: 0.1211 | 傳統製造與原物料: 0.0701 | 民生消費與零售: 0.0591 | 大盤指數、期貨與總體經濟: 0.0591 | 金融與保險業: 0.0544 | 航運與物流: 0.0511 | 其他產業或綜合新聞: 0.0503 | 營建與房地產: 0.0386 | 生技與醫療: 0.0382</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -6097,6 +6492,11 @@
           <t>電子科技與半導體: 0.2584 | 航運與物流: 0.1099 | 再生能源與永續發展: 0.1011 | 其他產業或綜合新聞: 0.0899 | 通訊網路與軟體服務: 0.0845 | 民生消費與零售: 0.0803 | 大盤指數、期貨與總體經濟: 0.0724 | 生技與醫療: 0.0646 | 金融與保險業: 0.0607 | 傳統製造與原物料: 0.0432 | 營建與房地產: 0.035</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -6162,6 +6562,11 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2584 | 其他產業或綜合新聞: 0.1897 | 通訊網路與軟體服務: 0.1571 | 航運與物流: 0.1133 | 傳統製造與原物料: 0.0699 | 生技與醫療: 0.0512 | 再生能源與永續發展: 0.0405 | 民生消費與零售: 0.0393 | 大盤指數、期貨與總體經濟: 0.0389 | 金融與保險業: 0.027 | 營建與房地產: 0.0147</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -6237,6 +6642,11 @@
           <t>生技與醫療: 0.7673 | 大盤指數、期貨與總體經濟: 0.0317 | 金融與保險業: 0.0312 | 其他產業或綜合新聞: 0.0272 | 再生能源與永續發展: 0.0255 | 通訊網路與軟體服務: 0.0249 | 航運與物流: 0.0231 | 營建與房地產: 0.0218 | 民生消費與零售: 0.0183 | 傳統製造與原物料: 0.0151 | 電子科技與半導體: 0.0138</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -6308,6 +6718,11 @@
           <t>民生消費與零售: 0.1575 | 再生能源與永續發展: 0.1288 | 通訊網路與軟體服務: 0.1173 | 電子科技與半導體: 0.1072 | 大盤指數、期貨與總體經濟: 0.097 | 其他產業或綜合新聞: 0.0903 | 營建與房地產: 0.0735 | 生技與醫療: 0.0707 | 金融與保險業: 0.07 | 航運與物流: 0.0565 | 傳統製造與原物料: 0.031</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -6379,6 +6794,11 @@
           <t>電子科技與半導體: 0.9302 | 再生能源與永續發展: 0.0144 | 民生消費與零售: 0.0082 | 其他產業或綜合新聞: 0.0075 | 傳統製造與原物料: 0.0074 | 通訊網路與軟體服務: 0.0062 | 大盤指數、期貨與總體經濟: 0.006 | 生技與醫療: 0.0056 | 航運與物流: 0.0052 | 金融與保險業: 0.0051 | 營建與房地產: 0.0042</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -6446,6 +6866,11 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>金融與保險業: 0.218 | 其他產業或綜合新聞: 0.1244 | 民生消費與零售: 0.0952 | 生技與醫療: 0.0876 | 大盤指數、期貨與總體經濟: 0.0835 | 再生能源與永續發展: 0.0788 | 航運與物流: 0.0701 | 傳統製造與原物料: 0.0617 | 通訊網路與軟體服務: 0.0609 | 電子科技與半導體: 0.0608 | 營建與房地產: 0.059</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -6517,6 +6942,11 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>生技與醫療: 0.9115 | 金融與保險業: 0.0665 | 其他產業或綜合新聞: 0.0043 | 傳統製造與原物料: 0.0034 | 大盤指數、期貨與總體經濟: 0.0032 | 民生消費與零售: 0.0026 | 航運與物流: 0.0025 | 再生能源與永續發展: 0.0017 | 通訊網路與軟體服務: 0.0016 | 營建與房地產: 0.0016 | 電子科技與半導體: 0.001</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -6594,6 +7024,11 @@
           <t>生技與醫療: 0.1957 | 營建與房地產: 0.1865 | 大盤指數、期貨與總體經濟: 0.1185 | 航運與物流: 0.1135 | 通訊網路與軟體服務: 0.0721 | 電子科技與半導體: 0.0649 | 傳統製造與原物料: 0.0596 | 金融與保險業: 0.0575 | 民生消費與零售: 0.0534 | 再生能源與永續發展: 0.0486 | 其他產業或綜合新聞: 0.0296</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -6667,6 +7102,11 @@
           <t>電子科技與半導體: 0.9189 | 通訊網路與軟體服務: 0.0271 | 再生能源與永續發展: 0.0129 | 航運與物流: 0.0104 | 大盤指數、期貨與總體經濟: 0.0085 | 其他產業或綜合新聞: 0.0067 | 傳統製造與原物料: 0.0058 | 民生消費與零售: 0.0038 | 生技與醫療: 0.0023 | 營建與房地產: 0.0022 | 金融與保險業: 0.0014</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -6728,6 +7168,11 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>金融與保險業: 0.3262 | 大盤指數、期貨與總體經濟: 0.1123 | 其他產業或綜合新聞: 0.1116 | 營建與房地產: 0.0909 | 再生能源與永續發展: 0.0841 | 民生消費與零售: 0.0607 | 傳統製造與原物料: 0.0569 | 通訊網路與軟體服務: 0.0483 | 航運與物流: 0.0374 | 生技與醫療: 0.0368 | 電子科技與半導體: 0.0347</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -6805,6 +7250,11 @@
           <t>大盤指數、期貨與總體經濟: 0.2905 | 金融與保險業: 0.1964 | 航運與物流: 0.1046 | 民生消費與零售: 0.073 | 通訊網路與軟體服務: 0.0614 | 再生能源與永續發展: 0.0565 | 傳統製造與原物料: 0.0525 | 生技與醫療: 0.0479 | 其他產業或綜合新聞: 0.0478 | 電子科技與半導體: 0.0351 | 營建與房地產: 0.0342</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -6872,6 +7322,11 @@
       <c r="M91" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.927 | 再生能源與永續發展: 0.0143 | 航運與物流: 0.0123 | 生技與醫療: 0.0094 | 大盤指數、期貨與總體經濟: 0.009 | 電子科技與半導體: 0.006 | 傳統製造與原物料: 0.0053 | 其他產業或綜合新聞: 0.0048 | 通訊網路與軟體服務: 0.0041 | 營建與房地產: 0.0041 | 金融與保險業: 0.0035</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -6947,6 +7402,11 @@
           <t>電子科技與半導體: 0.2364 | 通訊網路與軟體服務: 0.1287 | 民生消費與零售: 0.0836 | 再生能源與永續發展: 0.0826 | 航運與物流: 0.0738 | 金融與保險業: 0.0711 | 營建與房地產: 0.0702 | 生技與醫療: 0.0677 | 其他產業或綜合新聞: 0.0633 | 傳統製造與原物料: 0.0615 | 大盤指數、期貨與總體經濟: 0.0611</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -7010,6 +7470,11 @@
       <c r="M93" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.7868 | 再生能源與永續發展: 0.068 | 傳統製造與原物料: 0.0368 | 通訊網路與軟體服務: 0.0214 | 航運與物流: 0.0177 | 營建與房地產: 0.014 | 生技與醫療: 0.0127 | 民生消費與零售: 0.0125 | 大盤指數、期貨與總體經濟: 0.0119 | 其他產業或綜合新聞: 0.0095 | 金融與保險業: 0.0086</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -7083,6 +7548,11 @@
           <t>再生能源與永續發展: 0.7601 | 民生消費與零售: 0.2184 | 其他產業或綜合新聞: 0.0052 | 生技與醫療: 0.0047 | 航運與物流: 0.0031 | 大盤指數、期貨與總體經濟: 0.0026 | 傳統製造與原物料: 0.002 | 營建與房地產: 0.0013 | 通訊網路與軟體服務: 0.001 | 金融與保險業: 0.0009 | 電子科技與半導體: 0.0007</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -7152,6 +7622,11 @@
           <t>營建與房地產: 0.3716 | 再生能源與永續發展: 0.1971 | 傳統製造與原物料: 0.1084 | 其他產業或綜合新聞: 0.0832 | 大盤指數、期貨與總體經濟: 0.0676 | 民生消費與零售: 0.0672 | 生技與醫療: 0.025 | 航運與物流: 0.0235 | 金融與保險業: 0.0203 | 通訊網路與軟體服務: 0.0198 | 電子科技與半導體: 0.0164</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -7215,6 +7690,11 @@
       <c r="M96" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.1814 | 金融與保險業: 0.1133 | 傳統製造與原物料: 0.1081 | 其他產業或綜合新聞: 0.1056 | 大盤指數、期貨與總體經濟: 0.0941 | 民生消費與零售: 0.0753 | 航運與物流: 0.072 | 生技與醫療: 0.0693 | 營建與房地產: 0.069 | 通訊網路與軟體服務: 0.0633 | 再生能源與永續發展: 0.0484</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -7290,6 +7770,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -7359,6 +7844,11 @@
       <c r="M98" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -7438,6 +7928,11 @@
           <t>通訊網路與軟體服務: 0.4719 | 電子科技與半導體: 0.108 | 再生能源與永續發展: 0.0735 | 大盤指數、期貨與總體經濟: 0.071 | 其他產業或綜合新聞: 0.0685 | 生技與醫療: 0.0622 | 航運與物流: 0.0474 | 營建與房地產: 0.0275 | 傳統製造與原物料: 0.0251 | 民生消費與零售: 0.024 | 金融與保險業: 0.021</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -7503,6 +7998,11 @@
       <c r="M100" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.4537 | 再生能源與永續發展: 0.1714 | 其他產業或綜合新聞: 0.088 | 通訊網路與軟體服務: 0.0656 | 民生消費與零售: 0.0616 | 傳統製造與原物料: 0.0348 | 金融與保險業: 0.0337 | 大盤指數、期貨與總體經濟: 0.0324 | 航運與物流: 0.0243 | 生技與醫療: 0.0182 | 營建與房地產: 0.0163</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -7574,6 +8074,11 @@
           <t>再生能源與永續發展: 0.6321 | 營建與房地產: 0.2082 | 傳統製造與原物料: 0.1287 | 電子科技與半導體: 0.0175 | 大盤指數、期貨與總體經濟: 0.004 | 其他產業或綜合新聞: 0.0034 | 民生消費與零售: 0.002 | 航運與物流: 0.0012 | 生技與醫療: 0.0012 | 金融與保險業: 0.001 | 通訊網路與軟體服務: 0.0006</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -7633,6 +8138,11 @@
       <c r="M102" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2346 | 民生消費與零售: 0.1913 | 再生能源與永續發展: 0.1277 | 大盤指數、期貨與總體經濟: 0.1223 | 金融與保險業: 0.0804 | 其他產業或綜合新聞: 0.064 | 傳統製造與原物料: 0.0541 | 航運與物流: 0.0488 | 營建與房地產: 0.0292 | 通訊網路與軟體服務: 0.0241 | 生技與醫療: 0.0234</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -7702,6 +8212,11 @@
       <c r="M103" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.5939 | 其他產業或綜合新聞: 0.0945 | 民生消費與零售: 0.0869 | 生技與醫療: 0.0571 | 電子科技與半導體: 0.0409 | 大盤指數、期貨與總體經濟: 0.0398 | 航運與物流: 0.0295 | 營建與房地產: 0.0196 | 通訊網路與軟體服務: 0.0152 | 金融與保險業: 0.0136 | 傳統製造與原物料: 0.0089</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>人事異動</t>
         </is>
       </c>
     </row>
@@ -7773,6 +8288,11 @@
       <c r="M104" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.1561 | 其他產業或綜合新聞: 0.1361 | 再生能源與永續發展: 0.1343 | 大盤指數、期貨與總體經濟: 0.1079 | 航運與物流: 0.0988 | 營建與房地產: 0.0981 | 民生消費與零售: 0.0884 | 通訊網路與軟體服務: 0.073 | 傳統製造與原物料: 0.041 | 金融與保險業: 0.0383 | 生技與醫療: 0.028</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -7878,6 +8398,11 @@
           <t>電子科技與半導體: 0.743 | 金融與保險業: 0.0786 | 大盤指數、期貨與總體經濟: 0.0634 | 通訊網路與軟體服務: 0.0326 | 民生消費與零售: 0.0168 | 航運與物流: 0.0147 | 傳統製造與原物料: 0.0138 | 再生能源與永續發展: 0.0119 | 生技與醫療: 0.0099 | 營建與房地產: 0.0086 | 其他產業或綜合新聞: 0.0067</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -7947,6 +8472,11 @@
           <t>電子科技與半導體: 0.8272 | 通訊網路與軟體服務: 0.0497 | 再生能源與永續發展: 0.0236 | 大盤指數、期貨與總體經濟: 0.0201 | 其他產業或綜合新聞: 0.0172 | 傳統製造與原物料: 0.0141 | 民生消費與零售: 0.0133 | 金融與保險業: 0.0103 | 航運與物流: 0.0099 | 營建與房地產: 0.0078 | 生技與醫療: 0.0068</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -8016,6 +8546,11 @@
           <t>電子科技與半導體: 0.9477 | 民生消費與零售: 0.0163 | 再生能源與永續發展: 0.0099 | 通訊網路與軟體服務: 0.008 | 傳統製造與原物料: 0.0034 | 航運與物流: 0.0033 | 生技與醫療: 0.0031 | 其他產業或綜合新聞: 0.0026 | 營建與房地產: 0.0022 | 大盤指數、期貨與總體經濟: 0.0019 | 金融與保險業: 0.0016</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -8083,6 +8618,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -8146,6 +8686,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -8209,6 +8754,11 @@
       <c r="M110" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2538 | 再生能源與永續發展: 0.1507 | 傳統製造與原物料: 0.1247 | 其他產業或綜合新聞: 0.0811 | 通訊網路與軟體服務: 0.0811 | 生技與醫療: 0.0618 | 營建與房地產: 0.0535 | 金融與保險業: 0.0517 | 大盤指數、期貨與總體經濟: 0.0505 | 民生消費與零售: 0.0493 | 航運與物流: 0.0418</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
         </is>
       </c>
     </row>
@@ -8302,6 +8852,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -8373,6 +8928,11 @@
       <c r="M112" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -8458,6 +9018,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -8523,6 +9088,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -8586,6 +9156,11 @@
       <c r="M115" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.3902 | 大盤指數、期貨與總體經濟: 0.1383 | 其他產業或綜合新聞: 0.0653 | 民生消費與零售: 0.0597 | 航運與物流: 0.0574 | 金融與保險業: 0.0545 | 傳統製造與原物料: 0.054 | 營建與房地產: 0.0472 | 生技與醫療: 0.0462 | 通訊網路與軟體服務: 0.0453 | 再生能源與永續發展: 0.0418</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -8653,6 +9228,11 @@
       <c r="M116" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -8726,6 +9306,11 @@
       <c r="M117" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.183 | 大盤指數、期貨與總體經濟: 0.1456 | 金融與保險業: 0.0981 | 生技與醫療: 0.0904 | 通訊網路與軟體服務: 0.0904 | 民生消費與零售: 0.0841 | 再生能源與永續發展: 0.0721 | 其他產業或綜合新聞: 0.0715 | 營建與房地產: 0.0682 | 航運與物流: 0.0558 | 傳統製造與原物料: 0.0407</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -8807,6 +9392,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -8880,6 +9470,11 @@
       <c r="M119" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.1365 | 電子科技與半導體: 0.1195 | 民生消費與零售: 0.101 | 大盤指數、期貨與總體經濟: 0.0989 | 金融與保險業: 0.0987 | 通訊網路與軟體服務: 0.0925 | 傳統製造與原物料: 0.0761 | 航運與物流: 0.0732 | 生技與醫療: 0.073 | 其他產業或綜合新聞: 0.0708 | 營建與房地產: 0.0598</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -8969,6 +9564,11 @@
           <t>電子科技與半導體: 0.1987 | 通訊網路與軟體服務: 0.1316 | 傳統製造與原物料: 0.1234 | 航運與物流: 0.0951 | 大盤指數、期貨與總體經濟: 0.0848 | 金融與保險業: 0.0713 | 民生消費與零售: 0.0693 | 其他產業或綜合新聞: 0.0675 | 生技與醫療: 0.0573 | 再生能源與永續發展: 0.0519 | 營建與房地產: 0.0492</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -9034,6 +9634,11 @@
       <c r="M121" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.534 | 大盤指數、期貨與總體經濟: 0.1097 | 其他產業或綜合新聞: 0.0997 | 傳統製造與原物料: 0.0528 | 通訊網路與軟體服務: 0.0463 | 再生能源與永續發展: 0.0405 | 民生消費與零售: 0.03 | 航運與物流: 0.0254 | 營建與房地產: 0.023 | 生技與醫療: 0.0222 | 金融與保險業: 0.0164</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -9107,6 +9712,11 @@
           <t>通訊網路與軟體服務: 0.1704 | 電子科技與半導體: 0.1161 | 再生能源與永續發展: 0.1032 | 金融與保險業: 0.0902 | 生技與醫療: 0.0811 | 其他產業或綜合新聞: 0.0808 | 民生消費與零售: 0.0796 | 航運與物流: 0.0794 | 營建與房地產: 0.0777 | 大盤指數、期貨與總體經濟: 0.0697 | 傳統製造與原物料: 0.0518</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -9174,6 +9784,11 @@
           <t>通訊網路與軟體服務: 0.8865 | 生技與醫療: 0.0316 | 電子科技與半導體: 0.0226 | 再生能源與永續發展: 0.017 | 其他產業或綜合新聞: 0.0118 | 民生消費與零售: 0.0081 | 營建與房地產: 0.0078 | 金融與保險業: 0.0044 | 航運與物流: 0.0041 | 大盤指數、期貨與總體經濟: 0.0034 | 傳統製造與原物料: 0.0028</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -9233,6 +9848,11 @@
       <c r="M124" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.5077 | 通訊網路與軟體服務: 0.0853 | 民生消費與零售: 0.0838 | 大盤指數、期貨與總體經濟: 0.079 | 航運與物流: 0.0767 | 再生能源與永續發展: 0.0564 | 其他產業或綜合新聞: 0.0316 | 金融與保險業: 0.0297 | 傳統製造與原物料: 0.0221 | 生技與醫療: 0.016 | 營建與房地產: 0.0118</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -9308,6 +9928,11 @@
           <t>生技與醫療: 0.2095 | 航運與物流: 0.1959 | 電子科技與半導體: 0.1025 | 金融與保險業: 0.0939 | 民生消費與零售: 0.0833 | 大盤指數、期貨與總體經濟: 0.0806 | 通訊網路與軟體服務: 0.0582 | 再生能源與永續發展: 0.0485 | 營建與房地產: 0.0429 | 傳統製造與原物料: 0.0427 | 其他產業或綜合新聞: 0.0419</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -9365,6 +9990,11 @@
       <c r="M126" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.5289 | 金融與保險業: 0.2043 | 民生消費與零售: 0.0564 | 其他產業或綜合新聞: 0.0462 | 營建與房地產: 0.0352 | 電子科技與半導體: 0.0332 | 通訊網路與軟體服務: 0.0213 | 航運與物流: 0.019 | 再生能源與永續發展: 0.0187 | 生技與醫療: 0.0186 | 傳統製造與原物料: 0.0181</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -9436,6 +10066,11 @@
           <t>金融與保險業: 0.1285 | 民生消費與零售: 0.1182 | 大盤指數、期貨與總體經濟: 0.1074 | 其他產業或綜合新聞: 0.106 | 再生能源與永續發展: 0.1019 | 傳統製造與原物料: 0.0963 | 生技與醫療: 0.0772 | 營建與房地產: 0.071 | 通訊網路與軟體服務: 0.0705 | 航運與物流: 0.0623 | 電子科技與半導體: 0.0607</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -9499,6 +10134,11 @@
           <t>營建與房地產: 0.9838 | 民生消費與零售: 0.007 | 金融與保險業: 0.002 | 大盤指數、期貨與總體經濟: 0.0019 | 其他產業或綜合新聞: 0.0011 | 傳統製造與原物料: 0.0009 | 航運與物流: 0.0009 | 生技與醫療: 0.0008 | 通訊網路與軟體服務: 0.0006 | 再生能源與永續發展: 0.0006 | 電子科技與半導體: 0.0004</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -9560,6 +10200,11 @@
       <c r="M129" t="inlineStr">
         <is>
           <t>營建與房地產: 0.9771 | 民生消費與零售: 0.0081 | 大盤指數、期貨與總體經濟: 0.0033 | 金融與保險業: 0.0031 | 其他產業或綜合新聞: 0.0023 | 再生能源與永續發展: 0.0015 | 傳統製造與原物料: 0.0013 | 航運與物流: 0.0013 | 生技與醫療: 0.0009 | 電子科技與半導體: 0.0007 | 通訊網路與軟體服務: 0.0005</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -9627,6 +10272,11 @@
       <c r="M130" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.7106 | 通訊網路與軟體服務: 0.077 | 其他產業或綜合新聞: 0.034 | 傳統製造與原物料: 0.0278 | 再生能源與永續發展: 0.0262 | 大盤指數、期貨與總體經濟: 0.0259 | 民生消費與零售: 0.0254 | 航運與物流: 0.0234 | 生技與醫療: 0.0177 | 營建與房地產: 0.0176 | 金融與保險業: 0.0143</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -9694,6 +10344,11 @@
       <c r="M131" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2815 | 金融與保險業: 0.1832 | 傳統製造與原物料: 0.0742 | 大盤指數、期貨與總體經濟: 0.0716 | 民生消費與零售: 0.0675 | 其他產業或綜合新聞: 0.067 | 再生能源與永續發展: 0.0603 | 通訊網路與軟體服務: 0.0591 | 航運與物流: 0.0528 | 營建與房地產: 0.0436 | 生技與醫療: 0.0392</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -9769,6 +10424,11 @@
           <t>航運與物流: 0.1244 | 其他產業或綜合新聞: 0.1214 | 民生消費與零售: 0.1068 | 大盤指數、期貨與總體經濟: 0.1042 | 通訊網路與軟體服務: 0.0897 | 電子科技與半導體: 0.0878 | 再生能源與永續發展: 0.0852 | 金融與保險業: 0.0823 | 營建與房地產: 0.0728 | 生技與醫療: 0.0679 | 傳統製造與原物料: 0.0576</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -9842,6 +10502,11 @@
           <t>電子科技與半導體: 0.328 | 其他產業或綜合新聞: 0.2604 | 通訊網路與軟體服務: 0.0841 | 再生能源與永續發展: 0.076 | 民生消費與零售: 0.0461 | 傳統製造與原物料: 0.0453 | 大盤指數、期貨與總體經濟: 0.04 | 金融與保險業: 0.037 | 營建與房地產: 0.0327 | 航運與物流: 0.0297 | 生技與醫療: 0.0207</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -9911,6 +10576,11 @@
       <c r="M134" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.5965 | 大盤指數、期貨與總體經濟: 0.1045 | 金融與保險業: 0.0885 | 生技與醫療: 0.0757 | 通訊網路與軟體服務: 0.0421 | 航運與物流: 0.0305 | 民生消費與零售: 0.0195 | 其他產業或綜合新聞: 0.0184 | 再生能源與永續發展: 0.0099 | 傳統製造與原物料: 0.0086 | 營建與房地產: 0.0057</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -9982,6 +10652,11 @@
       <c r="M135" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2906 | 通訊網路與軟體服務: 0.1125 | 其他產業或綜合新聞: 0.1067 | 再生能源與永續發展: 0.0957 | 金融與保險業: 0.0869 | 民生消費與零售: 0.0784 | 大盤指數、期貨與總體經濟: 0.0594 | 傳統製造與原物料: 0.0499 | 航運與物流: 0.0463 | 營建與房地產: 0.0422 | 生技與醫療: 0.0314</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -10055,6 +10730,11 @@
           <t>傳統製造與原物料: 0.4177 | 電子科技與半導體: 0.2135 | 大盤指數、期貨與總體經濟: 0.0741 | 其他產業或綜合新聞: 0.0582 | 再生能源與永續發展: 0.0424 | 通訊網路與軟體服務: 0.0406 | 民生消費與零售: 0.039 | 金融與保險業: 0.0328 | 生技與醫療: 0.029 | 航運與物流: 0.0279 | 營建與房地產: 0.0248</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -10126,6 +10806,11 @@
       <c r="M137" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.3971 | 電子科技與半導體: 0.1007 | 金融與保險業: 0.0801 | 大盤指數、期貨與總體經濟: 0.0766 | 再生能源與永續發展: 0.0692 | 其他產業或綜合新聞: 0.0655 | 民生消費與零售: 0.0578 | 生技與醫療: 0.0494 | 營建與房地產: 0.039 | 航運與物流: 0.0338 | 傳統製造與原物料: 0.0308</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -10203,6 +10888,11 @@
           <t>通訊網路與軟體服務: 0.2509 | 再生能源與永續發展: 0.1489 | 電子科技與半導體: 0.1402 | 民生消費與零售: 0.0939 | 大盤指數、期貨與總體經濟: 0.0874 | 其他產業或綜合新聞: 0.0704 | 金融與保險業: 0.0566 | 航運與物流: 0.0468 | 傳統製造與原物料: 0.0417 | 生技與醫療: 0.0332 | 營建與房地產: 0.0299</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -10272,6 +10962,11 @@
           <t>通訊網路與軟體服務: 0.838 | 大盤指數、期貨與總體經濟: 0.0581 | 民生消費與零售: 0.0303 | 電子科技與半導體: 0.0279 | 其他產業或綜合新聞: 0.0141 | 航運與物流: 0.01 | 再生能源與永續發展: 0.0075 | 金融與保險業: 0.0043 | 生技與醫療: 0.0043 | 營建與房地產: 0.0031 | 傳統製造與原物料: 0.0024</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -10339,6 +11034,11 @@
           <t>電子科技與半導體: 0.2703 | 大盤指數、期貨與總體經濟: 0.1265 | 通訊網路與軟體服務: 0.1174 | 其他產業或綜合新聞: 0.0872 | 民生消費與零售: 0.0785 | 航運與物流: 0.0733 | 金融與保險業: 0.0669 | 再生能源與永續發展: 0.0615 | 傳統製造與原物料: 0.0505 | 生技與醫療: 0.0431 | 營建與房地產: 0.0249</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -10406,6 +11106,11 @@
       <c r="M141" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.8791 | 再生能源與永續發展: 0.0253 | 其他產業或綜合新聞: 0.0203 | 通訊網路與軟體服務: 0.0157 | 大盤指數、期貨與總體經濟: 0.011 | 民生消費與零售: 0.01 | 航運與物流: 0.0096 | 傳統製造與原物料: 0.008 | 生技與醫療: 0.0076 | 營建與房地產: 0.0076 | 金融與保險業: 0.0058</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -10495,6 +11200,11 @@
           <t>大盤指數、期貨與總體經濟: 0.4097 | 其他產業或綜合新聞: 0.1456 | 再生能源與永續發展: 0.0908 | 民生消費與零售: 0.0787 | 金融與保險業: 0.0646 | 電子科技與半導體: 0.0549 | 傳統製造與原物料: 0.0499 | 通訊網路與軟體服務: 0.0374 | 航運與物流: 0.0246 | 生技與醫療: 0.0227 | 營建與房地產: 0.0211</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -10554,6 +11264,11 @@
       <c r="M143" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2889 | 大盤指數、期貨與總體經濟: 0.1168 | 再生能源與永續發展: 0.1029 | 民生消費與零售: 0.0877 | 金融與保險業: 0.0853 | 通訊網路與軟體服務: 0.0713 | 生技與醫療: 0.0677 | 營建與房地產: 0.0568 | 傳統製造與原物料: 0.0443 | 航運與物流: 0.0411 | 其他產業或綜合新聞: 0.0371</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -10633,6 +11348,11 @@
           <t>其他產業或綜合新聞: 0.2291 | 電子科技與半導體: 0.126 | 民生消費與零售: 0.0944 | 通訊網路與軟體服務: 0.0836 | 金融與保險業: 0.08 | 大盤指數、期貨與總體經濟: 0.0741 | 再生能源與永續發展: 0.0729 | 航運與物流: 0.0644 | 傳統製造與原物料: 0.0602 | 營建與房地產: 0.0601 | 生技與醫療: 0.0551</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -10698,6 +11418,11 @@
           <t>再生能源與永續發展: 0.8217 | 民生消費與零售: 0.1739 | 傳統製造與原物料: 0.0009 | 航運與物流: 0.0008 | 其他產業或綜合新聞: 0.0006 | 營建與房地產: 0.0006 | 大盤指數、期貨與總體經濟: 0.0005 | 生技與醫療: 0.0005 | 電子科技與半導體: 0.0002 | 通訊網路與軟體服務: 0.0002 | 金融與保險業: 0.0002</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -10759,6 +11484,11 @@
       <c r="M146" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.9861 | 大盤指數、期貨與總體經濟: 0.0055 | 其他產業或綜合新聞: 0.0015 | 通訊網路與軟體服務: 0.0012 | 傳統製造與原物料: 0.0011 | 金融與保險業: 0.0009 | 航運與物流: 0.0008 | 民生消費與零售: 0.0008 | 再生能源與永續發展: 0.0007 | 生技與醫療: 0.0006 | 營建與房地產: 0.0006</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -10832,6 +11562,11 @@
           <t>通訊網路與軟體服務: 0.596 | 電子科技與半導體: 0.1126 | 再生能源與永續發展: 0.0852 | 大盤指數、期貨與總體經濟: 0.0699 | 其他產業或綜合新聞: 0.0431 | 民生消費與零售: 0.0371 | 金融與保險業: 0.0155 | 航運與物流: 0.0132 | 生技與醫療: 0.0108 | 營建與房地產: 0.0091 | 傳統製造與原物料: 0.0075</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -10901,6 +11636,11 @@
           <t>金融與保險業: 0.1686 | 通訊網路與軟體服務: 0.1615 | 電子科技與半導體: 0.1119 | 民生消費與零售: 0.1065 | 大盤指數、期貨與總體經濟: 0.0836 | 營建與房地產: 0.0823 | 其他產業或綜合新聞: 0.0784 | 航運與物流: 0.0693 | 再生能源與永續發展: 0.0585 | 生技與醫療: 0.0575 | 傳統製造與原物料: 0.0218</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -10968,6 +11708,11 @@
           <t>電子科技與半導體: 0.8007 | 通訊網路與軟體服務: 0.0948 | 再生能源與永續發展: 0.024 | 其他產業或綜合新聞: 0.0204 | 傳統製造與原物料: 0.0122 | 金融與保險業: 0.0092 | 航運與物流: 0.0089 | 民生消費與零售: 0.008 | 生技與醫療: 0.0077 | 營建與房地產: 0.0076 | 大盤指數、期貨與總體經濟: 0.0065</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -11033,6 +11778,11 @@
       <c r="M150" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.3634 | 電子科技與半導體: 0.1854 | 金融與保險業: 0.1732 | 其他產業或綜合新聞: 0.0732 | 通訊網路與軟體服務: 0.0482 | 再生能源與永續發展: 0.0344 | 營建與房地產: 0.0309 | 生技與醫療: 0.0287 | 航運與物流: 0.0218 | 傳統製造與原物料: 0.0206 | 民生消費與零售: 0.0202</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -11140,6 +11890,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -11207,6 +11962,11 @@
           <t>電子科技與半導體: 0.2065 | 通訊網路與軟體服務: 0.145 | 民生消費與零售: 0.14 | 金融與保險業: 0.1051 | 再生能源與永續發展: 0.0964 | 營建與房地產: 0.0627 | 大盤指數、期貨與總體經濟: 0.0559 | 其他產業或綜合新聞: 0.0557 | 傳統製造與原物料: 0.0523 | 航運與物流: 0.0435 | 生技與醫療: 0.0367</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -11272,6 +12032,11 @@
       <c r="M153" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.3014 | 電子科技與半導體: 0.1703 | 其他產業或綜合新聞: 0.1409 | 再生能源與永續發展: 0.1204 | 營建與房地產: 0.0557 | 傳統製造與原物料: 0.0495 | 生技與醫療: 0.0424 | 民生消費與零售: 0.035 | 航運與物流: 0.0336 | 金融與保險業: 0.0271 | 大盤指數、期貨與總體經濟: 0.0236</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -11343,6 +12108,11 @@
           <t>民生消費與零售: 0.2418 | 大盤指數、期貨與總體經濟: 0.2115 | 電子科技與半導體: 0.1741 | 生技與醫療: 0.1205 | 其他產業或綜合新聞: 0.0695 | 再生能源與永續發展: 0.0494 | 航運與物流: 0.0425 | 通訊網路與軟體服務: 0.0389 | 傳統製造與原物料: 0.03 | 金融與保險業: 0.0126 | 營建與房地產: 0.0091</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -11412,6 +12182,11 @@
           <t>其他產業或綜合新聞: 0.2827 | 電子科技與半導體: 0.2567 | 大盤指數、期貨與總體經濟: 0.1126 | 通訊網路與軟體服務: 0.0843 | 金融與保險業: 0.0677 | 再生能源與永續發展: 0.0586 | 生技與醫療: 0.0365 | 航運與物流: 0.0329 | 民生消費與零售: 0.0295 | 營建與房地產: 0.0218 | 傳統製造與原物料: 0.0167</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -11471,6 +12246,11 @@
       <c r="M156" t="inlineStr">
         <is>
           <t>金融與保險業: 0.2511 | 民生消費與零售: 0.2296 | 再生能源與永續發展: 0.0753 | 其他產業或綜合新聞: 0.0742 | 電子科技與半導體: 0.0636 | 營建與房地產: 0.0625 | 大盤指數、期貨與總體經濟: 0.0574 | 航運與物流: 0.0566 | 傳統製造與原物料: 0.0508 | 生技與醫療: 0.0466 | 通訊網路與軟體服務: 0.0322</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -11552,6 +12332,11 @@
           <t>電子科技與半導體: 0.4537 | 其他產業或綜合新聞: 0.1172 | 通訊網路與軟體服務: 0.0885 | 再生能源與永續發展: 0.0795 | 民生消費與零售: 0.064 | 金融與保險業: 0.0478 | 傳統製造與原物料: 0.0381 | 生技與醫療: 0.0346 | 大盤指數、期貨與總體經濟: 0.0302 | 航運與物流: 0.025 | 營建與房地產: 0.0216</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -11621,6 +12406,11 @@
           <t>電子科技與半導體: 0.8824 | 再生能源與永續發展: 0.0192 | 通訊網路與軟體服務: 0.016 | 傳統製造與原物料: 0.0136 | 其他產業或綜合新聞: 0.0119 | 營建與房地產: 0.0117 | 大盤指數、期貨與總體經濟: 0.0103 | 民生消費與零售: 0.0098 | 生技與醫療: 0.0087 | 航運與物流: 0.0087 | 金融與保險業: 0.0077</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -11690,6 +12480,11 @@
           <t>通訊網路與軟體服務: 0.7761 | 電子科技與半導體: 0.0484 | 其他產業或綜合新聞: 0.0398 | 再生能源與永續發展: 0.0365 | 大盤指數、期貨與總體經濟: 0.0266 | 民生消費與零售: 0.0204 | 金融與保險業: 0.0136 | 傳統製造與原物料: 0.0121 | 航運與物流: 0.0107 | 生技與醫療: 0.0095 | 營建與房地產: 0.0062</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -11757,6 +12552,11 @@
           <t>其他產業或綜合新聞: 0.2175 | 金融與保險業: 0.1965 | 傳統製造與原物料: 0.0916 | 電子科技與半導體: 0.078 | 生技與醫療: 0.0727 | 通訊網路與軟體服務: 0.0715 | 再生能源與永續發展: 0.0684 | 大盤指數、期貨與總體經濟: 0.0558 | 民生消費與零售: 0.0529 | 營建與房地產: 0.0496 | 航運與物流: 0.0455</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -11818,6 +12618,11 @@
       <c r="M161" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.224 | 再生能源與永續發展: 0.1839 | 航運與物流: 0.0969 | 傳統製造與原物料: 0.0893 | 大盤指數、期貨與總體經濟: 0.0753 | 營建與房地產: 0.0622 | 金融與保險業: 0.0609 | 通訊網路與軟體服務: 0.06 | 其他產業或綜合新聞: 0.0589 | 生技與醫療: 0.0536 | 民生消費與零售: 0.0351</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -11889,6 +12694,11 @@
           <t>電子科技與半導體: 0.16 | 通訊網路與軟體服務: 0.1318 | 再生能源與永續發展: 0.113 | 大盤指數、期貨與總體經濟: 0.1115 | 生技與醫療: 0.0845 | 其他產業或綜合新聞: 0.0786 | 金融與保險業: 0.0744 | 民生消費與零售: 0.0707 | 航運與物流: 0.0626 | 營建與房地產: 0.0608 | 傳統製造與原物料: 0.0521</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -11954,6 +12764,11 @@
       <c r="M163" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.6624 | 生技與醫療: 0.2196 | 再生能源與永續發展: 0.0293 | 其他產業或綜合新聞: 0.0145 | 大盤指數、期貨與總體經濟: 0.0134 | 傳統製造與原物料: 0.0134 | 航運與物流: 0.012 | 通訊網路與軟體服務: 0.0109 | 民生消費與零售: 0.0089 | 營建與房地產: 0.0089 | 金融與保險業: 0.0065</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -12025,6 +12840,11 @@
           <t>航運與物流: 0.6041 | 其他產業或綜合新聞: 0.0944 | 電子科技與半導體: 0.0604 | 生技與醫療: 0.0543 | 大盤指數、期貨與總體經濟: 0.0477 | 金融與保險業: 0.0385 | 傳統製造與原物料: 0.0356 | 再生能源與永續發展: 0.0225 | 通訊網路與軟體服務: 0.0165 | 民生消費與零售: 0.016 | 營建與房地產: 0.01</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -12086,6 +12906,11 @@
       <c r="M165" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.163 | 金融與保險業: 0.1517 | 電子科技與半導體: 0.1333 | 大盤指數、期貨與總體經濟: 0.1275 | 再生能源與永續發展: 0.0924 | 營建與房地產: 0.0744 | 通訊網路與軟體服務: 0.0631 | 其他產業或綜合新聞: 0.0627 | 傳統製造與原物料: 0.0578 | 航運與物流: 0.0384 | 生技與醫療: 0.0357</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -12159,6 +12984,11 @@
       <c r="M166" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2587 | 再生能源與永續發展: 0.1828 | 民生消費與零售: 0.1655 | 通訊網路與軟體服務: 0.0894 | 大盤指數、期貨與總體經濟: 0.0828 | 其他產業或綜合新聞: 0.0511 | 金融與保險業: 0.0468 | 航運與物流: 0.0346 | 營建與房地產: 0.0331 | 傳統製造與原物料: 0.0279 | 生技與醫療: 0.0272</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -12240,6 +13070,11 @@
           <t>大盤指數、期貨與總體經濟: 0.274 | 其他產業或綜合新聞: 0.2072 | 金融與保險業: 0.1743 | 電子科技與半導體: 0.0832 | 營建與房地產: 0.0523 | 民生消費與零售: 0.0436 | 再生能源與永續發展: 0.0396 | 航運與物流: 0.0337 | 生技與醫療: 0.0329 | 通訊網路與軟體服務: 0.0296 | 傳統製造與原物料: 0.0295</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>總經與政策</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -12311,6 +13146,11 @@
           <t>電子科技與半導體: 0.2955 | 再生能源與永續發展: 0.2503 | 其他產業或綜合新聞: 0.139 | 通訊網路與軟體服務: 0.1363 | 傳統製造與原物料: 0.0939 | 大盤指數、期貨與總體經濟: 0.0299 | 民生消費與零售: 0.0221 | 航運與物流: 0.0149 | 生技與醫療: 0.0073 | 營建與房地產: 0.0055 | 金融與保險業: 0.0052</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -12382,6 +13222,11 @@
           <t>其他產業或綜合新聞: 0.4223 | 大盤指數、期貨與總體經濟: 0.2023 | 金融與保險業: 0.0821 | 民生消費與零售: 0.0727 | 再生能源與永續發展: 0.0603 | 航運與物流: 0.0385 | 傳統製造與原物料: 0.0312 | 營建與房地產: 0.0282 | 電子科技與半導體: 0.0247 | 生技與醫療: 0.0215 | 通訊網路與軟體服務: 0.0162</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -12451,6 +13296,11 @@
           <t>金融與保險業: 0.2881 | 再生能源與永續發展: 0.115 | 其他產業或綜合新聞: 0.0903 | 電子科技與半導體: 0.088 | 通訊網路與軟體服務: 0.0705 | 大盤指數、期貨與總體經濟: 0.0678 | 民生消費與零售: 0.0637 | 傳統製造與原物料: 0.0615 | 營建與房地產: 0.0603 | 航運與物流: 0.0488 | 生技與醫療: 0.0462</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -12518,6 +13368,11 @@
       <c r="M171" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.8331 | 營建與房地產: 0.0511 | 其他產業或綜合新聞: 0.0415 | 電子科技與半導體: 0.0166 | 大盤指數、期貨與總體經濟: 0.0163 | 民生消費與零售: 0.0129 | 生技與醫療: 0.0075 | 航運與物流: 0.0059 | 金融與保險業: 0.0058 | 傳統製造與原物料: 0.0051 | 通訊網路與軟體服務: 0.0042</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -12595,6 +13450,11 @@
           <t>營建與房地產: 0.3966 | 電子科技與半導體: 0.3181 | 通訊網路與軟體服務: 0.1591 | 大盤指數、期貨與總體經濟: 0.0295 | 民生消費與零售: 0.0169 | 傳統製造與原物料: 0.0166 | 生技與醫療: 0.0158 | 金融與保險業: 0.0139 | 再生能源與永續發展: 0.0131 | 其他產業或綜合新聞: 0.012 | 航運與物流: 0.0083</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -12668,6 +13528,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -12731,6 +13596,11 @@
       <c r="M174" t="inlineStr">
         <is>
           <t>其他產業或綜合新聞: 0.1801 | 民生消費與零售: 0.1713 | 再生能源與永續發展: 0.1264 | 大盤指數、期貨與總體經濟: 0.1211 | 傳統製造與原物料: 0.1058 | 金融與保險業: 0.099 | 營建與房地產: 0.0635 | 生技與醫療: 0.0392 | 通訊網路與軟體服務: 0.0342 | 航運與物流: 0.03 | 電子科技與半導體: 0.0294</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -12806,6 +13676,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -12879,6 +13754,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -12950,6 +13830,11 @@
       <c r="M177" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.1547 | 再生能源與永續發展: 0.12 | 通訊網路與軟體服務: 0.1181 | 民生消費與零售: 0.1061 | 其他產業或綜合新聞: 0.0964 | 傳統製造與原物料: 0.0778 | 金融與保險業: 0.0738 | 生技與醫療: 0.0689 | 大盤指數、期貨與總體經濟: 0.0672 | 航運與物流: 0.0656 | 營建與房地產: 0.0515</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -13029,6 +13914,11 @@
           <t>再生能源與永續發展: 0.1519 | 其他產業或綜合新聞: 0.1306 | 大盤指數、期貨與總體經濟: 0.1005 | 電子科技與半導體: 0.0915 | 通訊網路與軟體服務: 0.0906 | 民生消費與零售: 0.0856 | 營建與房地產: 0.083 | 生技與醫療: 0.0732 | 金融與保險業: 0.0691 | 傳統製造與原物料: 0.0668 | 航運與物流: 0.0573</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -13088,6 +13978,11 @@
       <c r="M179" t="inlineStr">
         <is>
           <t>金融與保險業: 0.2118 | 民生消費與零售: 0.1763 | 大盤指數、期貨與總體經濟: 0.1086 | 營建與房地產: 0.1003 | 傳統製造與原物料: 0.0909 | 其他產業或綜合新聞: 0.0712 | 電子科技與半導體: 0.066 | 再生能源與永續發展: 0.0647 | 航運與物流: 0.04 | 通訊網路與軟體服務: 0.0355 | 生技與醫療: 0.0345</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -13161,6 +14056,11 @@
           <t>電子科技與半導體: 0.1425 | 金融與保險業: 0.1323 | 大盤指數、期貨與總體經濟: 0.121 | 再生能源與永續發展: 0.1143 | 營建與房地產: 0.0913 | 通訊網路與軟體服務: 0.089 | 其他產業或綜合新聞: 0.0823 | 民生消費與零售: 0.0697 | 傳統製造與原物料: 0.059 | 生技與醫療: 0.0494 | 航運與物流: 0.0492</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -13218,6 +14118,11 @@
       <c r="M181" t="inlineStr">
         <is>
           <t>金融與保險業: 0.2457 | 大盤指數、期貨與總體經濟: 0.2033 | 營建與房地產: 0.1262 | 電子科技與半導體: 0.0849 | 再生能源與永續發展: 0.0599 | 航運與物流: 0.0563 | 民生消費與零售: 0.0559 | 生技與醫療: 0.0546 | 通訊網路與軟體服務: 0.0475 | 其他產業或綜合新聞: 0.0391 | 傳統製造與原物料: 0.0267</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>股利與除權息</t>
         </is>
       </c>
     </row>
@@ -13367,6 +14272,11 @@
           <t>大盤指數、期貨與總體經濟: 0.6124 | 民生消費與零售: 0.0772 | 航運與物流: 0.0543 | 金融與保險業: 0.0497 | 再生能源與永續發展: 0.0432 | 傳統製造與原物料: 0.0379 | 其他產業或綜合新聞: 0.0308 | 生技與醫療: 0.0274 | 通訊網路與軟體服務: 0.0247 | 營建與房地產: 0.0219 | 電子科技與半導體: 0.0204</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -13432,6 +14342,11 @@
       <c r="M183" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -13507,6 +14422,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -13574,6 +14494,11 @@
           <t>大盤指數、期貨與總體經濟: 0.2168 | 電子科技與半導體: 0.1312 | 其他產業或綜合新聞: 0.1179 | 金融與保險業: 0.0905 | 通訊網路與軟體服務: 0.0879 | 再生能源與永續發展: 0.0791 | 民生消費與零售: 0.0592 | 生技與醫療: 0.058 | 營建與房地產: 0.0564 | 航運與物流: 0.0521 | 傳統製造與原物料: 0.0508</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -13639,6 +14564,11 @@
       <c r="M186" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.641 | 通訊網路與軟體服務: 0.0705 | 再生能源與永續發展: 0.0645 | 大盤指數、期貨與總體經濟: 0.0553 | 傳統製造與原物料: 0.0545 | 航運與物流: 0.0267 | 民生消費與零售: 0.0243 | 金融與保險業: 0.0227 | 生技與醫療: 0.0161 | 其他產業或綜合新聞: 0.0156 | 營建與房地產: 0.0088</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -13710,6 +14640,11 @@
           <t>大盤指數、期貨與總體經濟: 0.3733 | 電子科技與半導體: 0.098 | 民生消費與零售: 0.0928 | 再生能源與永續發展: 0.0821 | 航運與物流: 0.0811 | 其他產業或綜合新聞: 0.0678 | 金融與保險業: 0.0533 | 生技與醫療: 0.0521 | 傳統製造與原物料: 0.0414 | 通訊網路與軟體服務: 0.0361 | 營建與房地產: 0.0221</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -13777,6 +14712,11 @@
       <c r="M188" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.203 | 電子科技與半導體: 0.1676 | 大盤指數、期貨與總體經濟: 0.1581 | 再生能源與永續發展: 0.1181 | 其他產業或綜合新聞: 0.0772 | 傳統製造與原物料: 0.0764 | 民生消費與零售: 0.0612 | 金融與保險業: 0.0511 | 航運與物流: 0.0329 | 生技與醫療: 0.0286 | 營建與房地產: 0.0259</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -13852,6 +14792,11 @@
           <t>大盤指數、期貨與總體經濟: 0.3811 | 電子科技與半導體: 0.1624 | 再生能源與永續發展: 0.1168 | 通訊網路與軟體服務: 0.0898 | 其他產業或綜合新聞: 0.0791 | 金融與保險業: 0.0491 | 民生消費與零售: 0.0301 | 傳統製造與原物料: 0.0284 | 航運與物流: 0.0252 | 生技與醫療: 0.0228 | 營建與房地產: 0.0153</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -13919,6 +14864,11 @@
       <c r="M190" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.3922 | 通訊網路與軟體服務: 0.1299 | 大盤指數、期貨與總體經濟: 0.0894 | 再生能源與永續發展: 0.0891 | 其他產業或綜合新聞: 0.0813 | 金融與保險業: 0.0541 | 民生消費與零售: 0.0532 | 生技與醫療: 0.0432 | 傳統製造與原物料: 0.0256 | 航運與物流: 0.0239 | 營建與房地產: 0.0182</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -13990,6 +14940,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -14055,6 +15010,11 @@
           <t>電子科技與半導體: 0.7133 | 金融與保險業: 0.0688 | 通訊網路與軟體服務: 0.0493 | 民生消費與零售: 0.0394 | 其他產業或綜合新聞: 0.0319 | 再生能源與永續發展: 0.0266 | 傳統製造與原物料: 0.0174 | 營建與房地產: 0.016 | 航運與物流: 0.0138 | 大盤指數、期貨與總體經濟: 0.0126 | 生技與醫療: 0.0109</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -14120,6 +15080,11 @@
       <c r="M193" t="inlineStr">
         <is>
           <t>航運與物流: 0.3005 | 電子科技與半導體: 0.157 | 再生能源與永續發展: 0.1427 | 民生消費與零售: 0.0596 | 其他產業或綜合新聞: 0.0583 | 生技與醫療: 0.0551 | 傳統製造與原物料: 0.0546 | 大盤指數、期貨與總體經濟: 0.0471 | 營建與房地產: 0.0424 | 金融與保險業: 0.0414 | 通訊網路與軟體服務: 0.0414</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -14193,6 +15158,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -14258,6 +15228,11 @@
       <c r="M195" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.3702 | 再生能源與永續發展: 0.1467 | 大盤指數、期貨與總體經濟: 0.0948 | 傳統製造與原物料: 0.0946 | 航運與物流: 0.0585 | 其他產業或綜合新聞: 0.0539 | 生技與醫療: 0.0431 | 民生消費與零售: 0.0426 | 通訊網路與軟體服務: 0.0355 | 金融與保險業: 0.0354 | 營建與房地產: 0.0247</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -14329,6 +15304,11 @@
           <t>傳統製造與原物料: 0.6275 | 電子科技與半導體: 0.1015 | 再生能源與永續發展: 0.0496 | 民生消費與零售: 0.047 | 其他產業或綜合新聞: 0.0336 | 生技與醫療: 0.0313 | 金融與保險業: 0.0258 | 航運與物流: 0.0228 | 通訊網路與軟體服務: 0.0226 | 營建與房地產: 0.0199 | 大盤指數、期貨與總體經濟: 0.0183</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -14392,6 +15372,11 @@
       <c r="M197" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.9662 | 傳統製造與原物料: 0.0071 | 大盤指數、期貨與總體經濟: 0.0049 | 再生能源與永續發展: 0.0045 | 民生消費與零售: 0.0039 | 其他產業或綜合新聞: 0.0035 | 航運與物流: 0.0031 | 生技與醫療: 0.0019 | 營建與房地產: 0.0017 | 通訊網路與軟體服務: 0.0016 | 金融與保險業: 0.0016</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -14461,6 +15446,11 @@
       <c r="M198" t="inlineStr">
         <is>
           <t>生技與醫療: 0.6413 | 再生能源與永續發展: 0.1145 | 其他產業或綜合新聞: 0.0456 | 民生消費與零售: 0.0345 | 傳統製造與原物料: 0.0339 | 大盤指數、期貨與總體經濟: 0.0304 | 航運與物流: 0.0247 | 通訊網路與軟體服務: 0.0198 | 金融與保險業: 0.0191 | 電子科技與半導體: 0.0185 | 營建與房地產: 0.0176</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -14534,6 +15524,11 @@
           <t>其他產業或綜合新聞: 0.1252 | 電子科技與半導體: 0.116 | 大盤指數、期貨與總體經濟: 0.114 | 民生消費與零售: 0.1127 | 再生能源與永續發展: 0.101 | 通訊網路與軟體服務: 0.0842 | 金融與保險業: 0.0804 | 營建與房地產: 0.0777 | 航運與物流: 0.0767 | 生技與醫療: 0.0704 | 傳統製造與原物料: 0.0416</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -14603,6 +15598,11 @@
           <t>電子科技與半導體: 0.5334 | 民生消費與零售: 0.08 | 航運與物流: 0.0723 | 再生能源與永續發展: 0.0659 | 大盤指數、期貨與總體經濟: 0.0511 | 金融與保險業: 0.0426 | 其他產業或綜合新聞: 0.0373 | 通訊網路與軟體服務: 0.0348 | 生技與醫療: 0.0294 | 傳統製造與原物料: 0.0278 | 營建與房地產: 0.0254</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -14664,6 +15664,11 @@
           <t>電子科技與半導體: 0.3308 | 通訊網路與軟體服務: 0.1236 | 航運與物流: 0.0889 | 再生能源與永續發展: 0.087 | 金融與保險業: 0.0703 | 大盤指數、期貨與總體經濟: 0.0662 | 傳統製造與原物料: 0.0534 | 其他產業或綜合新聞: 0.0528 | 營建與房地產: 0.0513 | 生技與醫療: 0.0381 | 民生消費與零售: 0.0377</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -14723,6 +15728,11 @@
       <c r="M202" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.2094 | 大盤指數、期貨與總體經濟: 0.155 | 民生消費與零售: 0.1471 | 航運與物流: 0.126 | 金融與保險業: 0.1007 | 其他產業或綜合新聞: 0.0571 | 傳統製造與原物料: 0.0496 | 通訊網路與軟體服務: 0.0425 | 營建與房地產: 0.0411 | 生技與醫療: 0.0398 | 電子科技與半導體: 0.0316</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -14794,6 +15804,11 @@
       <c r="M203" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.1747 | 再生能源與永續發展: 0.1533 | 民生消費與零售: 0.1072 | 電子科技與半導體: 0.0974 | 航運與物流: 0.0957 | 其他產業或綜合新聞: 0.0765 | 生技與醫療: 0.0763 | 金融與保險業: 0.076 | 營建與房地產: 0.0629 | 傳統製造與原物料: 0.0493 | 通訊網路與軟體服務: 0.0305</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -14899,6 +15914,11 @@
           <t>電子科技與半導體: 0.7733 | 金融與保險業: 0.0595 | 大盤指數、期貨與總體經濟: 0.0442 | 通訊網路與軟體服務: 0.0212 | 民生消費與零售: 0.0189 | 傳統製造與原物料: 0.0187 | 航運與物流: 0.0166 | 生技與醫療: 0.014 | 再生能源與永續發展: 0.014 | 其他產業或綜合新聞: 0.0103 | 營建與房地產: 0.0093</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -14970,6 +15990,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -15033,6 +16058,11 @@
       <c r="M206" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.392 | 電子科技與半導體: 0.3274 | 其他產業或綜合新聞: 0.0488 | 傳統製造與原物料: 0.0414 | 大盤指數、期貨與總體經濟: 0.0401 | 民生消費與零售: 0.0307 | 航運與物流: 0.0276 | 生技與醫療: 0.0249 | 營建與房地產: 0.0232 | 通訊網路與軟體服務: 0.0221 | 金融與保險業: 0.0217</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -15100,6 +16130,11 @@
           <t>通訊網路與軟體服務: 0.2265 | 電子科技與半導體: 0.1904 | 金融與保險業: 0.174 | 其他產業或綜合新聞: 0.0728 | 傳統製造與原物料: 0.0677 | 大盤指數、期貨與總體經濟: 0.0604 | 再生能源與永續發展: 0.0515 | 民生消費與零售: 0.0457 | 營建與房地產: 0.0436 | 生技與醫療: 0.0342 | 航運與物流: 0.0333</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -15167,6 +16202,11 @@
           <t>傳統製造與原物料: 0.3467 | 電子科技與半導體: 0.2203 | 大盤指數、期貨與總體經濟: 0.1964 | 再生能源與永續發展: 0.0631 | 民生消費與零售: 0.0459 | 其他產業或綜合新聞: 0.033 | 航運與物流: 0.0282 | 通訊網路與軟體服務: 0.0234 | 金融與保險業: 0.0162 | 生技與醫療: 0.0149 | 營建與房地產: 0.012</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -15234,6 +16274,11 @@
       <c r="M209" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.9537 | 再生能源與永續發展: 0.022 | 其他產業或綜合新聞: 0.0084 | 傳統製造與原物料: 0.0032 | 大盤指數、期貨與總體經濟: 0.0024 | 生技與醫療: 0.0023 | 民生消費與零售: 0.0018 | 航運與物流: 0.0018 | 通訊網路與軟體服務: 0.0017 | 營建與房地產: 0.0015 | 金融與保險業: 0.0011</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -15309,6 +16354,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -15378,6 +16428,11 @@
       <c r="M211" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.1745 | 民生消費與零售: 0.1402 | 其他產業或綜合新聞: 0.1349 | 金融與保險業: 0.1069 | 航運與物流: 0.0874 | 生技與醫療: 0.0722 | 大盤指數、期貨與總體經濟: 0.0713 | 再生能源與永續發展: 0.0709 | 通訊網路與軟體服務: 0.0556 | 營建與房地產: 0.052 | 傳統製造與原物料: 0.0341</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -15453,6 +16508,11 @@
           <t>金融與保險業: 0.3186 | 大盤指數、期貨與總體經濟: 0.2517 | 民生消費與零售: 0.0823 | 航運與物流: 0.0625 | 其他產業或綜合新聞: 0.0542 | 再生能源與永續發展: 0.0475 | 電子科技與半導體: 0.0444 | 通訊網路與軟體服務: 0.0407 | 傳統製造與原物料: 0.0392 | 生技與醫療: 0.0313 | 營建與房地產: 0.0276</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -15524,6 +16584,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -15589,6 +16654,11 @@
       <c r="M214" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -15664,6 +16734,11 @@
           <t>再生能源與永續發展: 0.13 | 電子科技與半導體: 0.1113 | 傳統製造與原物料: 0.0988 | 民生消費與零售: 0.0969 | 金融與保險業: 0.0895 | 航運與物流: 0.0819 | 營建與房地產: 0.0818 | 其他產業或綜合新聞: 0.0799 | 生技與醫療: 0.078 | 大盤指數、期貨與總體經濟: 0.0762 | 通訊網路與軟體服務: 0.0756</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -15735,6 +16810,11 @@
           <t>其他產業或綜合新聞: 0.2487 | 大盤指數、期貨與總體經濟: 0.2152 | 再生能源與永續發展: 0.1993 | 通訊網路與軟體服務: 0.0891 | 民生消費與零售: 0.0724 | 電子科技與半導體: 0.0555 | 航運與物流: 0.0495 | 金融與保險業: 0.0366 | 營建與房地產: 0.0146 | 傳統製造與原物料: 0.0098 | 生技與醫療: 0.0092</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -15806,6 +16886,11 @@
       <c r="M217" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -15885,6 +16970,11 @@
           <t>通訊網路與軟體服務: 0.3031 | 電子科技與半導體: 0.2597 | 再生能源與永續發展: 0.1642 | 大盤指數、期貨與總體經濟: 0.0887 | 其他產業或綜合新聞: 0.0384 | 金融與保險業: 0.0311 | 民生消費與零售: 0.0304 | 航運與物流: 0.0303 | 生技與醫療: 0.0224 | 傳統製造與原物料: 0.0161 | 營建與房地產: 0.0155</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -15958,6 +17048,11 @@
           <t>電子科技與半導體: 0.354 | 大盤指數、期貨與總體經濟: 0.1668 | 通訊網路與軟體服務: 0.1069 | 民生消費與零售: 0.0711 | 再生能源與永續發展: 0.068 | 其他產業或綜合新聞: 0.0607 | 金融與保險業: 0.0419 | 傳統製造與原物料: 0.0392 | 航運與物流: 0.0356 | 生技與醫療: 0.0298 | 營建與房地產: 0.026</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -16023,6 +17118,11 @@
       <c r="M220" t="inlineStr">
         <is>
           <t>其他產業或綜合新聞: 0.2557 | 通訊網路與軟體服務: 0.1578 | 再生能源與永續發展: 0.1422 | 電子科技與半導體: 0.0943 | 傳統製造與原物料: 0.0736 | 金融與保險業: 0.0573 | 生技與醫療: 0.0509 | 航運與物流: 0.0473 | 大盤指數、期貨與總體經濟: 0.0436 | 民生消費與零售: 0.0391 | 營建與房地產: 0.0381</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -16098,6 +17198,11 @@
           <t>生技與醫療: 0.4276 | 電子科技與半導體: 0.1562 | 其他產業或綜合新聞: 0.0806 | 營建與房地產: 0.0647 | 金融與保險業: 0.054 | 航運與物流: 0.0428 | 再生能源與永續發展: 0.0393 | 大盤指數、期貨與總體經濟: 0.0378 | 民生消費與零售: 0.0356 | 通訊網路與軟體服務: 0.0331 | 傳統製造與原物料: 0.0283</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -16167,6 +17272,11 @@
       <c r="M222" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2587 | 通訊網路與軟體服務: 0.1659 | 其他產業或綜合新聞: 0.1302 | 再生能源與永續發展: 0.1072 | 民生消費與零售: 0.0779 | 大盤指數、期貨與總體經濟: 0.0645 | 生技與醫療: 0.0544 | 航運與物流: 0.0388 | 營建與房地產: 0.0378 | 金融與保險業: 0.0343 | 傳統製造與原物料: 0.0303</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -16244,6 +17354,11 @@
           <t>再生能源與永續發展: 0.29 | 其他產業或綜合新聞: 0.1065 | 營建與房地產: 0.0951 | 民生消費與零售: 0.0886 | 大盤指數、期貨與總體經濟: 0.0867 | 生技與醫療: 0.0796 | 金融與保險業: 0.0681 | 傳統製造與原物料: 0.0662 | 航運與物流: 0.0474 | 通訊網路與軟體服務: 0.0387 | 電子科技與半導體: 0.0331</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -16315,6 +17430,11 @@
           <t>民生消費與零售: 0.2648 | 大盤指數、期貨與總體經濟: 0.1917 | 再生能源與永續發展: 0.1196 | 其他產業或綜合新聞: 0.0858 | 電子科技與半導體: 0.0817 | 傳統製造與原物料: 0.069 | 航運與物流: 0.0469 | 通訊網路與軟體服務: 0.0452 | 營建與房地產: 0.033 | 金融與保險業: 0.0316 | 生技與醫療: 0.0305</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -16386,6 +17506,11 @@
           <t>電子科技與半導體: 0.5057 | 其他產業或綜合新聞: 0.1365 | 通訊網路與軟體服務: 0.1267 | 再生能源與永續發展: 0.0612 | 傳統製造與原物料: 0.0326 | 生技與醫療: 0.03 | 大盤指數、期貨與總體經濟: 0.0268 | 航運與物流: 0.0241 | 營建與房地產: 0.0221 | 民生消費與零售: 0.0196 | 金融與保險業: 0.0146</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -16451,6 +17576,11 @@
       <c r="M226" t="inlineStr">
         <is>
           <t>航運與物流: 0.3258 | 營建與房地產: 0.2055 | 再生能源與永續發展: 0.0757 | 其他產業或綜合新聞: 0.0672 | 大盤指數、期貨與總體經濟: 0.0634 | 電子科技與半導體: 0.05 | 生技與醫療: 0.0463 | 民生消費與零售: 0.0448 | 金融與保險業: 0.042 | 傳統製造與原物料: 0.0398 | 通訊網路與軟體服務: 0.0395</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -16520,6 +17650,11 @@
       <c r="M227" t="inlineStr">
         <is>
           <t>金融與保險業: 0.3709 | 大盤指數、期貨與總體經濟: 0.2576 | 傳統製造與原物料: 0.0986 | 其他產業或綜合新聞: 0.0911 | 再生能源與永續發展: 0.0777 | 民生消費與零售: 0.0471 | 通訊網路與軟體服務: 0.0158 | 營建與房地產: 0.0117 | 航運與物流: 0.0108 | 生技與醫療: 0.0107 | 電子科技與半導體: 0.0081</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -16591,6 +17726,11 @@
           <t>通訊網路與軟體服務: 0.198 | 電子科技與半導體: 0.1915 | 其他產業或綜合新聞: 0.1594 | 再生能源與永續發展: 0.1182 | 金融與保險業: 0.0575 | 營建與房地產: 0.0561 | 生技與醫療: 0.0505 | 民生消費與零售: 0.0467 | 航運與物流: 0.0463 | 大盤指數、期貨與總體經濟: 0.0415 | 傳統製造與原物料: 0.0343</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -16656,6 +17796,11 @@
       <c r="M229" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2482 | 大盤指數、期貨與總體經濟: 0.1192 | 再生能源與永續發展: 0.0956 | 其他產業或綜合新聞: 0.0923 | 傳統製造與原物料: 0.0771 | 航運與物流: 0.0683 | 民生消費與零售: 0.067 | 金融與保險業: 0.0627 | 通訊網路與軟體服務: 0.0604 | 生技與醫療: 0.0579 | 營建與房地產: 0.0515</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -16727,6 +17872,11 @@
           <t>電子科技與半導體: 0.6664 | 通訊網路與軟體服務: 0.0919 | 再生能源與永續發展: 0.0482 | 其他產業或綜合新聞: 0.0471 | 民生消費與零售: 0.0378 | 大盤指數、期貨與總體經濟: 0.0354 | 航運與物流: 0.0244 | 傳統製造與原物料: 0.0189 | 營建與房地產: 0.0136 | 金融與保險業: 0.009 | 生技與醫療: 0.0073</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -16796,6 +17946,11 @@
           <t>通訊網路與軟體服務: 0.6165 | 電子科技與半導體: 0.0759 | 生技與醫療: 0.0706 | 再生能源與永續發展: 0.0469 | 大盤指數、期貨與總體經濟: 0.0448 | 金融與保險業: 0.0444 | 其他產業或綜合新聞: 0.0383 | 傳統製造與原物料: 0.0211 | 營建與房地產: 0.0158 | 航運與物流: 0.0131 | 民生消費與零售: 0.0127</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -16863,6 +18018,11 @@
           <t>金融與保險業: 0.1423 | 大盤指數、期貨與總體經濟: 0.1191 | 其他產業或綜合新聞: 0.1097 | 民生消費與零售: 0.1041 | 再生能源與永續發展: 0.0911 | 營建與房地產: 0.0787 | 生技與醫療: 0.0787 | 傳統製造與原物料: 0.0773 | 通訊網路與軟體服務: 0.0727 | 航運與物流: 0.0685 | 電子科技與半導體: 0.0577</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -16924,6 +18084,11 @@
       <c r="M233" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2793 | 通訊網路與軟體服務: 0.1405 | 再生能源與永續發展: 0.0947 | 民生消費與零售: 0.0934 | 大盤指數、期貨與總體經濟: 0.0902 | 其他產業或綜合新聞: 0.0803 | 航運與物流: 0.0583 | 金融與保險業: 0.0579 | 生技與醫療: 0.0469 | 傳統製造與原物料: 0.0352 | 營建與房地產: 0.0234</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -16993,6 +18158,11 @@
           <t>大盤指數、期貨與總體經濟: 0.2173 | 金融與保險業: 0.2037 | 民生消費與零售: 0.0957 | 通訊網路與軟體服務: 0.0785 | 營建與房地產: 0.0775 | 航運與物流: 0.0718 | 其他產業或綜合新聞: 0.0677 | 電子科技與半導體: 0.0612 | 傳統製造與原物料: 0.0465 | 再生能源與永續發展: 0.0458 | 生技與醫療: 0.0343</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -17052,6 +18222,11 @@
       <c r="M235" t="inlineStr">
         <is>
           <t>生技與醫療: 0.795 | 航運與物流: 0.0297 | 民生消費與零售: 0.0256 | 再生能源與永續發展: 0.0223 | 大盤指數、期貨與總體經濟: 0.0205 | 電子科技與半導體: 0.0204 | 營建與房地產: 0.0194 | 其他產業或綜合新聞: 0.0189 | 通訊網路與軟體服務: 0.0179 | 傳統製造與原物料: 0.0163 | 金融與保險業: 0.0142</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -17123,6 +18298,11 @@
           <t>電子科技與半導體: 0.6007 | 傳統製造與原物料: 0.0781 | 其他產業或綜合新聞: 0.0666 | 再生能源與永續發展: 0.0573 | 大盤指數、期貨與總體經濟: 0.0496 | 通訊網路與軟體服務: 0.0378 | 民生消費與零售: 0.026 | 營建與房地產: 0.0252 | 金融與保險業: 0.0239 | 航運與物流: 0.0217 | 生技與醫療: 0.0133</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -17182,6 +18362,11 @@
       <c r="M237" t="inlineStr">
         <is>
           <t>金融與保險業: 0.2656 | 大盤指數、期貨與總體經濟: 0.1389 | 民生消費與零售: 0.1118 | 營建與房地產: 0.0861 | 再生能源與永續發展: 0.079 | 傳統製造與原物料: 0.0651 | 電子科技與半導體: 0.0646 | 其他產業或綜合新聞: 0.0615 | 通訊網路與軟體服務: 0.058 | 生技與醫療: 0.035 | 航運與物流: 0.0344</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -17255,6 +18440,11 @@
           <t>通訊網路與軟體服務: 0.1324 | 再生能源與永續發展: 0.111 | 電子科技與半導體: 0.1045 | 民生消費與零售: 0.1005 | 航運與物流: 0.095 | 其他產業或綜合新聞: 0.0919 | 金融與保險業: 0.085 | 生技與醫療: 0.079 | 大盤指數、期貨與總體經濟: 0.0743 | 營建與房地產: 0.072 | 傳統製造與原物料: 0.0544</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -17324,6 +18514,11 @@
           <t>通訊網路與軟體服務: 0.3309 | 航運與物流: 0.1961 | 其他產業或綜合新聞: 0.0874 | 再生能源與永續發展: 0.0812 | 大盤指數、期貨與總體經濟: 0.0721 | 民生消費與零售: 0.0688 | 電子科技與半導體: 0.0656 | 金融與保險業: 0.0356 | 生技與醫療: 0.0287 | 營建與房地產: 0.0175 | 傳統製造與原物料: 0.0163</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -17387,6 +18582,11 @@
           <t>電子科技與半導體: 0.5588 | 通訊網路與軟體服務: 0.4096 | 大盤指數、期貨與總體經濟: 0.0114 | 其他產業或綜合新聞: 0.0076 | 再生能源與永續發展: 0.0047 | 民生消費與零售: 0.0027 | 傳統製造與原物料: 0.0015 | 航運與物流: 0.0011 | 營建與房地產: 0.001 | 生技與醫療: 0.0009 | 金融與保險業: 0.0006</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -17450,6 +18650,11 @@
       <c r="M241" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.3017 | 其他產業或綜合新聞: 0.1241 | 通訊網路與軟體服務: 0.0911 | 再生能源與永續發展: 0.0741 | 金融與保險業: 0.0688 | 大盤指數、期貨與總體經濟: 0.0656 | 民生消費與零售: 0.0619 | 傳統製造與原物料: 0.0566 | 營建與房地產: 0.0555 | 航運與物流: 0.0519 | 生技與醫療: 0.0488</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -17523,6 +18728,11 @@
           <t>電子科技與半導體: 0.2736 | 民生消費與零售: 0.108 | 通訊網路與軟體服務: 0.108 | 其他產業或綜合新聞: 0.1049 | 再生能源與永續發展: 0.0995 | 大盤指數、期貨與總體經濟: 0.0949 | 金融與保險業: 0.0586 | 航運與物流: 0.0502 | 生技與醫療: 0.0369 | 傳統製造與原物料: 0.0337 | 營建與房地產: 0.0318</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -17590,6 +18800,11 @@
       <c r="M243" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.2201 | 其他產業或綜合新聞: 0.1714 | 航運與物流: 0.139 | 傳統製造與原物料: 0.1389 | 民生消費與零售: 0.0706 | 再生能源與永續發展: 0.0643 | 電子科技與半導體: 0.0626 | 通訊網路與軟體服務: 0.0612 | 營建與房地產: 0.025 | 生技與醫療: 0.0237 | 金融與保險業: 0.0232</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -17665,6 +18880,11 @@
           <t>其他產業或綜合新聞: 0.1748 | 傳統製造與原物料: 0.1082 | 民生消費與零售: 0.0999 | 大盤指數、期貨與總體經濟: 0.0976 | 再生能源與永續發展: 0.088 | 電子科技與半導體: 0.0833 | 金融與保險業: 0.0806 | 營建與房地產: 0.077 | 生技與醫療: 0.0692 | 航運與物流: 0.066 | 通訊網路與軟體服務: 0.0555</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -17734,6 +18954,11 @@
       <c r="M245" t="inlineStr">
         <is>
           <t>其他產業或綜合新聞: 0.1628 | 民生消費與零售: 0.141 | 再生能源與永續發展: 0.0898 | 金融與保險業: 0.0897 | 大盤指數、期貨與總體經濟: 0.089 | 傳統製造與原物料: 0.0874 | 航運與物流: 0.0764 | 電子科技與半導體: 0.072 | 生技與醫療: 0.0704 | 營建與房地產: 0.0675 | 通訊網路與軟體服務: 0.0541</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -17919,6 +19144,11 @@
           <t>大盤指數、期貨與總體經濟: 0.1551 | 電子科技與半導體: 0.1143 | 航運與物流: 0.1033 | 民生消費與零售: 0.0999 | 金融與保險業: 0.0982 | 通訊網路與軟體服務: 0.0837 | 生技與醫療: 0.0784 | 再生能源與永續發展: 0.0765 | 其他產業或綜合新聞: 0.0744 | 傳統製造與原物料: 0.073 | 營建與房地產: 0.0432</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -17988,6 +19218,11 @@
           <t>通訊網路與軟體服務: 0.2392 | 電子科技與半導體: 0.1634 | 大盤指數、期貨與總體經濟: 0.1236 | 其他產業或綜合新聞: 0.115 | 再生能源與永續發展: 0.1123 | 民生消費與零售: 0.0593 | 金融與保險業: 0.0442 | 傳統製造與原物料: 0.0382 | 生技與醫療: 0.0368 | 航運與物流: 0.0363 | 營建與房地產: 0.0317</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -18053,6 +19288,11 @@
       <c r="M248" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.3619 | 再生能源與永續發展: 0.1299 | 通訊網路與軟體服務: 0.0998 | 電子科技與半導體: 0.0958 | 其他產業或綜合新聞: 0.0674 | 金融與保險業: 0.0659 | 大盤指數、期貨與總體經濟: 0.0445 | 營建與房地產: 0.0357 | 生技與醫療: 0.034 | 航運與物流: 0.0334 | 傳統製造與原物料: 0.0317</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -18132,6 +19372,11 @@
           <t>電子科技與半導體: 0.4124 | 再生能源與永續發展: 0.1551 | 其他產業或綜合新聞: 0.1323 | 通訊網路與軟體服務: 0.1058 | 大盤指數、期貨與總體經濟: 0.0556 | 民生消費與零售: 0.0453 | 生技與醫療: 0.0273 | 航運與物流: 0.0228 | 金融與保險業: 0.0168 | 傳統製造與原物料: 0.0149 | 營建與房地產: 0.0117</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -18207,6 +19452,11 @@
           <t>再生能源與永續發展: 0.1454 | 電子科技與半導體: 0.1393 | 通訊網路與軟體服務: 0.1285 | 航運與物流: 0.0965 | 民生消費與零售: 0.0952 | 生技與醫療: 0.0744 | 金融與保險業: 0.071 | 傳統製造與原物料: 0.0681 | 營建與房地產: 0.0628 | 大盤指數、期貨與總體經濟: 0.0617 | 其他產業或綜合新聞: 0.0573</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -18272,6 +19522,11 @@
           <t>民生消費與零售: 0.2537 | 金融與保險業: 0.1864 | 其他產業或綜合新聞: 0.0935 | 再生能源與永續發展: 0.0891 | 電子科技與半導體: 0.07 | 營建與房地產: 0.0648 | 大盤指數、期貨與總體經濟: 0.0624 | 傳統製造與原物料: 0.0525 | 航運與物流: 0.049 | 生技與醫療: 0.0445 | 通訊網路與軟體服務: 0.0341</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -18331,6 +19586,11 @@
       <c r="M252" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.2265 | 金融與保險業: 0.2066 | 再生能源與永續發展: 0.0987 | 營建與房地產: 0.0848 | 電子科技與半導體: 0.0812 | 其他產業或綜合新聞: 0.066 | 大盤指數、期貨與總體經濟: 0.0634 | 航運與物流: 0.0511 | 生技與醫療: 0.0455 | 傳統製造與原物料: 0.0409 | 通訊網路與軟體服務: 0.0352</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -18402,6 +19662,11 @@
           <t>其他產業或綜合新聞: 0.2139 | 金融與保險業: 0.1467 | 電子科技與半導體: 0.1376 | 通訊網路與軟體服務: 0.0975 | 再生能源與永續發展: 0.0763 | 大盤指數、期貨與總體經濟: 0.0715 | 傳統製造與原物料: 0.059 | 航運與物流: 0.0577 | 營建與房地產: 0.0515 | 生技與醫療: 0.0442 | 民生消費與零售: 0.0441</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -18461,6 +19726,11 @@
       <c r="M254" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.583 | 電子科技與半導體: 0.4058 | 大盤指數、期貨與總體經濟: 0.0025 | 再生能源與永續發展: 0.0017 | 傳統製造與原物料: 0.0015 | 其他產業或綜合新聞: 0.0014 | 營建與房地產: 0.0011 | 航運與物流: 0.001 | 民生消費與零售: 0.0007 | 金融與保險業: 0.0007 | 生技與醫療: 0.0005</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -18538,6 +19808,11 @@
           <t>其他產業或綜合新聞: 0.1354 | 大盤指數、期貨與總體經濟: 0.1142 | 民生消費與零售: 0.1057 | 再生能源與永續發展: 0.1045 | 電子科技與半導體: 0.1045 | 傳統製造與原物料: 0.0898 | 航運與物流: 0.0837 | 通訊網路與軟體服務: 0.0729 | 金融與保險業: 0.0693 | 營建與房地產: 0.0607 | 生技與醫療: 0.0593</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -18607,6 +19882,11 @@
           <t>電子科技與半導體: 0.3491 | 其他產業或綜合新聞: 0.2083 | 通訊網路與軟體服務: 0.1512 | 再生能源與永續發展: 0.0794 | 生技與醫療: 0.0765 | 民生消費與零售: 0.0323 | 大盤指數、期貨與總體經濟: 0.0268 | 傳統製造與原物料: 0.0256 | 航運與物流: 0.0204 | 營建與房地產: 0.0168 | 金融與保險業: 0.0137</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -18672,6 +19952,11 @@
           <t>金融與保險業: 0.2666 | 民生消費與零售: 0.1174 | 傳統製造與原物料: 0.0857 | 生技與醫療: 0.0851 | 營建與房地產: 0.0823 | 其他產業或綜合新聞: 0.0813 | 航運與物流: 0.072 | 再生能源與永續發展: 0.0632 | 大盤指數、期貨與總體經濟: 0.0607 | 通訊網路與軟體服務: 0.0498 | 電子科技與半導體: 0.0359</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -18735,6 +20020,11 @@
       <c r="M258" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.501 | 民生消費與零售: 0.1399 | 大盤指數、期貨與總體經濟: 0.0853 | 傳統製造與原物料: 0.0556 | 其他產業或綜合新聞: 0.0391 | 航運與物流: 0.0377 | 金融與保險業: 0.0358 | 生技與醫療: 0.0272 | 再生能源與永續發展: 0.0263 | 通訊網路與軟體服務: 0.0261 | 營建與房地產: 0.0259</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -18806,6 +20096,11 @@
       <c r="M259" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.3618 | 其他產業或綜合新聞: 0.1464 | 大盤指數、期貨與總體經濟: 0.121 | 通訊網路與軟體服務: 0.1127 | 再生能源與永續發展: 0.0699 | 民生消費與零售: 0.0621 | 傳統製造與原物料: 0.0374 | 航運與物流: 0.0319 | 金融與保險業: 0.0298 | 生技與醫療: 0.0143 | 營建與房地產: 0.0126</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -18883,6 +20178,11 @@
       <c r="M260" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.3818 | 大盤指數、期貨與總體經濟: 0.1257 | 營建與房地產: 0.1107 | 再生能源與永續發展: 0.0773 | 航運與物流: 0.0681 | 其他產業或綜合新聞: 0.0461 | 傳統製造與原物料: 0.044 | 生技與醫療: 0.0414 | 金融與保險業: 0.0375 | 通訊網路與軟體服務: 0.0361 | 電子科技與半導體: 0.0315</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -18982,6 +20282,11 @@
           <t>大盤指數、期貨與總體經濟: 0.4167 | 金融與保險業: 0.0899 | 通訊網路與軟體服務: 0.0802 | 其他產業或綜合新聞: 0.0643 | 航運與物流: 0.0596 | 電子科技與半導體: 0.0571 | 營建與房地產: 0.0509 | 再生能源與永續發展: 0.049 | 傳統製造與原物料: 0.0486 | 民生消費與零售: 0.0435 | 生技與醫療: 0.0402</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -19051,6 +20356,11 @@
           <t>其他產業或綜合新聞: 0.7307 | 電子科技與半導體: 0.189 | 通訊網路與軟體服務: 0.0186 | 航運與物流: 0.012 | 民生消費與零售: 0.0105 | 傳統製造與原物料: 0.0093 | 再生能源與永續發展: 0.0089 | 大盤指數、期貨與總體經濟: 0.0077 | 營建與房地產: 0.005 | 生技與醫療: 0.0048 | 金融與保險業: 0.0034</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -19114,6 +20424,11 @@
       <c r="M263" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.1764 | 大盤指數、期貨與總體經濟: 0.1283 | 再生能源與永續發展: 0.1001 | 電子科技與半導體: 0.094 | 金融與保險業: 0.0856 | 營建與房地產: 0.0841 | 航運與物流: 0.0817 | 傳統製造與原物料: 0.066 | 生技與醫療: 0.0625 | 其他產業或綜合新聞: 0.0609 | 通訊網路與軟體服務: 0.0604</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -19181,6 +20496,11 @@
       <c r="M264" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.2585 | 其他產業或綜合新聞: 0.1583 | 民生消費與零售: 0.0977 | 營建與房地產: 0.0876 | 大盤指數、期貨與總體經濟: 0.0854 | 傳統製造與原物料: 0.0572 | 生技與醫療: 0.0572 | 電子科技與半導體: 0.0542 | 航運與物流: 0.0525 | 通訊網路與軟體服務: 0.0521 | 金融與保險業: 0.039</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -19252,6 +20572,11 @@
           <t>金融與保險業: 0.1403 | 大盤指數、期貨與總體經濟: 0.1226 | 再生能源與永續發展: 0.1028 | 其他產業或綜合新聞: 0.1014 | 民生消費與零售: 0.0983 | 營建與房地產: 0.0873 | 生技與醫療: 0.0844 | 傳統製造與原物料: 0.0793 | 電子科技與半導體: 0.0782 | 通訊網路與軟體服務: 0.0565 | 航運與物流: 0.0488</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -19317,6 +20642,11 @@
       <c r="M266" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.1828 | 金融與保險業: 0.1045 | 民生消費與零售: 0.1013 | 傳統製造與原物料: 0.0875 | 營建與房地產: 0.0865 | 生技與醫療: 0.0827 | 航運與物流: 0.0754 | 電子科技與半導體: 0.0724 | 通訊網路與軟體服務: 0.072 | 其他產業或綜合新聞: 0.0694 | 再生能源與永續發展: 0.0654</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>股利與除權息</t>
         </is>
       </c>
     </row>
@@ -19386,6 +20716,11 @@
       <c r="M267" t="inlineStr">
         <is>
           <t>航運與物流: 0.6395 | 大盤指數、期貨與總體經濟: 0.1349 | 傳統製造與原物料: 0.0684 | 電子科技與半導體: 0.0399 | 再生能源與永續發展: 0.0328 | 民生消費與零售: 0.0197 | 其他產業或綜合新聞: 0.0179 | 金融與保險業: 0.0128 | 通訊網路與軟體服務: 0.0127 | 生技與醫療: 0.0122 | 營建與房地產: 0.0091</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -19463,6 +20798,11 @@
           <t>大盤指數、期貨與總體經濟: 0.2904 | 民生消費與零售: 0.181 | 再生能源與永續發展: 0.1311 | 電子科技與半導體: 0.127 | 通訊網路與軟體服務: 0.076 | 航運與物流: 0.0589 | 金融與保險業: 0.0462 | 其他產業或綜合新聞: 0.0332 | 傳統製造與原物料: 0.0232 | 生技與醫療: 0.02 | 營建與房地產: 0.013</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -19534,6 +20874,11 @@
           <t>電子科技與半導體: 0.1481 | 傳統製造與原物料: 0.1349 | 其他產業或綜合新聞: 0.1058 | 大盤指數、期貨與總體經濟: 0.1024 | 民生消費與零售: 0.1 | 航運與物流: 0.0862 | 再生能源與永續發展: 0.0826 | 通訊網路與軟體服務: 0.0794 | 金融與保險業: 0.065 | 生技與醫療: 0.0535 | 營建與房地產: 0.042</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -19603,6 +20948,11 @@
       <c r="M270" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2935 | 民生消費與零售: 0.1346 | 其他產業或綜合新聞: 0.1277 | 航運與物流: 0.09 | 傳統製造與原物料: 0.0866 | 再生能源與永續發展: 0.0839 | 通訊網路與軟體服務: 0.067 | 生技與醫療: 0.0339 | 大盤指數、期貨與總體經濟: 0.0322 | 金融與保險業: 0.0299 | 營建與房地產: 0.0206</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -19678,6 +21028,11 @@
           <t>電子科技與半導體: 0.3058 | 大盤指數、期貨與總體經濟: 0.2574 | 傳統製造與原物料: 0.1053 | 民生消費與零售: 0.0727 | 其他產業或綜合新聞: 0.0716 | 金融與保險業: 0.0539 | 再生能源與永續發展: 0.0468 | 通訊網路與軟體服務: 0.0331 | 航運與物流: 0.0218 | 生技與醫療: 0.021 | 營建與房地產: 0.0105</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -19739,6 +21094,11 @@
       <c r="M272" t="inlineStr">
         <is>
           <t>金融與保險業: 0.147 | 民生消費與零售: 0.1245 | 大盤指數、期貨與總體經濟: 0.1067 | 營建與房地產: 0.0955 | 傳統製造與原物料: 0.0823 | 通訊網路與軟體服務: 0.0806 | 再生能源與永續發展: 0.0792 | 電子科技與半導體: 0.075 | 生技與醫療: 0.0722 | 航運與物流: 0.0721 | 其他產業或綜合新聞: 0.0649</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -19838,6 +21198,11 @@
           <t>大盤指數、期貨與總體經濟: 0.1312 | 金融與保險業: 0.1252 | 民生消費與零售: 0.1172 | 再生能源與永續發展: 0.1086 | 其他產業或綜合新聞: 0.0962 | 電子科技與半導體: 0.0911 | 生技與醫療: 0.0859 | 營建與房地產: 0.0758 | 航運與物流: 0.0589 | 傳統製造與原物料: 0.0558 | 通訊網路與軟體服務: 0.0541</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -19907,6 +21272,11 @@
       <c r="M274" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -19978,6 +21348,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -20047,6 +21422,11 @@
           <t>再生能源與永續發展: 0.5441 | 電子科技與半導體: 0.3106 | 通訊網路與軟體服務: 0.085 | 其他產業或綜合新聞: 0.0273 | 大盤指數、期貨與總體經濟: 0.0126 | 民生消費與零售: 0.0082 | 營建與房地產: 0.0039 | 傳統製造與原物料: 0.0023 | 航運與物流: 0.0022 | 金融與保險業: 0.0022 | 生技與醫療: 0.0014</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -20114,6 +21494,11 @@
       <c r="M277" t="inlineStr">
         <is>
           <t>其他產業或綜合新聞: 0.22 | 通訊網路與軟體服務: 0.1259 | 民生消費與零售: 0.1213 | 電子科技與半導體: 0.113 | 再生能源與永續發展: 0.0739 | 傳統製造與原物料: 0.0682 | 金融與保險業: 0.0596 | 大盤指數、期貨與總體經濟: 0.0556 | 航運與物流: 0.0548 | 營建與房地產: 0.0545 | 生技與醫療: 0.0533</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -20187,6 +21572,11 @@
           <t>民生消費與零售: 0.6697 | 通訊網路與軟體服務: 0.0798 | 航運與物流: 0.0644 | 其他產業或綜合新聞: 0.0615 | 大盤指數、期貨與總體經濟: 0.0571 | 再生能源與永續發展: 0.0324 | 電子科技與半導體: 0.0191 | 營建與房地產: 0.0064 | 傳統製造與原物料: 0.0035 | 金融與保險業: 0.0032 | 生技與醫療: 0.0029</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -20244,6 +21634,11 @@
       <c r="M279" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.3149 | 金融與保險業: 0.2927 | 營建與房地產: 0.1132 | 其他產業或綜合新聞: 0.0614 | 民生消費與零售: 0.045 | 電子科技與半導體: 0.0372 | 再生能源與永續發展: 0.0304 | 生技與醫療: 0.0294 | 通訊網路與軟體服務: 0.0276 | 航運與物流: 0.0244 | 傳統製造與原物料: 0.0238</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -20311,6 +21706,11 @@
       <c r="M280" t="inlineStr">
         <is>
           <t>航運與物流: 0.4865 | 傳統製造與原物料: 0.1014 | 大盤指數、期貨與總體經濟: 0.0907 | 再生能源與永續發展: 0.0833 | 民生消費與零售: 0.0804 | 其他產業或綜合新聞: 0.0371 | 生技與醫療: 0.0319 | 營建與房地產: 0.0287 | 金融與保險業: 0.0265 | 通訊網路與軟體服務: 0.0182 | 電子科技與半導體: 0.0153</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -20382,6 +21782,11 @@
       <c r="M281" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.5522 | 生技與醫療: 0.1163 | 電子科技與半導體: 0.1157 | 航運與物流: 0.0563 | 再生能源與永續發展: 0.0541 | 其他產業或綜合新聞: 0.027 | 民生消費與零售: 0.0242 | 大盤指數、期貨與總體經濟: 0.0176 | 金融與保險業: 0.0136 | 營建與房地產: 0.0123 | 傳統製造與原物料: 0.0107</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -20457,6 +21862,11 @@
           <t>航運與物流: 0.2756 | 電子科技與半導體: 0.0962 | 再生能源與永續發展: 0.0941 | 其他產業或綜合新聞: 0.0921 | 通訊網路與軟體服務: 0.0842 | 民生消費與零售: 0.0802 | 大盤指數、期貨與總體經濟: 0.0727 | 營建與房地產: 0.0605 | 金融與保險業: 0.0569 | 生技與醫療: 0.0541 | 傳統製造與原物料: 0.0332</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -20524,6 +21934,11 @@
           <t>電子科技與半導體: 0.4899 | 再生能源與永續發展: 0.1482 | 其他產業或綜合新聞: 0.063 | 傳統製造與原物料: 0.0497 | 大盤指數、期貨與總體經濟: 0.0452 | 通訊網路與軟體服務: 0.0443 | 民生消費與零售: 0.0405 | 航運與物流: 0.0363 | 金融與保險業: 0.0327 | 營建與房地產: 0.0304 | 生技與醫療: 0.0197</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -20585,6 +22000,11 @@
       <c r="M284" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2046 | 大盤指數、期貨與總體經濟: 0.1649 | 傳統製造與原物料: 0.1343 | 金融與保險業: 0.1338 | 通訊網路與軟體服務: 0.0893 | 民生消費與零售: 0.0696 | 再生能源與永續發展: 0.0602 | 其他產業或綜合新聞: 0.0532 | 航運與物流: 0.0374 | 營建與房地產: 0.0301 | 生技與醫療: 0.0225</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -20670,6 +22090,11 @@
           <t>電子科技與半導體: 0.9555 | 大盤指數、期貨與總體經濟: 0.0195 | 通訊網路與軟體服務: 0.0141 | 再生能源與永續發展: 0.0044 | 其他產業或綜合新聞: 0.0015 | 傳統製造與原物料: 0.0013 | 金融與保險業: 0.001 | 民生消費與零售: 0.0009 | 航運與物流: 0.0009 | 生技與醫療: 0.0005 | 營建與房地產: 0.0004</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -20747,6 +22172,11 @@
       <c r="M286" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
         </is>
       </c>
     </row>
@@ -20842,6 +22272,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -20905,6 +22340,11 @@
       <c r="M288" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.3525 | 電子科技與半導體: 0.2945 | 金融與保險業: 0.0739 | 生技與醫療: 0.0534 | 民生消費與零售: 0.0483 | 通訊網路與軟體服務: 0.0413 | 其他產業或綜合新聞: 0.0382 | 航運與物流: 0.0372 | 再生能源與永續發展: 0.0263 | 傳統製造與原物料: 0.0172 | 營建與房地產: 0.0171</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -20982,6 +22422,11 @@
           <t>大盤指數、期貨與總體經濟: 0.2305 | 金融與保險業: 0.1102 | 民生消費與零售: 0.0972 | 航運與物流: 0.0875 | 其他產業或綜合新聞: 0.0861 | 再生能源與永續發展: 0.0855 | 電子科技與半導體: 0.0703 | 營建與房地產: 0.0683 | 通訊網路與軟體服務: 0.0617 | 生技與醫療: 0.0613 | 傳統製造與原物料: 0.0413</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -21049,6 +22494,11 @@
       <c r="M290" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -21126,6 +22576,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -21195,6 +22650,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -21252,6 +22712,11 @@
       <c r="M293" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.1571 | 再生能源與永續發展: 0.1318 | 民生消費與零售: 0.0998 | 電子科技與半導體: 0.0991 | 金融與保險業: 0.0859 | 航運與物流: 0.0826 | 傳統製造與原物料: 0.0788 | 營建與房地產: 0.0772 | 通訊網路與軟體服務: 0.077 | 生技與醫療: 0.0608 | 其他產業或綜合新聞: 0.0499</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -21321,6 +22786,11 @@
       <c r="M294" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -21402,6 +22872,11 @@
           <t>通訊網路與軟體服務: 0.9535 | 電子科技與半導體: 0.038 | 大盤指數、期貨與總體經濟: 0.0017 | 金融與保險業: 0.0014 | 其他產業或綜合新聞: 0.0013 | 再生能源與永續發展: 0.0011 | 民生消費與零售: 0.0009 | 航運與物流: 0.0008 | 生技與醫療: 0.0005 | 營建與房地產: 0.0005 | 傳統製造與原物料: 0.0004</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -21477,6 +22952,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -21544,6 +23024,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -21611,6 +23096,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -21676,6 +23166,11 @@
       <c r="M299" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.149 | 民生消費與零售: 0.1156 | 大盤指數、期貨與總體經濟: 0.1132 | 傳統製造與原物料: 0.0906 | 其他產業或綜合新聞: 0.0861 | 營建與房地產: 0.0858 | 金融與保險業: 0.082 | 電子科技與半導體: 0.0782 | 通訊網路與軟體服務: 0.0757 | 航運與物流: 0.067 | 生技與醫療: 0.0568</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -21751,6 +23246,11 @@
           <t>電子科技與半導體: 0.4425 | 通訊網路與軟體服務: 0.1347 | 再生能源與永續發展: 0.1207 | 傳統製造與原物料: 0.0988 | 民生消費與零售: 0.082 | 大盤指數、期貨與總體經濟: 0.0414 | 其他產業或綜合新聞: 0.0385 | 航運與物流: 0.025 | 金融與保險業: 0.0118 | 生技與醫療: 0.0026 | 營建與房地產: 0.0021</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -21816,6 +23316,11 @@
           <t>航運與物流: 0.4309 | 其他產業或綜合新聞: 0.117 | 大盤指數、期貨與總體經濟: 0.0929 | 通訊網路與軟體服務: 0.0707 | 民生消費與零售: 0.0663 | 電子科技與半導體: 0.0578 | 再生能源與永續發展: 0.0459 | 生技與醫療: 0.0417 | 金融與保險業: 0.0268 | 營建與房地產: 0.0252 | 傳統製造與原物料: 0.025</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>人事異動</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -21879,6 +23384,11 @@
       <c r="M302" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.7945 | 航運與物流: 0.118 | 大盤指數、期貨與總體經濟: 0.0626 | 其他產業或綜合新聞: 0.0077 | 民生消費與零售: 0.004 | 電子科技與半導體: 0.0037 | 營建與房地產: 0.0025 | 通訊網路與軟體服務: 0.0019 | 金融與保險業: 0.0017 | 生技與醫療: 0.0017 | 傳統製造與原物料: 0.0017</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -21960,6 +23470,11 @@
           <t>大盤指數、期貨與總體經濟: 0.3333 | 電子科技與半導體: 0.1951 | 金融與保險業: 0.1088 | 民生消費與零售: 0.0955 | 再生能源與永續發展: 0.0852 | 其他產業或綜合新聞: 0.0759 | 通訊網路與軟體服務: 0.0387 | 傳統製造與原物料: 0.0288 | 生技與醫療: 0.0158 | 航運與物流: 0.0132 | 營建與房地產: 0.0096</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -22029,6 +23544,11 @@
           <t>電子科技與半導體: 0.7156 | 通訊網路與軟體服務: 0.0641 | 其他產業或綜合新聞: 0.0481 | 再生能源與永續發展: 0.037 | 航運與物流: 0.0281 | 民生消費與零售: 0.0208 | 營建與房地產: 0.0207 | 傳統製造與原物料: 0.0178 | 大盤指數、期貨與總體經濟: 0.0168 | 生技與醫療: 0.0167 | 金融與保險業: 0.0143</t>
         </is>
       </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -22090,6 +23610,11 @@
       <c r="M305" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -22159,6 +23684,11 @@
           <t>通訊網路與軟體服務: 0.6108 | 電子科技與半導體: 0.1582 | 大盤指數、期貨與總體經濟: 0.0587 | 再生能源與永續發展: 0.0471 | 其他產業或綜合新聞: 0.0469 | 航運與物流: 0.0177 | 金融與保險業: 0.0156 | 傳統製造與原物料: 0.015 | 民生消費與零售: 0.0147 | 生技與醫療: 0.0081 | 營建與房地產: 0.0073</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -22218,6 +23748,11 @@
       <c r="M307" t="inlineStr">
         <is>
           <t>金融與保險業: 0.3664 | 民生消費與零售: 0.0822 | 生技與醫療: 0.075 | 傳統製造與原物料: 0.0697 | 營建與房地產: 0.0695 | 大盤指數、期貨與總體經濟: 0.0665 | 航運與物流: 0.0649 | 再生能源與永續發展: 0.0646 | 通訊網路與軟體服務: 0.0592 | 電子科技與半導體: 0.0442 | 其他產業或綜合新聞: 0.0379</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -22285,6 +23820,11 @@
       <c r="M308" t="inlineStr">
         <is>
           <t>生技與醫療: 0.5431 | 大盤指數、期貨與總體經濟: 0.1338 | 金融與保險業: 0.0934 | 再生能源與永續發展: 0.0414 | 民生消費與零售: 0.0404 | 其他產業或綜合新聞: 0.0382 | 航運與物流: 0.0278 | 傳統製造與原物料: 0.023 | 營建與房地產: 0.022 | 通訊網路與軟體服務: 0.0198 | 電子科技與半導體: 0.0171</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -22358,6 +23898,11 @@
           <t>通訊網路與軟體服務: 0.7393 | 大盤指數、期貨與總體經濟: 0.0472 | 電子科技與半導體: 0.0335 | 再生能源與永續發展: 0.0324 | 民生消費與零售: 0.0283 | 其他產業或綜合新聞: 0.0256 | 航運與物流: 0.0233 | 金融與保險業: 0.0216 | 傳統製造與原物料: 0.0177 | 生技與醫療: 0.0164 | 營建與房地產: 0.0147</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -22431,6 +23976,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -22496,6 +24046,11 @@
       <c r="M311" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.327 | 電子科技與半導體: 0.3204 | 金融與保險業: 0.097 | 其他產業或綜合新聞: 0.0826 | 民生消費與零售: 0.0317 | 航運與物流: 0.0307 | 大盤指數、期貨與總體經濟: 0.0295 | 再生能源與永續發展: 0.0285 | 傳統製造與原物料: 0.0224 | 生技與醫療: 0.0164 | 營建與房地產: 0.0138</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -22571,6 +24126,11 @@
       <c r="M312" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.1835 | 通訊網路與軟體服務: 0.1254 | 再生能源與永續發展: 0.0977 | 其他產業或綜合新聞: 0.0971 | 民生消費與零售: 0.0954 | 金融與保險業: 0.0865 | 傳統製造與原物料: 0.0689 | 航運與物流: 0.0675 | 大盤指數、期貨與總體經濟: 0.0649 | 生技與醫療: 0.0641 | 營建與房地產: 0.049</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -22646,6 +24206,11 @@
       <c r="M313" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.2409 | 再生能源與永續發展: 0.1648 | 其他產業或綜合新聞: 0.1443 | 電子科技與半導體: 0.0798 | 通訊網路與軟體服務: 0.0743 | 航運與物流: 0.0695 | 民生消費與零售: 0.0561 | 營建與房地產: 0.0499 | 傳統製造與原物料: 0.0466 | 生技與醫療: 0.0396 | 金融與保險業: 0.0343</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -22753,6 +24318,11 @@
           <t>大盤指數、期貨與總體經濟: 0.8637 | 金融與保險業: 0.1122 | 通訊網路與軟體服務: 0.0065 | 電子科技與半導體: 0.0051 | 民生消費與零售: 0.0029 | 航運與物流: 0.0026 | 其他產業或綜合新聞: 0.002 | 傳統製造與原物料: 0.0018 | 生技與醫療: 0.0015 | 營建與房地產: 0.001 | 再生能源與永續發展: 0.0007</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -22826,6 +24396,11 @@
           <t>傳統製造與原物料: 0.1446 | 再生能源與永續發展: 0.1141 | 電子科技與半導體: 0.1089 | 航運與物流: 0.0948 | 大盤指數、期貨與總體經濟: 0.0833 | 生技與醫療: 0.0814 | 通訊網路與軟體服務: 0.0802 | 營建與房地產: 0.08 | 民生消費與零售: 0.0744 | 其他產業或綜合新聞: 0.0694 | 金融與保險業: 0.0688</t>
         </is>
       </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -22899,6 +24474,11 @@
           <t>電子科技與半導體: 0.2787 | 生技與醫療: 0.2338 | 通訊網路與軟體服務: 0.2266 | 大盤指數、期貨與總體經濟: 0.118 | 民生消費與零售: 0.0602 | 其他產業或綜合新聞: 0.0327 | 再生能源與永續發展: 0.031 | 航運與物流: 0.0106 | 傳統製造與原物料: 0.0045 | 營建與房地產: 0.0021 | 金融與保險業: 0.0018</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -22966,6 +24546,11 @@
           <t>電子科技與半導體: 0.8477 | 金融與保險業: 0.0246 | 傳統製造與原物料: 0.0197 | 民生消費與零售: 0.0176 | 再生能源與永續發展: 0.0148 | 航運與物流: 0.0145 | 其他產業或綜合新聞: 0.0144 | 通訊網路與軟體服務: 0.0124 | 營建與房地產: 0.0122 | 大盤指數、期貨與總體經濟: 0.0116 | 生技與醫療: 0.0105</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -23035,6 +24620,11 @@
           <t>生技與醫療: 0.4232 | 大盤指數、期貨與總體經濟: 0.1398 | 民生消費與零售: 0.0787 | 金融與保險業: 0.0688 | 航運與物流: 0.0678 | 再生能源與永續發展: 0.0619 | 其他產業或綜合新聞: 0.0472 | 傳統製造與原物料: 0.0466 | 營建與房地產: 0.0252 | 通訊網路與軟體服務: 0.0207 | 電子科技與半導體: 0.0199</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -23104,6 +24694,11 @@
           <t>電子科技與半導體: 0.2008 | 再生能源與永續發展: 0.1558 | 傳統製造與原物料: 0.1528 | 其他產業或綜合新聞: 0.1346 | 通訊網路與軟體服務: 0.1201 | 營建與房地產: 0.1074 | 生技與醫療: 0.0408 | 大盤指數、期貨與總體經濟: 0.0288 | 航運與物流: 0.0233 | 民生消費與零售: 0.0185 | 金融與保險業: 0.0172</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -23171,6 +24766,11 @@
           <t>傳統製造與原物料: 0.1868 | 再生能源與永續發展: 0.1111 | 航運與物流: 0.099 | 民生消費與零售: 0.0875 | 生技與醫療: 0.0865 | 營建與房地產: 0.0816 | 其他產業或綜合新聞: 0.0794 | 通訊網路與軟體服務: 0.0749 | 電子科技與半導體: 0.0698 | 金融與保險業: 0.063 | 大盤指數、期貨與總體經濟: 0.0604</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -23236,6 +24836,11 @@
       <c r="M321" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.7012 | 通訊網路與軟體服務: 0.0679 | 其他產業或綜合新聞: 0.0444 | 航運與物流: 0.038 | 再生能源與永續發展: 0.029 | 民生消費與零售: 0.0285 | 傳統製造與原物料: 0.0265 | 大盤指數、期貨與總體經濟: 0.0241 | 營建與房地產: 0.0158 | 生技與醫療: 0.0144 | 金融與保險業: 0.0102</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -23313,6 +24918,11 @@
           <t>再生能源與永續發展: 0.2665 | 大盤指數、期貨與總體經濟: 0.1601 | 電子科技與半導體: 0.1501 | 其他產業或綜合新聞: 0.11 | 傳統製造與原物料: 0.0914 | 生技與醫療: 0.0495 | 民生消費與零售: 0.0492 | 營建與房地產: 0.0371 | 航運與物流: 0.0318 | 金融與保險業: 0.0292 | 通訊網路與軟體服務: 0.025</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -23380,6 +24990,11 @@
       <c r="M323" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.9191 | 再生能源與永續發展: 0.0195 | 大盤指數、期貨與總體經濟: 0.016 | 其他產業或綜合新聞: 0.0089 | 傳統製造與原物料: 0.0087 | 民生消費與零售: 0.0068 | 航運與物流: 0.006 | 生技與醫療: 0.0046 | 營建與房地產: 0.0037 | 通訊網路與軟體服務: 0.0035 | 金融與保險業: 0.0031</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -23455,6 +25070,11 @@
           <t>電子科技與半導體: 0.189 | 通訊網路與軟體服務: 0.1217 | 民生消費與零售: 0.0976 | 傳統製造與原物料: 0.0938 | 再生能源與永續發展: 0.0926 | 金融與保險業: 0.0747 | 生技與醫療: 0.0734 | 航運與物流: 0.0728 | 其他產業或綜合新聞: 0.0672 | 大盤指數、期貨與總體經濟: 0.0663 | 營建與房地產: 0.0509</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -23516,6 +25136,11 @@
           <t>大盤指數、期貨與總體經濟: 0.1852 | 民生消費與零售: 0.136 | 金融與保險業: 0.1293 | 電子科技與半導體: 0.0953 | 再生能源與永續發展: 0.0919 | 其他產業或綜合新聞: 0.0744 | 傳統製造與原物料: 0.0692 | 生技與醫療: 0.0664 | 航運與物流: 0.0649 | 通訊網路與軟體服務: 0.0613 | 營建與房地產: 0.026</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -23575,6 +25200,11 @@
       <c r="M326" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.2307 | 金融與保險業: 0.1703 | 傳統製造與原物料: 0.1653 | 營建與房地產: 0.1413 | 大盤指數、期貨與總體經濟: 0.0869 | 航運與物流: 0.0687 | 再生能源與永續發展: 0.0377 | 其他產業或綜合新聞: 0.0289 | 生技與醫療: 0.0261 | 通訊網路與軟體服務: 0.026 | 電子科技與半導體: 0.0182</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -23644,6 +25274,11 @@
       <c r="M327" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -23715,6 +25350,11 @@
           <t>電子科技與半導體: 0.2218 | 再生能源與永續發展: 0.1365 | 通訊網路與軟體服務: 0.1089 | 其他產業或綜合新聞: 0.1021 | 金融與保險業: 0.0963 | 民生消費與零售: 0.0876 | 大盤指數、期貨與總體經濟: 0.0663 | 生技與醫療: 0.059 | 航運與物流: 0.0416 | 傳統製造與原物料: 0.0403 | 營建與房地產: 0.0397</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -23784,6 +25424,11 @@
       <c r="M329" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.6941 | 通訊網路與軟體服務: 0.056 | 大盤指數、期貨與總體經濟: 0.0426 | 再生能源與永續發展: 0.0341 | 民生消費與零售: 0.0278 | 航運與物流: 0.027 | 金融與保險業: 0.0256 | 其他產業或綜合新聞: 0.0248 | 傳統製造與原物料: 0.0245 | 生技與醫療: 0.0238 | 營建與房地產: 0.0195</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -23901,6 +25546,11 @@
           <t>金融與保險業: 0.1292 | 其他產業或綜合新聞: 0.1265 | 大盤指數、期貨與總體經濟: 0.1121 | 電子科技與半導體: 0.1095 | 民生消費與零售: 0.1045 | 再生能源與永續發展: 0.0838 | 通訊網路與軟體服務: 0.0818 | 生技與醫療: 0.075 | 航運與物流: 0.0745 | 營建與房地產: 0.0637 | 傳統製造與原物料: 0.0394</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -23960,6 +25610,11 @@
       <c r="M331" t="inlineStr">
         <is>
           <t>傳統製造與原物料: 0.2052 | 再生能源與永續發展: 0.1252 | 民生消費與零售: 0.1235 | 電子科技與半導體: 0.1002 | 大盤指數、期貨與總體經濟: 0.084 | 航運與物流: 0.0823 | 通訊網路與軟體服務: 0.0734 | 生技與醫療: 0.0601 | 其他產業或綜合新聞: 0.0507 | 營建與房地產: 0.05 | 金融與保險業: 0.0455</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -24039,6 +25694,11 @@
           <t>電子科技與半導體: 0.5758 | 再生能源與永續發展: 0.0731 | 民生消費與零售: 0.0673 | 其他產業或綜合新聞: 0.0483 | 生技與醫療: 0.048 | 大盤指數、期貨與總體經濟: 0.0452 | 金融與保險業: 0.0365 | 傳統製造與原物料: 0.0356 | 航運與物流: 0.0265 | 營建與房地產: 0.0237 | 通訊網路與軟體服務: 0.0198</t>
         </is>
       </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -24098,6 +25758,11 @@
       <c r="M333" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.2001 | 民生消費與零售: 0.1206 | 金融與保險業: 0.1069 | 生技與醫療: 0.086 | 傳統製造與原物料: 0.0824 | 其他產業或綜合新聞: 0.0764 | 航運與物流: 0.0732 | 營建與房地產: 0.0666 | 再生能源與永續發展: 0.0632 | 通訊網路與軟體服務: 0.0628 | 電子科技與半導體: 0.0617</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -24171,6 +25836,11 @@
           <t>電子科技與半導體: 0.2201 | 通訊網路與軟體服務: 0.1668 | 民生消費與零售: 0.117 | 再生能源與永續發展: 0.1084 | 大盤指數、期貨與總體經濟: 0.0814 | 金融與保險業: 0.0727 | 其他產業或綜合新聞: 0.0667 | 航運與物流: 0.0544 | 生技與醫療: 0.0482 | 傳統製造與原物料: 0.0445 | 營建與房地產: 0.0198</t>
         </is>
       </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -24242,6 +25912,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -24311,6 +25986,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -24372,6 +26052,11 @@
           <t>通訊網路與軟體服務: 0.7668 | 電子科技與半導體: 0.1832 | 大盤指數、期貨與總體經濟: 0.0389 | 金融與保險業: 0.0051 | 航運與物流: 0.0013 | 再生能源與永續發展: 0.0013 | 民生消費與零售: 0.0013 | 其他產業或綜合新聞: 0.0008 | 生技與醫療: 0.0006 | 傳統製造與原物料: 0.0005 | 營建與房地產: 0.0003</t>
         </is>
       </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -24431,6 +26116,11 @@
       <c r="M338" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.1811 | 民生消費與零售: 0.1119 | 金融與保險業: 0.1102 | 傳統製造與原物料: 0.0885 | 生技與醫療: 0.0808 | 營建與房地產: 0.0804 | 通訊網路與軟體服務: 0.0768 | 電子科技與半導體: 0.0735 | 再生能源與永續發展: 0.071 | 其他產業或綜合新聞: 0.067 | 航運與物流: 0.0589</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -24506,6 +26196,11 @@
           <t>通訊網路與軟體服務: 0.4896 | 再生能源與永續發展: 0.1177 | 大盤指數、期貨與總體經濟: 0.0708 | 其他產業或綜合新聞: 0.0553 | 營建與房地產: 0.0434 | 民生消費與零售: 0.0429 | 航運與物流: 0.0422 | 金融與保險業: 0.0404 | 生技與醫療: 0.038 | 傳統製造與原物料: 0.0303 | 電子科技與半導體: 0.0295</t>
         </is>
       </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -24567,6 +26262,11 @@
           <t>航運與物流: 0.6229 | 再生能源與永續發展: 0.3314 | 大盤指數、期貨與總體經濟: 0.0345 | 民生消費與零售: 0.0032 | 傳統製造與原物料: 0.0025 | 其他產業或綜合新聞: 0.0015 | 營建與房地產: 0.001 | 生技與醫療: 0.0008 | 電子科技與半導體: 0.0008 | 金融與保險業: 0.0007 | 通訊網路與軟體服務: 0.0007</t>
         </is>
       </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -24628,6 +26328,11 @@
           <t>金融與保險業: 0.1913 | 民生消費與零售: 0.1325 | 電子科技與半導體: 0.1098 | 大盤指數、期貨與總體經濟: 0.1098 | 通訊網路與軟體服務: 0.0867 | 營建與房地產: 0.0842 | 傳統製造與原物料: 0.0725 | 再生能源與永續發展: 0.0649 | 航運與物流: 0.0524 | 其他產業或綜合新聞: 0.0501 | 生技與醫療: 0.0458</t>
         </is>
       </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -24689,6 +26394,11 @@
           <t>金融與保險業: 0.228 | 大盤指數、期貨與總體經濟: 0.1267 | 電子科技與半導體: 0.1237 | 通訊網路與軟體服務: 0.1067 | 民生消費與零售: 0.078 | 再生能源與永續發展: 0.0749 | 傳統製造與原物料: 0.0665 | 其他產業或綜合新聞: 0.0648 | 營建與房地產: 0.052 | 航運與物流: 0.0425 | 生技與醫療: 0.0363</t>
         </is>
       </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -24750,6 +26460,11 @@
           <t>金融與保險業: 0.5496 | 大盤指數、期貨與總體經濟: 0.4272 | 民生消費與零售: 0.0049 | 其他產業或綜合新聞: 0.0034 | 電子科技與半導體: 0.0033 | 航運與物流: 0.0029 | 傳統製造與原物料: 0.0024 | 再生能源與永續發展: 0.002 | 通訊網路與軟體服務: 0.0015 | 生技與醫療: 0.0015 | 營建與房地產: 0.0012</t>
         </is>
       </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -24811,6 +26526,11 @@
           <t>通訊網路與軟體服務: 0.4609 | 電子科技與半導體: 0.1187 | 金融與保險業: 0.1166 | 大盤指數、期貨與總體經濟: 0.0603 | 傳統製造與原物料: 0.0565 | 民生消費與零售: 0.0412 | 其他產業或綜合新聞: 0.0342 | 再生能源與永續發展: 0.0323 | 航運與物流: 0.032 | 生技與醫療: 0.0271 | 營建與房地產: 0.0203</t>
         </is>
       </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -24872,6 +26592,11 @@
       <c r="M345" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.7278 | 電子科技與半導體: 0.0922 | 金融與保險業: 0.0336 | 航運與物流: 0.0312 | 傳統製造與原物料: 0.0288 | 再生能源與永續發展: 0.0201 | 生技與醫療: 0.0153 | 其他產業或綜合新聞: 0.0142 | 大盤指數、期貨與總體經濟: 0.0133 | 民生消費與零售: 0.0131 | 營建與房地產: 0.0103</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -24939,6 +26664,11 @@
           <t>電子科技與半導體: 0.9066 | 通訊網路與軟體服務: 0.0299 | 大盤指數、期貨與總體經濟: 0.0129 | 航運與物流: 0.0098 | 民生消費與零售: 0.0085 | 傳統製造與原物料: 0.0081 | 營建與房地產: 0.0059 | 金融與保險業: 0.0053 | 再生能源與永續發展: 0.0052 | 生技與醫療: 0.0043 | 其他產業或綜合新聞: 0.0034</t>
         </is>
       </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -25000,6 +26730,11 @@
           <t>通訊網路與軟體服務: 0.6136 | 電子科技與半導體: 0.2919 | 大盤指數、期貨與總體經濟: 0.0181 | 航運與物流: 0.0161 | 傳統製造與原物料: 0.0128 | 生技與醫療: 0.0095 | 營建與房地產: 0.0092 | 民生消費與零售: 0.0086 | 金融與保險業: 0.0075 | 其他產業或綜合新聞: 0.0071 | 再生能源與永續發展: 0.0056</t>
         </is>
       </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -25059,6 +26794,11 @@
       <c r="M348" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.9207 | 大盤指數、期貨與總體經濟: 0.0373 | 再生能源與永續發展: 0.0111 | 其他產業或綜合新聞: 0.0059 | 傳統製造與原物料: 0.0054 | 航運與物流: 0.0041 | 生技與醫療: 0.0039 | 通訊網路與軟體服務: 0.0033 | 民生消費與零售: 0.0033 | 金融與保險業: 0.0025 | 營建與房地產: 0.0023</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -25130,6 +26870,11 @@
           <t>通訊網路與軟體服務: 0.3855 | 大盤指數、期貨與總體經濟: 0.1042 | 電子科技與半導體: 0.0999 | 民生消費與零售: 0.0976 | 再生能源與永續發展: 0.0921 | 金融與保險業: 0.0516 | 生技與醫療: 0.0506 | 其他產業或綜合新聞: 0.0495 | 傳統製造與原物料: 0.0319 | 航運與物流: 0.0285 | 營建與房地產: 0.0085</t>
         </is>
       </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -25189,6 +26934,11 @@
       <c r="M350" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.6303 | 大盤指數、期貨與總體經濟: 0.1325 | 電子科技與半導體: 0.1006 | 傳統製造與原物料: 0.0278 | 航運與物流: 0.0245 | 再生能源與永續發展: 0.0229 | 金融與保險業: 0.018 | 民生消費與零售: 0.014 | 其他產業或綜合新聞: 0.0132 | 營建與房地產: 0.0085 | 生技與醫療: 0.0077</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -25262,6 +27012,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -25323,6 +27078,11 @@
           <t>金融與保險業: 0.2338 | 電子科技與半導體: 0.2019 | 大盤指數、期貨與總體經濟: 0.1083 | 傳統製造與原物料: 0.0867 | 通訊網路與軟體服務: 0.0862 | 民生消費與零售: 0.0754 | 航運與物流: 0.0607 | 其他產業或綜合新聞: 0.046 | 再生能源與永續發展: 0.0397 | 生技與醫療: 0.0311 | 營建與房地產: 0.0302</t>
         </is>
       </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -25390,6 +27150,11 @@
           <t>大盤指數、期貨與總體經濟: 0.2883 | 金融與保險業: 0.1878 | 其他產業或綜合新聞: 0.099 | 再生能源與永續發展: 0.0906 | 民生消費與零售: 0.0725 | 傳統製造與原物料: 0.0655 | 營建與房地產: 0.0507 | 電子科技與半導體: 0.0471 | 通訊網路與軟體服務: 0.0389 | 航運與物流: 0.0314 | 生技與醫療: 0.028</t>
         </is>
       </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -25449,6 +27214,11 @@
       <c r="M354" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.9047 | 金融與保險業: 0.0507 | 民生消費與零售: 0.0099 | 電子科技與半導體: 0.0085 | 大盤指數、期貨與總體經濟: 0.0077 | 再生能源與永續發展: 0.0033 | 生技與醫療: 0.0032 | 其他產業或綜合新聞: 0.0031 | 傳統製造與原物料: 0.0031 | 營建與房地產: 0.003 | 航運與物流: 0.0029</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -25522,6 +27292,11 @@
           <t>通訊網路與軟體服務: 0.5057 | 電子科技與半導體: 0.425 | 再生能源與永續發展: 0.0191 | 航運與物流: 0.0141 | 其他產業或綜合新聞: 0.0123 | 生技與醫療: 0.0062 | 民生消費與零售: 0.0062 | 金融與保險業: 0.004 | 大盤指數、期貨與總體經濟: 0.0033 | 傳統製造與原物料: 0.0021 | 營建與房地產: 0.002</t>
         </is>
       </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -25591,6 +27366,11 @@
       <c r="M356" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.3971 | 大盤指數、期貨與總體經濟: 0.1608 | 通訊網路與軟體服務: 0.1085 | 傳統製造與原物料: 0.061 | 民生消費與零售: 0.0521 | 再生能源與永續發展: 0.0496 | 營建與房地產: 0.0434 | 金融與保險業: 0.0422 | 其他產業或綜合新聞: 0.0419 | 航運與物流: 0.0271 | 生技與醫療: 0.0163</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -25670,6 +27450,11 @@
           <t>電子科技與半導體: 0.2958 | 金融與保險業: 0.1977 | 大盤指數、期貨與總體經濟: 0.1083 | 通訊網路與軟體服務: 0.0869 | 其他產業或綜合新聞: 0.0672 | 航運與物流: 0.0452 | 再生能源與永續發展: 0.043 | 民生消費與零售: 0.042 | 生技與醫療: 0.0412 | 傳統製造與原物料: 0.0401 | 營建與房地產: 0.0326</t>
         </is>
       </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -25739,6 +27524,11 @@
       <c r="M358" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -25834,6 +27624,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -25901,6 +27696,11 @@
       <c r="M360" t="inlineStr">
         <is>
           <t>其他產業或綜合新聞: 0.3344 | 再生能源與永續發展: 0.133 | 通訊網路與軟體服務: 0.109 | 電子科技與半導體: 0.0733 | 民生消費與零售: 0.0729 | 航運與物流: 0.059 | 生技與醫療: 0.0572 | 金融與保險業: 0.0526 | 大盤指數、期貨與總體經濟: 0.0477 | 營建與房地產: 0.0313 | 傳統製造與原物料: 0.0295</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -25974,6 +27774,11 @@
       <c r="M361" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2239 | 通訊網路與軟體服務: 0.1148 | 金融與保險業: 0.1051 | 再生能源與永續發展: 0.1018 | 大盤指數、期貨與總體經濟: 0.0918 | 其他產業或綜合新聞: 0.0806 | 航運與物流: 0.0778 | 民生消費與零售: 0.0713 | 生技與醫療: 0.054 | 傳統製造與原物料: 0.0523 | 營建與房地產: 0.0265</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -26083,6 +27888,11 @@
           <t>大盤指數、期貨與總體經濟: 0.3276 | 金融與保險業: 0.1057 | 其他產業或綜合新聞: 0.1053 | 電子科技與半導體: 0.0825 | 民生消費與零售: 0.0715 | 通訊網路與軟體服務: 0.0658 | 營建與房地產: 0.0594 | 航運與物流: 0.0574 | 生技與醫療: 0.0529 | 再生能源與永續發展: 0.041 | 傳統製造與原物料: 0.0309</t>
         </is>
       </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -26156,6 +27966,11 @@
       <c r="M363" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -26275,6 +28090,11 @@
           <t>大盤指數、期貨與總體經濟: 0.2149 | 通訊網路與軟體服務: 0.199 | 其他產業或綜合新聞: 0.1632 | 民生消費與零售: 0.1576 | 航運與物流: 0.078 | 電子科技與半導體: 0.0435 | 金融與保險業: 0.0418 | 傳統製造與原物料: 0.0391 | 再生能源與永續發展: 0.0361 | 生技與醫療: 0.0139 | 營建與房地產: 0.0129</t>
         </is>
       </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -26346,6 +28166,11 @@
           <t>電子科技與半導體: 0.2088 | 大盤指數、期貨與總體經濟: 0.1249 | 再生能源與永續發展: 0.1131 | 金融與保險業: 0.105 | 生技與醫療: 0.1036 | 民生消費與零售: 0.0902 | 其他產業或綜合新聞: 0.0799 | 營建與房地產: 0.0531 | 通訊網路與軟體服務: 0.0468 | 傳統製造與原物料: 0.0387 | 航運與物流: 0.036</t>
         </is>
       </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -26405,6 +28230,11 @@
       <c r="M366" t="inlineStr">
         <is>
           <t>航運與物流: 0.9389 | 大盤指數、期貨與總體經濟: 0.027 | 再生能源與永續發展: 0.0202 | 民生消費與零售: 0.0045 | 金融與保險業: 0.0036 | 傳統製造與原物料: 0.0017 | 營建與房地產: 0.0013 | 其他產業或綜合新聞: 0.0012 | 生技與醫療: 0.0008 | 電子科技與半導體: 0.0005 | 通訊網路與軟體服務: 0.0003</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -26482,6 +28312,11 @@
           <t>電子科技與半導體: 0.4196 | 民生消費與零售: 0.0998 | 大盤指數、期貨與總體經濟: 0.0826 | 通訊網路與軟體服務: 0.0791 | 其他產業或綜合新聞: 0.0733 | 再生能源與永續發展: 0.0672 | 航運與物流: 0.0603 | 金融與保險業: 0.0388 | 傳統製造與原物料: 0.0342 | 生技與醫療: 0.0285 | 營建與房地產: 0.0165</t>
         </is>
       </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
@@ -26553,6 +28388,11 @@
           <t>通訊網路與軟體服務: 0.4447 | 電子科技與半導體: 0.1876 | 民生消費與零售: 0.1114 | 大盤指數、期貨與總體經濟: 0.0663 | 再生能源與永續發展: 0.0481 | 其他產業或綜合新聞: 0.0398 | 航運與物流: 0.0328 | 營建與房地產: 0.0218 | 生技與醫療: 0.0186 | 金融與保險業: 0.017 | 傳統製造與原物料: 0.0119</t>
         </is>
       </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
@@ -26612,6 +28452,11 @@
       <c r="M369" t="inlineStr">
         <is>
           <t>生技與醫療: 0.9302 | 民生消費與零售: 0.011 | 再生能源與永續發展: 0.0096 | 大盤指數、期貨與總體經濟: 0.0084 | 航運與物流: 0.0073 | 傳統製造與原物料: 0.0063 | 營建與房地產: 0.006 | 電子科技與半導體: 0.0058 | 金融與保險業: 0.0056 | 通訊網路與軟體服務: 0.0054 | 其他產業或綜合新聞: 0.0044</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -26679,6 +28524,11 @@
       <c r="M370" t="inlineStr">
         <is>
           <t>航運與物流: 0.3915 | 電子科技與半導體: 0.1203 | 其他產業或綜合新聞: 0.1113 | 再生能源與永續發展: 0.1045 | 民生消費與零售: 0.0853 | 大盤指數、期貨與總體經濟: 0.0515 | 營建與房地產: 0.038 | 通訊網路與軟體服務: 0.0364 | 傳統製造與原物料: 0.0311 | 生技與醫療: 0.016 | 金融與保險業: 0.014</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -26750,6 +28600,11 @@
           <t>通訊網路與軟體服務: 0.3789 | 電子科技與半導體: 0.1231 | 再生能源與永續發展: 0.1043 | 金融與保險業: 0.0711 | 其他產業或綜合新聞: 0.0687 | 大盤指數、期貨與總體經濟: 0.0667 | 民生消費與零售: 0.0492 | 航運與物流: 0.0424 | 營建與房地產: 0.0377 | 生技與醫療: 0.0322 | 傳統製造與原物料: 0.0257</t>
         </is>
       </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
@@ -26819,6 +28674,11 @@
           <t>電子科技與半導體: 0.62 | 通訊網路與軟體服務: 0.3235 | 其他產業或綜合新聞: 0.0422 | 再生能源與永續發展: 0.0048 | 傳統製造與原物料: 0.0041 | 民生消費與零售: 0.002 | 大盤指數、期貨與總體經濟: 0.001 | 航運與物流: 0.0008 | 生技與醫療: 0.0007 | 營建與房地產: 0.0005 | 金融與保險業: 0.0004</t>
         </is>
       </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
@@ -26882,6 +28742,11 @@
           <t>電子科技與半導體: 0.9879 | 傳統製造與原物料: 0.0017 | 大盤指數、期貨與總體經濟: 0.0016 | 其他產業或綜合新聞: 0.0015 | 再生能源與永續發展: 0.0015 | 通訊網路與軟體服務: 0.0012 | 航運與物流: 0.0012 | 民生消費與零售: 0.0011 | 營建與房地產: 0.001 | 生技與醫療: 0.0008 | 金融與保險業: 0.0006</t>
         </is>
       </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
@@ -26939,6 +28804,11 @@
       <c r="M374" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.9457 | 電子科技與半導體: 0.0261 | 大盤指數、期貨與總體經濟: 0.0043 | 傳統製造與原物料: 0.0043 | 航運與物流: 0.0033 | 再生能源與永續發展: 0.0031 | 其他產業或綜合新聞: 0.0031 | 民生消費與零售: 0.0029 | 營建與房地產: 0.0025 | 生技與醫療: 0.0025 | 金融與保險業: 0.0022</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -27014,6 +28884,11 @@
           <t>電子科技與半導體: 0.3315 | 通訊網路與軟體服務: 0.1652 | 大盤指數、期貨與總體經濟: 0.1323 | 再生能源與永續發展: 0.1145 | 金融與保險業: 0.0574 | 其他產業或綜合新聞: 0.0572 | 航運與物流: 0.0398 | 民生消費與零售: 0.0366 | 傳統製造與原物料: 0.0255 | 生技與醫療: 0.0228 | 營建與房地產: 0.0172</t>
         </is>
       </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
@@ -27079,6 +28954,11 @@
       <c r="M376" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.438 | 金融與保險業: 0.1543 | 民生消費與零售: 0.1433 | 電子科技與半導體: 0.0497 | 其他產業或綜合新聞: 0.0485 | 再生能源與永續發展: 0.0474 | 營建與房地產: 0.0379 | 傳統製造與原物料: 0.0233 | 航運與物流: 0.0206 | 通訊網路與軟體服務: 0.019 | 生技與醫療: 0.018</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -27152,6 +29032,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
@@ -27211,6 +29096,11 @@
       <c r="M378" t="inlineStr">
         <is>
           <t>傳統製造與原物料: 0.9266 | 再生能源與永續發展: 0.0154 | 大盤指數、期貨與總體經濟: 0.014 | 民生消費與零售: 0.0138 | 航運與物流: 0.0066 | 金融與保險業: 0.005 | 生技與醫療: 0.0049 | 營建與房地產: 0.0045 | 其他產業或綜合新聞: 0.0041 | 通訊網路與軟體服務: 0.0026 | 電子科技與半導體: 0.0024</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -27284,6 +29174,11 @@
       <c r="M379" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -27379,6 +29274,11 @@
           <t>電子科技與半導體: 0.519 | 通訊網路與軟體服務: 0.1087 | 大盤指數、期貨與總體經濟: 0.094 | 民生消費與零售: 0.0816 | 其他產業或綜合新聞: 0.0477 | 再生能源與永續發展: 0.045 | 航運與物流: 0.039 | 金融與保險業: 0.0264 | 傳統製造與原物料: 0.0204 | 生技與醫療: 0.0095 | 營建與房地產: 0.0089</t>
         </is>
       </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
@@ -27448,6 +29348,11 @@
           <t>電子科技與半導體: 0.2574 | 大盤指數、期貨與總體經濟: 0.1685 | 再生能源與永續發展: 0.1507 | 通訊網路與軟體服務: 0.0797 | 金融與保險業: 0.0752 | 其他產業或綜合新聞: 0.0638 | 生技與醫療: 0.06 | 民生消費與零售: 0.0444 | 傳統製造與原物料: 0.0366 | 航運與物流: 0.0355 | 營建與房地產: 0.0282</t>
         </is>
       </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
@@ -27517,6 +29422,11 @@
           <t>電子科技與半導體: 0.4276 | 通訊網路與軟體服務: 0.1038 | 再生能源與永續發展: 0.0962 | 大盤指數、期貨與總體經濟: 0.0652 | 其他產業或綜合新聞: 0.0632 | 民生消費與零售: 0.0483 | 金融與保險業: 0.0467 | 傳統製造與原物料: 0.0439 | 生技與醫療: 0.0438 | 航運與物流: 0.0356 | 營建與房地產: 0.0257</t>
         </is>
       </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
@@ -27588,6 +29498,11 @@
           <t>電子科技與半導體: 0.6915 | 大盤指數、期貨與總體經濟: 0.13 | 通訊網路與軟體服務: 0.0583 | 金融與保險業: 0.0264 | 再生能源與永續發展: 0.021 | 傳統製造與原物料: 0.0178 | 其他產業或綜合新聞: 0.0169 | 民生消費與零售: 0.0127 | 航運與物流: 0.0102 | 生技與醫療: 0.0088 | 營建與房地產: 0.0065</t>
         </is>
       </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
@@ -27649,6 +29564,11 @@
       <c r="M384" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.5172 | 電子科技與半導體: 0.1931 | 通訊網路與軟體服務: 0.1185 | 航運與物流: 0.0653 | 其他產業或綜合新聞: 0.0297 | 再生能源與永續發展: 0.0205 | 金融與保險業: 0.0149 | 傳統製造與原物料: 0.0131 | 民生消費與零售: 0.0102 | 營建與房地產: 0.0093 | 生技與醫療: 0.0083</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -27720,6 +29640,11 @@
           <t>電子科技與半導體: 0.364 | 通訊網路與軟體服務: 0.1042 | 民生消費與零售: 0.0855 | 再生能源與永續發展: 0.085 | 傳統製造與原物料: 0.074 | 其他產業或綜合新聞: 0.0722 | 大盤指數、期貨與總體經濟: 0.0621 | 航運與物流: 0.0471 | 金融與保險業: 0.0413 | 生技與醫療: 0.0326 | 營建與房地產: 0.032</t>
         </is>
       </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
@@ -27791,6 +29716,11 @@
           <t>大盤指數、期貨與總體經濟: 0.4698 | 電子科技與半導體: 0.1648 | 金融與保險業: 0.0701 | 傳統製造與原物料: 0.0529 | 民生消費與零售: 0.0488 | 通訊網路與軟體服務: 0.047 | 再生能源與永續發展: 0.0372 | 其他產業或綜合新聞: 0.0321 | 營建與房地產: 0.0273 | 航運與物流: 0.0252 | 生技與醫療: 0.0249</t>
         </is>
       </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
@@ -27854,6 +29784,11 @@
       <c r="M387" t="inlineStr">
         <is>
           <t>金融與保險業: 0.7711 | 大盤指數、期貨與總體經濟: 0.0794 | 航運與物流: 0.0241 | 再生能源與永續發展: 0.0238 | 其他產業或綜合新聞: 0.0224 | 傳統製造與原物料: 0.0166 | 電子科技與半導體: 0.0138 | 營建與房地產: 0.0126 | 民生消費與零售: 0.0125 | 生技與醫療: 0.0125 | 通訊網路與軟體服務: 0.0111</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -27929,6 +29864,11 @@
           <t>大盤指數、期貨與總體經濟: 0.177 | 民生消費與零售: 0.0983 | 其他產業或綜合新聞: 0.0974 | 金融與保險業: 0.0974 | 通訊網路與軟體服務: 0.097 | 電子科技與半導體: 0.0873 | 營建與房地產: 0.0779 | 再生能源與永續發展: 0.0761 | 生技與醫療: 0.0652 | 傳統製造與原物料: 0.0634 | 航運與物流: 0.063</t>
         </is>
       </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
@@ -27998,6 +29938,11 @@
           <t>通訊網路與軟體服務: 0.1994 | 航運與物流: 0.1716 | 電子科技與半導體: 0.1479 | 其他產業或綜合新聞: 0.1016 | 再生能源與永續發展: 0.088 | 大盤指數、期貨與總體經濟: 0.0869 | 民生消費與零售: 0.0668 | 金融與保險業: 0.0408 | 生技與醫療: 0.0374 | 營建與房地產: 0.0303 | 傳統製造與原物料: 0.0293</t>
         </is>
       </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
@@ -28067,6 +30012,11 @@
           <t>通訊網路與軟體服務: 0.5889 | 大盤指數、期貨與總體經濟: 0.0846 | 其他產業或綜合新聞: 0.0749 | 民生消費與零售: 0.0717 | 電子科技與半導體: 0.0651 | 再生能源與永續發展: 0.0531 | 航運與物流: 0.03 | 傳統製造與原物料: 0.0114 | 生技與醫療: 0.0078 | 金融與保險業: 0.0066 | 營建與房地產: 0.0059</t>
         </is>
       </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
@@ -28132,6 +30082,11 @@
       <c r="M391" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.4579 | 電子科技與半導體: 0.1311 | 再生能源與永續發展: 0.0745 | 其他產業或綜合新聞: 0.064 | 傳統製造與原物料: 0.0511 | 金融與保險業: 0.0448 | 民生消費與零售: 0.0395 | 航運與物流: 0.0382 | 生技與醫療: 0.0345 | 大盤指數、期貨與總體經濟: 0.0338 | 營建與房地產: 0.0306</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -28203,6 +30158,11 @@
           <t>航運與物流: 0.2738 | 傳統製造與原物料: 0.2294 | 民生消費與零售: 0.1013 | 再生能源與永續發展: 0.0916 | 大盤指數、期貨與總體經濟: 0.0898 | 其他產業或綜合新聞: 0.0799 | 金融與保險業: 0.0338 | 生技與醫療: 0.031 | 營建與房地產: 0.0255 | 通訊網路與軟體服務: 0.0246 | 電子科技與半導體: 0.0193</t>
         </is>
       </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -28270,6 +30230,11 @@
           <t>電子科技與半導體: 0.9328 | 再生能源與永續發展: 0.013 | 金融與保險業: 0.0105 | 大盤指數、期貨與總體經濟: 0.0095 | 其他產業或綜合新聞: 0.0082 | 通訊網路與軟體服務: 0.0069 | 生技與醫療: 0.0044 | 航運與物流: 0.0044 | 民生消費與零售: 0.0041 | 傳統製造與原物料: 0.0036 | 營建與房地產: 0.0027</t>
         </is>
       </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -28335,6 +30300,11 @@
       <c r="M394" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.314 | 電子科技與半導體: 0.1445 | 通訊網路與軟體服務: 0.1253 | 其他產業或綜合新聞: 0.094 | 民生消費與零售: 0.0594 | 傳統製造與原物料: 0.056 | 生技與醫療: 0.0463 | 再生能源與永續發展: 0.0451 | 營建與房地產: 0.0422 | 航運與物流: 0.039 | 金融與保險業: 0.0342</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -28406,6 +30376,11 @@
       <c r="M395" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -28479,6 +30454,11 @@
           <t>航運與物流: 0.3944 | 大盤指數、期貨與總體經濟: 0.2215 | 電子科技與半導體: 0.117 | 金融與保險業: 0.0756 | 民生消費與零售: 0.0518 | 再生能源與永續發展: 0.0381 | 通訊網路與軟體服務: 0.035 | 其他產業或綜合新聞: 0.025 | 生技與醫療: 0.0196 | 傳統製造與原物料: 0.0163 | 營建與房地產: 0.0057</t>
         </is>
       </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -28550,6 +30530,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -28621,6 +30606,11 @@
           <t>大盤指數、期貨與總體經濟: 0.1519 | 航運與物流: 0.132 | 再生能源與永續發展: 0.1282 | 電子科技與半導體: 0.1269 | 金融與保險業: 0.0988 | 其他產業或綜合新聞: 0.0815 | 通訊網路與軟體服務: 0.0808 | 生技與醫療: 0.0554 | 傳統製造與原物料: 0.0552 | 民生消費與零售: 0.0503 | 營建與房地產: 0.039</t>
         </is>
       </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -28690,6 +30680,11 @@
           <t>電子科技與半導體: 0.3835 | 其他產業或綜合新聞: 0.364 | 生技與醫療: 0.1006 | 通訊網路與軟體服務: 0.0477 | 再生能源與永續發展: 0.037 | 營建與房地產: 0.0157 | 傳統製造與原物料: 0.0138 | 民生消費與零售: 0.0121 | 航運與物流: 0.0089 | 大盤指數、期貨與總體經濟: 0.0089 | 金融與保險業: 0.0078</t>
         </is>
       </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -28753,6 +30748,11 @@
       <c r="M400" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.4193 | 通訊網路與軟體服務: 0.2957 | 大盤指數、期貨與總體經濟: 0.1098 | 再生能源與永續發展: 0.0781 | 航運與物流: 0.0278 | 民生消費與零售: 0.0191 | 其他產業或綜合新聞: 0.0184 | 營建與房地產: 0.0082 | 傳統製造與原物料: 0.0081 | 金融與保險業: 0.008 | 生技與醫療: 0.0074</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -28828,6 +30828,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -28891,6 +30896,11 @@
       <c r="M402" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.1355 | 大盤指數、期貨與總體經濟: 0.1106 | 民生消費與零售: 0.1039 | 其他產業或綜合新聞: 0.0959 | 航運與物流: 0.0901 | 營建與房地產: 0.0868 | 傳統製造與原物料: 0.0861 | 金融與保險業: 0.0784 | 電子科技與半導體: 0.0772 | 通訊網路與軟體服務: 0.0739 | 生技與醫療: 0.0618</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -28962,6 +30972,11 @@
       <c r="M403" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.673 | 通訊網路與軟體服務: 0.1093 | 再生能源與永續發展: 0.0623 | 其他產業或綜合新聞: 0.0337 | 航運與物流: 0.0265 | 營建與房地產: 0.0194 | 民生消費與零售: 0.0182 | 金融與保險業: 0.0171 | 生技與醫療: 0.0167 | 傳統製造與原物料: 0.0138 | 大盤指數、期貨與總體經濟: 0.0099</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -29045,6 +31060,11 @@
           <t>電子科技與半導體: 0.2151 | 大盤指數、期貨與總體經濟: 0.1577 | 再生能源與永續發展: 0.1393 | 民生消費與零售: 0.1127 | 其他產業或綜合新聞: 0.0766 | 通訊網路與軟體服務: 0.0716 | 航運與物流: 0.0538 | 生技與醫療: 0.0531 | 金融與保險業: 0.0511 | 傳統製造與原物料: 0.0401 | 營建與房地產: 0.029</t>
         </is>
       </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -29116,6 +31136,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
@@ -29181,6 +31206,11 @@
       <c r="M406" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.1215 | 其他產業或綜合新聞: 0.1181 | 民生消費與零售: 0.1161 | 電子科技與半導體: 0.1054 | 金融與保險業: 0.0926 | 通訊網路與軟體服務: 0.0819 | 航運與物流: 0.0795 | 再生能源與永續發展: 0.0787 | 生技與醫療: 0.0722 | 營建與房地產: 0.0675 | 傳統製造與原物料: 0.0666</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -29256,6 +31286,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -29323,6 +31358,11 @@
       <c r="M408" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.1448 | 再生能源與永續發展: 0.1289 | 營建與房地產: 0.1096 | 其他產業或綜合新聞: 0.1002 | 民生消費與零售: 0.0857 | 大盤指數、期貨與總體經濟: 0.0839 | 通訊網路與軟體服務: 0.0789 | 金融與保險業: 0.0786 | 傳統製造與原物料: 0.0694 | 航運與物流: 0.0608 | 生技與醫療: 0.0594</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -29400,6 +31440,11 @@
           <t>其他產業或綜合新聞: 0.2127 | 電子科技與半導體: 0.1937 | 通訊網路與軟體服務: 0.183 | 再生能源與永續發展: 0.0797 | 金融與保險業: 0.0644 | 生技與醫療: 0.0634 | 民生消費與零售: 0.0553 | 航運與物流: 0.0536 | 營建與房地產: 0.0481 | 傳統製造與原物料: 0.0306 | 大盤指數、期貨與總體經濟: 0.0155</t>
         </is>
       </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -29469,6 +31514,11 @@
           <t>金融與保險業: 0.2111 | 再生能源與永續發展: 0.183 | 大盤指數、期貨與總體經濟: 0.1376 | 民生消費與零售: 0.1217 | 其他產業或綜合新聞: 0.1119 | 電子科技與半導體: 0.0494 | 傳統製造與原物料: 0.0486 | 生技與醫療: 0.0368 | 航運與物流: 0.0355 | 營建與房地產: 0.0327 | 通訊網路與軟體服務: 0.0317</t>
         </is>
       </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -29534,6 +31584,11 @@
       <c r="M411" t="inlineStr">
         <is>
           <t>民生消費與零售: 0.2923 | 其他產業或綜合新聞: 0.252 | 通訊網路與軟體服務: 0.1867 | 電子科技與半導體: 0.1366 | 再生能源與永續發展: 0.0274 | 金融與保險業: 0.0261 | 傳統製造與原物料: 0.0197 | 大盤指數、期貨與總體經濟: 0.0177 | 航運與物流: 0.0165 | 生技與醫療: 0.0144 | 營建與房地產: 0.0106</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -29611,6 +31666,11 @@
           <t>營建與房地產: 0.7487 | 大盤指數、期貨與總體經濟: 0.0803 | 電子科技與半導體: 0.0646 | 民生消費與零售: 0.0282 | 其他產業或綜合新聞: 0.0254 | 再生能源與永續發展: 0.013 | 金融與保險業: 0.0111 | 航運與物流: 0.0089 | 通訊網路與軟體服務: 0.0073 | 傳統製造與原物料: 0.0068 | 生技與醫療: 0.0056</t>
         </is>
       </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
@@ -29670,6 +31730,11 @@
       <c r="M413" t="inlineStr">
         <is>
           <t>營建與房地產: 0.9827 | 大盤指數、期貨與總體經濟: 0.0046 | 金融與保險業: 0.0031 | 民生消費與零售: 0.0025 | 再生能源與永續發展: 0.0014 | 其他產業或綜合新聞: 0.0013 | 通訊網路與軟體服務: 0.0011 | 電子科技與半導體: 0.0011 | 生技與醫療: 0.0009 | 傳統製造與原物料: 0.0009 | 航運與物流: 0.0007</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>股利與除權息</t>
         </is>
       </c>
     </row>
@@ -29739,6 +31804,11 @@
       <c r="M414" t="inlineStr">
         <is>
           <t>航運與物流: 0.4583 | 再生能源與永續發展: 0.0867 | 大盤指數、期貨與總體經濟: 0.0692 | 民生消費與零售: 0.068 | 其他產業或綜合新聞: 0.0616 | 傳統製造與原物料: 0.0528 | 生技與醫療: 0.0478 | 金融與保險業: 0.0432 | 電子科技與半導體: 0.0418 | 營建與房地產: 0.0373 | 通訊網路與軟體服務: 0.0333</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -29812,6 +31882,11 @@
           <t>金融與保險業: 0.6122 | 通訊網路與軟體服務: 0.1389 | 民生消費與零售: 0.0706 | 其他產業或綜合新聞: 0.0541 | 再生能源與永續發展: 0.0315 | 大盤指數、期貨與總體經濟: 0.0283 | 電子科技與半導體: 0.025 | 營建與房地產: 0.0128 | 航運與物流: 0.0096 | 傳統製造與原物料: 0.0088 | 生技與醫療: 0.0084</t>
         </is>
       </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -29879,6 +31954,11 @@
           <t>金融與保險業: 0.9689 | 其他產業或綜合新聞: 0.0073 | 大盤指數、期貨與總體經濟: 0.0064 | 傳統製造與原物料: 0.0033 | 民生消費與零售: 0.0032 | 再生能源與永續發展: 0.0029 | 航運與物流: 0.0021 | 生技與醫療: 0.0016 | 通訊網路與軟體服務: 0.0016 | 營建與房地產: 0.0015 | 電子科技與半導體: 0.0012</t>
         </is>
       </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -29940,6 +32020,11 @@
       <c r="M417" t="inlineStr">
         <is>
           <t>金融與保險業: 0.179 | 民生消費與零售: 0.1136 | 傳統製造與原物料: 0.1109 | 再生能源與永續發展: 0.1024 | 營建與房地產: 0.1024 | 大盤指數、期貨與總體經濟: 0.0774 | 電子科技與半導體: 0.0757 | 通訊網路與軟體服務: 0.0748 | 生技與醫療: 0.0693 | 航運與物流: 0.0478 | 其他產業或綜合新聞: 0.0467</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -30017,6 +32102,11 @@
           <t>通訊網路與軟體服務: 0.6835 | 電子科技與半導體: 0.1073 | 再生能源與永續發展: 0.0324 | 航運與物流: 0.0274 | 其他產業或綜合新聞: 0.027 | 營建與房地產: 0.0244 | 民生消費與零售: 0.0221 | 大盤指數、期貨與總體經濟: 0.0215 | 傳統製造與原物料: 0.0209 | 金融與保險業: 0.0171 | 生技與醫療: 0.0164</t>
         </is>
       </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
@@ -30082,6 +32172,11 @@
       <c r="M419" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.4845 | 其他產業或綜合新聞: 0.2429 | 傳統製造與原物料: 0.0552 | 通訊網路與軟體服務: 0.0497 | 大盤指數、期貨與總體經濟: 0.0426 | 再生能源與永續發展: 0.0423 | 航運與物流: 0.0211 | 民生消費與零售: 0.0201 | 生技與醫療: 0.0163 | 營建與房地產: 0.0161 | 金融與保險業: 0.0094</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -30151,6 +32246,11 @@
       <c r="M420" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.784 | 通訊網路與軟體服務: 0.1923 | 航運與物流: 0.0076 | 再生能源與永續發展: 0.0048 | 其他產業或綜合新聞: 0.0042 | 大盤指數、期貨與總體經濟: 0.0023 | 民生消費與零售: 0.002 | 傳統製造與原物料: 0.001 | 金融與保險業: 0.0007 | 營建與房地產: 0.0005 | 生技與醫療: 0.0005</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -30226,6 +32326,11 @@
           <t>通訊網路與軟體服務: 0.875 | 電子科技與半導體: 0.0277 | 民生消費與零售: 0.0155 | 大盤指數、期貨與總體經濟: 0.0155 | 其他產業或綜合新聞: 0.0132 | 再生能源與永續發展: 0.0121 | 營建與房地產: 0.0104 | 金融與保險業: 0.0098 | 生技與醫療: 0.0082 | 航運與物流: 0.0063 | 傳統製造與原物料: 0.0063</t>
         </is>
       </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -30295,6 +32400,11 @@
       <c r="M422" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.1256 | 電子科技與半導體: 0.1251 | 通訊網路與軟體服務: 0.1222 | 民生消費與零售: 0.0901 | 傳統製造與原物料: 0.0899 | 大盤指數、期貨與總體經濟: 0.0855 | 其他產業或綜合新聞: 0.085 | 金融與保險業: 0.0783 | 營建與房地產: 0.0756 | 生技與醫療: 0.0754 | 航運與物流: 0.0475</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -30372,6 +32482,11 @@
           <t>電子科技與半導體: 0.7071 | 再生能源與永續發展: 0.0937 | 航運與物流: 0.0482 | 大盤指數、期貨與總體經濟: 0.0393 | 民生消費與零售: 0.0302 | 其他產業或綜合新聞: 0.0181 | 生技與醫療: 0.0157 | 金融與保險業: 0.0148 | 通訊網路與軟體服務: 0.0135 | 營建與房地產: 0.0108 | 傳統製造與原物料: 0.0086</t>
         </is>
       </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
@@ -30437,6 +32552,11 @@
           <t>電子科技與半導體: 0.8026 | 其他產業或綜合新聞: 0.0712 | 再生能源與永續發展: 0.0557 | 傳統製造與原物料: 0.0136 | 通訊網路與軟體服務: 0.0112 | 民生消費與零售: 0.0099 | 航運與物流: 0.009 | 大盤指數、期貨與總體經濟: 0.0087 | 營建與房地產: 0.0064 | 金融與保險業: 0.0063 | 生技與醫療: 0.0056</t>
         </is>
       </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
@@ -30498,6 +32618,11 @@
           <t>航運與物流: 0.1627 | 電子科技與半導體: 0.1243 | 大盤指數、期貨與總體經濟: 0.119 | 民生消費與零售: 0.1136 | 通訊網路與軟體服務: 0.089 | 金融與保險業: 0.0807 | 營建與房地產: 0.0766 | 再生能源與永續發展: 0.0669 | 傳統製造與原物料: 0.0668 | 生技與醫療: 0.0604 | 其他產業或綜合新聞: 0.04</t>
         </is>
       </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
@@ -30563,6 +32688,11 @@
           <t>電子科技與半導體: 0.2564 | 通訊網路與軟體服務: 0.1534 | 金融與保險業: 0.1048 | 民生消費與零售: 0.1016 | 大盤指數、期貨與總體經濟: 0.0896 | 其他產業或綜合新聞: 0.0762 | 再生能源與永續發展: 0.0652 | 傳統製造與原物料: 0.052 | 航運與物流: 0.038 | 營建與房地產: 0.0334 | 生技與醫療: 0.0294</t>
         </is>
       </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
@@ -30624,6 +32754,11 @@
       <c r="M427" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.8545 | 電子科技與半導體: 0.0567 | 金融與保險業: 0.0226 | 大盤指數、期貨與總體經濟: 0.0145 | 再生能源與永續發展: 0.0102 | 其他產業或綜合新聞: 0.01 | 傳統製造與原物料: 0.0085 | 營建與房地產: 0.0083 | 航運與物流: 0.0053 | 民生消費與零售: 0.0049 | 生技與醫療: 0.0046</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -30691,6 +32826,11 @@
       <c r="M428" t="inlineStr">
         <is>
           <t>生技與醫療: 0.7052 | 其他產業或綜合新聞: 0.0793 | 大盤指數、期貨與總體經濟: 0.0311 | 民生消費與零售: 0.0272 | 營建與房地產: 0.0253 | 電子科技與半導體: 0.0249 | 通訊網路與軟體服務: 0.0237 | 航運與物流: 0.0229 | 金融與保險業: 0.0213 | 傳統製造與原物料: 0.0201 | 再生能源與永續發展: 0.0189</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -30762,6 +32902,11 @@
           <t>電子科技與半導體: 0.7289 | 再生能源與永續發展: 0.096 | 其他產業或綜合新聞: 0.0443 | 大盤指數、期貨與總體經濟: 0.0319 | 航運與物流: 0.0276 | 傳統製造與原物料: 0.0235 | 民生消費與零售: 0.0199 | 生技與醫療: 0.0134 | 通訊網路與軟體服務: 0.0063 | 金融與保險業: 0.0053 | 營建與房地產: 0.0029</t>
         </is>
       </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
@@ -30825,6 +32970,11 @@
       <c r="M430" t="inlineStr">
         <is>
           <t>航運與物流: 0.4074 | 通訊網路與軟體服務: 0.3662 | 民生消費與零售: 0.1571 | 再生能源與永續發展: 0.0164 | 電子科技與半導體: 0.0148 | 其他產業或綜合新聞: 0.0108 | 大盤指數、期貨與總體經濟: 0.0105 | 營建與房地產: 0.0078 | 金融與保險業: 0.0045 | 生技與醫療: 0.0025 | 傳統製造與原物料: 0.0021</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -30902,6 +33052,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
@@ -30967,6 +33122,11 @@
           <t>電子科技與半導體: 0.246 | 通訊網路與軟體服務: 0.1383 | 其他產業或綜合新聞: 0.1069 | 營建與房地產: 0.0912 | 再生能源與永續發展: 0.0797 | 傳統製造與原物料: 0.0631 | 民生消費與零售: 0.0623 | 金融與保險業: 0.0607 | 大盤指數、期貨與總體經濟: 0.0588 | 航運與物流: 0.0469 | 生技與醫療: 0.0461</t>
         </is>
       </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
@@ -31028,6 +33188,11 @@
       <c r="M433" t="inlineStr">
         <is>
           <t>金融與保險業: 0.1969 | 民生消費與零售: 0.1783 | 營建與房地產: 0.1018 | 大盤指數、期貨與總體經濟: 0.0807 | 生技與醫療: 0.0755 | 再生能源與永續發展: 0.0732 | 傳統製造與原物料: 0.0697 | 電子科技與半導體: 0.066 | 其他產業或綜合新聞: 0.0637 | 航運與物流: 0.055 | 通訊網路與軟體服務: 0.0394</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>一般新聞</t>
         </is>
       </c>
     </row>
@@ -31103,6 +33268,11 @@
           <t>電子科技與半導體: 0.2387 | 大盤指數、期貨與總體經濟: 0.1329 | 其他產業或綜合新聞: 0.1323 | 傳統製造與原物料: 0.1123 | 再生能源與永續發展: 0.0702 | 民生消費與零售: 0.0653 | 通訊網路與軟體服務: 0.0581 | 金融與保險業: 0.0531 | 生技與醫療: 0.0493 | 航運與物流: 0.0468 | 營建與房地產: 0.0411</t>
         </is>
       </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -31164,6 +33334,11 @@
       <c r="M435" t="inlineStr">
         <is>
           <t>金融與保險業: 0.3462 | 電子科技與半導體: 0.2738 | 通訊網路與軟體服務: 0.0622 | 民生消費與零售: 0.048 | 其他產業或綜合新聞: 0.0474 | 再生能源與永續發展: 0.0453 | 大盤指數、期貨與總體經濟: 0.0413 | 營建與房地產: 0.037 | 傳統製造與原物料: 0.0361 | 航運與物流: 0.0326 | 生技與醫療: 0.0301</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -31237,6 +33412,11 @@
           <t>再生能源與永續發展: 0.192 | 民生消費與零售: 0.1573 | 電子科技與半導體: 0.1292 | 其他產業或綜合新聞: 0.1146 | 大盤指數、期貨與總體經濟: 0.1069 | 傳統製造與原物料: 0.0808 | 航運與物流: 0.0525 | 營建與房地產: 0.0461 | 金融與保險業: 0.0443 | 生技與醫療: 0.0429 | 通訊網路與軟體服務: 0.0334</t>
         </is>
       </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
@@ -31306,6 +33486,11 @@
       <c r="M437" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.155 | 電子科技與半導體: 0.1485 | 再生能源與永續發展: 0.1196 | 大盤指數、期貨與總體經濟: 0.107 | 其他產業或綜合新聞: 0.1066 | 民生消費與零售: 0.0775 | 金融與保險業: 0.0727 | 生技與醫療: 0.0683 | 傳統製造與原物料: 0.0591 | 航運與物流: 0.0503 | 營建與房地產: 0.0356</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -31383,6 +33568,11 @@
           <t>電子科技與半導體: 0.359 | 其他產業或綜合新聞: 0.1053 | 大盤指數、期貨與總體經濟: 0.1023 | 再生能源與永續發展: 0.0966 | 傳統製造與原物料: 0.0725 | 航運與物流: 0.064 | 通訊網路與軟體服務: 0.0522 | 民生消費與零售: 0.0432 | 金融與保險業: 0.0404 | 營建與房地產: 0.0329 | 生技與醫療: 0.0316</t>
         </is>
       </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
@@ -31456,6 +33646,11 @@
           <t>電子科技與半導體: 0.5866 | 再生能源與永續發展: 0.1205 | 其他產業或綜合新聞: 0.0803 | 大盤指數、期貨與總體經濟: 0.0464 | 傳統製造與原物料: 0.0329 | 金融與保險業: 0.0315 | 民生消費與零售: 0.0285 | 航運與物流: 0.0216 | 生技與醫療: 0.018 | 營建與房地產: 0.0171 | 通訊網路與軟體服務: 0.0166</t>
         </is>
       </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
@@ -31519,6 +33714,11 @@
       <c r="M440" t="inlineStr">
         <is>
           <t>生技與醫療: 0.3704 | 大盤指數、期貨與總體經濟: 0.1116 | 金融與保險業: 0.0789 | 民生消費與零售: 0.0637 | 航運與物流: 0.0629 | 營建與房地產: 0.0567 | 其他產業或綜合新聞: 0.0566 | 傳統製造與原物料: 0.0549 | 通訊網路與軟體服務: 0.0514 | 電子科技與半導體: 0.0482 | 再生能源與永續發展: 0.0447</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -31618,6 +33818,11 @@
           <t>電子科技與半導體: 0.517 | 大盤指數、期貨與總體經濟: 0.1359 | 民生消費與零售: 0.076 | 其他產業或綜合新聞: 0.0642 | 通訊網路與軟體服務: 0.0421 | 金融與保險業: 0.036 | 傳統製造與原物料: 0.0328 | 再生能源與永續發展: 0.0311 | 生技與醫療: 0.0251 | 航運與物流: 0.0222 | 營建與房地產: 0.0176</t>
         </is>
       </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -31689,6 +33894,11 @@
           <t>再生能源與永續發展: 0.8474 | 金融與保險業: 0.0392 | 其他產業或綜合新聞: 0.0238 | 大盤指數、期貨與總體經濟: 0.0179 | 電子科技與半導體: 0.0168 | 通訊網路與軟體服務: 0.0128 | 民生消費與零售: 0.0124 | 傳統製造與原物料: 0.0086 | 航運與物流: 0.0085 | 生技與醫療: 0.0073 | 營建與房地產: 0.0053</t>
         </is>
       </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
@@ -31754,6 +33964,11 @@
       <c r="M443" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -31831,6 +34046,11 @@
       <c r="M444" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -31910,6 +34130,11 @@
           <t>電子科技與半導體: 0.2283 | 航運與物流: 0.1441 | 民生消費與零售: 0.1095 | 通訊網路與軟體服務: 0.0826 | 大盤指數、期貨與總體經濟: 0.0771 | 生技與醫療: 0.0746 | 再生能源與永續發展: 0.0734 | 金融與保險業: 0.0687 | 其他產業或綜合新聞: 0.0677 | 營建與房地產: 0.0551 | 傳統製造與原物料: 0.0189</t>
         </is>
       </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
@@ -31981,6 +34206,11 @@
           <t>通訊網路與軟體服務: 0.4008 | 電子科技與半導體: 0.1356 | 其他產業或綜合新聞: 0.0859 | 再生能源與永續發展: 0.0745 | 航運與物流: 0.0623 | 民生消費與零售: 0.0538 | 金融與保險業: 0.0505 | 營建與房地產: 0.0493 | 大盤指數、期貨與總體經濟: 0.0397 | 生技與醫療: 0.0317 | 傳統製造與原物料: 0.0158</t>
         </is>
       </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
@@ -32038,6 +34268,11 @@
       <c r="M447" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.6852 | 金融與保險業: 0.123 | 電子科技與半導體: 0.03 | 營建與房地產: 0.0291 | 其他產業或綜合新聞: 0.0268 | 民生消費與零售: 0.024 | 生技與醫療: 0.0215 | 再生能源與永續發展: 0.019 | 通訊網路與軟體服務: 0.0145 | 航運與物流: 0.0143 | 傳統製造與原物料: 0.0127</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -32111,6 +34346,11 @@
           <t>再生能源與永續發展: 0.3888 | 營建與房地產: 0.1154 | 民生消費與零售: 0.079 | 金融與保險業: 0.0781 | 大盤指數、期貨與總體經濟: 0.074 | 傳統製造與原物料: 0.0673 | 其他產業或綜合新聞: 0.057 | 航運與物流: 0.0452 | 生技與醫療: 0.039 | 通訊網路與軟體服務: 0.0337 | 電子科技與半導體: 0.0223</t>
         </is>
       </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
@@ -32178,6 +34418,11 @@
           <t>再生能源與永續發展: 0.9506 | 大盤指數、期貨與總體經濟: 0.0304 | 金融與保險業: 0.0055 | 營建與房地產: 0.0026 | 民生消費與零售: 0.0023 | 電子科技與半導體: 0.0019 | 其他產業或綜合新聞: 0.0018 | 傳統製造與原物料: 0.0016 | 航運與物流: 0.0015 | 生技與醫療: 0.0009 | 通訊網路與軟體服務: 0.0008</t>
         </is>
       </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
@@ -32245,6 +34490,11 @@
           <t>其他產業或綜合新聞: 0.4013 | 大盤指數、期貨與總體經濟: 0.2962 | 航運與物流: 0.1768 | 再生能源與永續發展: 0.025 | 生技與醫療: 0.0235 | 民生消費與零售: 0.0192 | 金融與保險業: 0.0191 | 傳統製造與原物料: 0.014 | 電子科技與半導體: 0.0108 | 通訊網路與軟體服務: 0.01 | 營建與房地產: 0.0041</t>
         </is>
       </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -32310,6 +34560,11 @@
       <c r="M451" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -32379,6 +34634,11 @@
       <c r="M452" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.8239 | 通訊網路與軟體服務: 0.0825 | 大盤指數、期貨與總體經濟: 0.0194 | 再生能源與永續發展: 0.015 | 金融與保險業: 0.0133 | 其他產業或綜合新聞: 0.008 | 民生消費與零售: 0.0079 | 生技與醫療: 0.0078 | 傳統製造與原物料: 0.0078 | 營建與房地產: 0.0076 | 航運與物流: 0.0066</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -32454,6 +34714,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
@@ -32525,6 +34790,11 @@
           <t>電子科技與半導體: 0.6972 | 通訊網路與軟體服務: 0.1855 | 再生能源與永續發展: 0.0232 | 傳統製造與原物料: 0.0156 | 大盤指數、期貨與總體經濟: 0.0143 | 航運與物流: 0.0137 | 民生消費與零售: 0.0137 | 其他產業或綜合新聞: 0.0115 | 營建與房地產: 0.0103 | 生技與醫療: 0.0086 | 金融與保險業: 0.0064</t>
         </is>
       </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
@@ -32594,6 +34864,11 @@
       <c r="M455" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.2316 | 再生能源與永續發展: 0.1909 | 通訊網路與軟體服務: 0.0909 | 民生消費與零售: 0.0844 | 大盤指數、期貨與總體經濟: 0.0787 | 其他產業或綜合新聞: 0.0737 | 營建與房地產: 0.0698 | 航運與物流: 0.048 | 生技與醫療: 0.0468 | 傳統製造與原物料: 0.0429 | 金融與保險業: 0.0423</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -32669,6 +34944,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
@@ -32728,6 +35008,11 @@
       <c r="M457" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.9899 | 大盤指數、期貨與總體經濟: 0.0036 | 再生能源與永續發展: 0.0016 | 民生消費與零售: 0.0012 | 航運與物流: 0.0008 | 其他產業或綜合新聞: 0.0008 | 金融與保險業: 0.0007 | 傳統製造與原物料: 0.0005 | 生技與醫療: 0.0004 | 營建與房地產: 0.0003 | 通訊網路與軟體服務: 0.0002</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -32797,6 +35082,11 @@
       <c r="M458" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.3154 | 電子科技與半導體: 0.1679 | 再生能源與永續發展: 0.1416 | 其他產業或綜合新聞: 0.1024 | 傳統製造與原物料: 0.088 | 大盤指數、期貨與總體經濟: 0.052 | 生技與醫療: 0.0448 | 營建與房地產: 0.0329 | 航運與物流: 0.025 | 民生消費與零售: 0.0164 | 金融與保險業: 0.0136</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -32902,6 +35192,11 @@
           <t>電子科技與半導體: 0.7224 | 大盤指數、期貨與總體經濟: 0.0768 | 金融與保險業: 0.0583 | 通訊網路與軟體服務: 0.0244 | 傳統製造與原物料: 0.0221 | 民生消費與零售: 0.0216 | 航運與物流: 0.0188 | 再生能源與永續發展: 0.0175 | 生技與醫療: 0.0136 | 其他產業或綜合新聞: 0.0124 | 營建與房地產: 0.012</t>
         </is>
       </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
@@ -32967,6 +35262,11 @@
       <c r="M460" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -33038,6 +35338,11 @@
           <t>大盤指數、期貨與總體經濟: 0.1955 | 其他產業或綜合新聞: 0.151 | 航運與物流: 0.1444 | 電子科技與半導體: 0.0938 | 金融與保險業: 0.0925 | 再生能源與永續發展: 0.0904 | 生技與醫療: 0.0785 | 民生消費與零售: 0.0438 | 營建與房地產: 0.0408 | 通訊網路與軟體服務: 0.0369 | 傳統製造與原物料: 0.0325</t>
         </is>
       </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -33105,6 +35410,11 @@
       <c r="M462" t="inlineStr">
         <is>
           <t>航運與物流: 0.2252 | 其他產業或綜合新聞: 0.117 | 大盤指數、期貨與總體經濟: 0.1165 | 電子科技與半導體: 0.0993 | 再生能源與永續發展: 0.0983 | 金融與保險業: 0.09 | 民生消費與零售: 0.0697 | 通訊網路與軟體服務: 0.0673 | 生技與醫療: 0.0495 | 營建與房地產: 0.0346 | 傳統製造與原物料: 0.0325</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -33190,6 +35500,11 @@
           <t>大盤指數、期貨與總體經濟: 0.1569 | 電子科技與半導體: 0.1388 | 金融與保險業: 0.121 | 再生能源與永續發展: 0.1066 | 航運與物流: 0.1005 | 通訊網路與軟體服務: 0.098 | 生技與醫療: 0.0688 | 營建與房地產: 0.0628 | 民生消費與零售: 0.0603 | 其他產業或綜合新聞: 0.0476 | 傳統製造與原物料: 0.0387</t>
         </is>
       </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
@@ -33257,6 +35572,11 @@
       <c r="M464" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.2206 | 金融與保險業: 0.109 | 其他產業或綜合新聞: 0.102 | 民生消費與零售: 0.0983 | 通訊網路與軟體服務: 0.096 | 電子科技與半導體: 0.0895 | 再生能源與永續發展: 0.0681 | 營建與房地產: 0.0641 | 生技與醫療: 0.0603 | 航運與物流: 0.0531 | 傳統製造與原物料: 0.0391</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -33326,6 +35646,11 @@
       <c r="M465" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -33401,6 +35726,11 @@
       <c r="M466" t="inlineStr">
         <is>
           <t>大盤指數、期貨與總體經濟: 0.339 | 電子科技與半導體: 0.2849 | 再生能源與永續發展: 0.0918 | 其他產業或綜合新聞: 0.0801 | 民生消費與零售: 0.0624 | 傳統製造與原物料: 0.0472 | 金融與保險業: 0.0295 | 通訊網路與軟體服務: 0.0238 | 航運與物流: 0.0177 | 生技與醫療: 0.0129 | 營建與房地產: 0.0106</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -33496,6 +35826,11 @@
           <t>電子科技與半導體: 0.3334 | 大盤指數、期貨與總體經濟: 0.1423 | 通訊網路與軟體服務: 0.1078 | 金融與保險業: 0.0704 | 再生能源與永續發展: 0.0635 | 航運與物流: 0.0626 | 傳統製造與原物料: 0.0536 | 其他產業或綜合新聞: 0.0448 | 民生消費與零售: 0.0438 | 營建與房地產: 0.0428 | 生技與醫療: 0.035</t>
         </is>
       </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
@@ -33559,6 +35894,11 @@
       <c r="M468" t="inlineStr">
         <is>
           <t>專家關鍵字直接命中</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -33638,6 +35978,11 @@
           <t>電子科技與半導體: 0.9309 | 再生能源與永續發展: 0.0154 | 通訊網路與軟體服務: 0.0133 | 其他產業或綜合新聞: 0.012 | 航運與物流: 0.0062 | 大盤指數、期貨與總體經濟: 0.0045 | 金融與保險業: 0.0039 | 傳統製造與原物料: 0.0038 | 民生消費與零售: 0.0036 | 營建與房地產: 0.0032 | 生技與醫療: 0.003</t>
         </is>
       </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
@@ -33709,6 +36054,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
@@ -33778,6 +36128,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
@@ -33845,6 +36200,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
@@ -33912,6 +36272,11 @@
           <t>專家關鍵字直接命中</t>
         </is>
       </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
@@ -33973,6 +36338,11 @@
       <c r="M474" t="inlineStr">
         <is>
           <t>傳統製造與原物料: 0.2018 | 大盤指數、期貨與總體經濟: 0.1631 | 金融與保險業: 0.1303 | 再生能源與永續發展: 0.1084 | 民生消費與零售: 0.0856 | 生技與醫療: 0.0724 | 其他產業或綜合新聞: 0.0675 | 電子科技與半導體: 0.0639 | 營建與房地產: 0.0582 | 通訊網路與軟體服務: 0.0266 | 航運與物流: 0.0223</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -34040,6 +36410,11 @@
       <c r="M475" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.2644 | 其他產業或綜合新聞: 0.219 | 民生消費與零售: 0.2009 | 大盤指數、期貨與總體經濟: 0.0856 | 營建與房地產: 0.0685 | 電子科技與半導體: 0.053 | 傳統製造與原物料: 0.0306 | 生技與醫療: 0.0213 | 航運與物流: 0.0207 | 通訊網路與軟體服務: 0.019 | 金融與保險業: 0.017</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -34113,6 +36488,11 @@
           <t>大盤指數、期貨與總體經濟: 0.1321 | 民生消費與零售: 0.1034 | 其他產業或綜合新聞: 0.0983 | 電子科技與半導體: 0.0983 | 再生能源與永續發展: 0.0947 | 傳統製造與原物料: 0.0934 | 通訊網路與軟體服務: 0.0867 | 航運與物流: 0.0818 | 金融與保險業: 0.0773 | 生技與醫療: 0.0746 | 營建與房地產: 0.0594</t>
         </is>
       </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
@@ -34174,6 +36554,11 @@
       <c r="M477" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.8171 | 再生能源與永續發展: 0.1688 | 大盤指數、期貨與總體經濟: 0.0031 | 通訊網路與軟體服務: 0.0024 | 民生消費與零售: 0.0021 | 傳統製造與原物料: 0.0018 | 其他產業或綜合新聞: 0.0015 | 航運與物流: 0.0011 | 營建與房地產: 0.001 | 生技與醫療: 0.0006 | 金融與保險業: 0.0005</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -34241,6 +36626,11 @@
       <c r="M478" t="inlineStr">
         <is>
           <t>營建與房地產: 0.9405 | 民生消費與零售: 0.0159 | 大盤指數、期貨與總體經濟: 0.0127 | 再生能源與永續發展: 0.0052 | 其他產業或綜合新聞: 0.005 | 金融與保險業: 0.0041 | 電子科技與半導體: 0.0039 | 通訊網路與軟體服務: 0.0036 | 傳統製造與原物料: 0.0033 | 生技與醫療: 0.003 | 航運與物流: 0.0029</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -34314,6 +36704,11 @@
           <t>通訊網路與軟體服務: 0.6196 | 民生消費與零售: 0.1009 | 電子科技與半導體: 0.0584 | 大盤指數、期貨與總體經濟: 0.0568 | 航運與物流: 0.0363 | 再生能源與永續發展: 0.0288 | 營建與房地產: 0.0223 | 金融與保險業: 0.0207 | 其他產業或綜合新聞: 0.0203 | 生技與醫療: 0.0193 | 傳統製造與原物料: 0.0165</t>
         </is>
       </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -34379,6 +36774,11 @@
       <c r="M480" t="inlineStr">
         <is>
           <t>金融與保險業: 0.4962 | 大盤指數、期貨與總體經濟: 0.1387 | 民生消費與零售: 0.0789 | 其他產業或綜合新聞: 0.0734 | 傳統製造與原物料: 0.0358 | 再生能源與永續發展: 0.0335 | 生技與醫療: 0.0319 | 營建與房地產: 0.0304 | 航運與物流: 0.0287 | 電子科技與半導體: 0.0269 | 通訊網路與軟體服務: 0.0255</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -34450,6 +36850,11 @@
           <t>其他產業或綜合新聞: 0.201 | 金融與保險業: 0.1826 | 大盤指數、期貨與總體經濟: 0.1341 | 電子科技與半導體: 0.1099 | 再生能源與永續發展: 0.097 | 通訊網路與軟體服務: 0.0957 | 民生消費與零售: 0.048 | 傳統製造與原物料: 0.0441 | 生技與醫療: 0.036 | 營建與房地產: 0.0275 | 航運與物流: 0.0242</t>
         </is>
       </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
@@ -34517,6 +36922,11 @@
       <c r="M482" t="inlineStr">
         <is>
           <t>金融與保險業: 0.7436 | 再生能源與永續發展: 0.0445 | 其他產業或綜合新聞: 0.0383 | 大盤指數、期貨與總體經濟: 0.0348 | 生技與醫療: 0.0279 | 民生消費與零售: 0.0277 | 通訊網路與軟體服務: 0.0186 | 傳統製造與原物料: 0.0181 | 營建與房地產: 0.0168 | 航運與物流: 0.016 | 電子科技與半導體: 0.0139</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -34586,6 +36996,11 @@
       <c r="M483" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.7476 | 其他產業或綜合新聞: 0.094 | 航運與物流: 0.0282 | 民生消費與零售: 0.0274 | 營建與房地產: 0.0262 | 再生能源與永續發展: 0.0188 | 通訊網路與軟體服務: 0.0183 | 生技與醫療: 0.015 | 金融與保險業: 0.0116 | 大盤指數、期貨與總體經濟: 0.0078 | 傳統製造與原物料: 0.005</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -34677,6 +37092,11 @@
           <t>再生能源與永續發展: 0.1517 | 電子科技與半導體: 0.1474 | 金融與保險業: 0.1248 | 大盤指數、期貨與總體經濟: 0.1168 | 民生消費與零售: 0.0911 | 其他產業或綜合新聞: 0.0908 | 通訊網路與軟體服務: 0.0795 | 生技與醫療: 0.065 | 傳統製造與原物料: 0.0531 | 營建與房地產: 0.0484 | 航運與物流: 0.0314</t>
         </is>
       </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
@@ -34742,6 +37162,11 @@
           <t>通訊網路與軟體服務: 0.2488 | 大盤指數、期貨與總體經濟: 0.1151 | 電子科技與半導體: 0.1073 | 再生能源與永續發展: 0.1061 | 金融與保險業: 0.0934 | 民生消費與零售: 0.0876 | 航運與物流: 0.0665 | 營建與房地產: 0.0571 | 生技與醫療: 0.0501 | 其他產業或綜合新聞: 0.0344 | 傳統製造與原物料: 0.0336</t>
         </is>
       </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
@@ -34807,6 +37232,11 @@
           <t>電子科技與半導體: 0.2961 | 傳統製造與原物料: 0.1148 | 通訊網路與軟體服務: 0.0769 | 再生能源與永續發展: 0.0768 | 航運與物流: 0.0706 | 大盤指數、期貨與總體經濟: 0.068 | 生技與醫療: 0.0678 | 其他產業或綜合新聞: 0.0647 | 營建與房地產: 0.0628 | 民生消費與零售: 0.0529 | 金融與保險業: 0.0487</t>
         </is>
       </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
@@ -34870,6 +37300,11 @@
       <c r="M487" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.8147 | 通訊網路與軟體服務: 0.1698 | 其他產業或綜合新聞: 0.0039 | 航運與物流: 0.003 | 再生能源與永續發展: 0.003 | 民生消費與零售: 0.0018 | 傳統製造與原物料: 0.0011 | 大盤指數、期貨與總體經濟: 0.0011 | 生技與醫療: 0.0007 | 營建與房地產: 0.0005 | 金融與保險業: 0.0004</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -34937,6 +37372,11 @@
       <c r="M488" t="inlineStr">
         <is>
           <t>再生能源與永續發展: 0.9144 | 民生消費與零售: 0.0317 | 其他產業或綜合新聞: 0.0164 | 傳統製造與原物料: 0.0065 | 生技與醫療: 0.0052 | 航運與物流: 0.0052 | 大盤指數、期貨與總體經濟: 0.0049 | 電子科技與半導體: 0.0048 | 通訊網路與軟體服務: 0.0047 | 營建與房地產: 0.0033 | 金融與保險業: 0.0029</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
         </is>
       </c>
     </row>
@@ -35012,6 +37452,11 @@
           <t>通訊網路與軟體服務: 0.124 | 大盤指數、期貨與總體經濟: 0.123 | 電子科技與半導體: 0.102 | 再生能源與永續發展: 0.0992 | 其他產業或綜合新聞: 0.0981 | 金融與保險業: 0.0864 | 民生消費與零售: 0.0856 | 生技與醫療: 0.0807 | 營建與房地產: 0.0725 | 航運與物流: 0.0713 | 傳統製造與原物料: 0.0572</t>
         </is>
       </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
@@ -35071,6 +37516,11 @@
       <c r="M490" t="inlineStr">
         <is>
           <t>通訊網路與軟體服務: 0.4412 | 電子科技與半導體: 0.3642 | 大盤指數、期貨與總體經濟: 0.0491 | 再生能源與永續發展: 0.0283 | 民生消費與零售: 0.0249 | 傳統製造與原物料: 0.0202 | 航運與物流: 0.0185 | 生技與醫療: 0.0158 | 營建與房地產: 0.014 | 其他產業或綜合新聞: 0.0131 | 金融與保險業: 0.0108</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -35142,6 +37592,11 @@
           <t>生技與醫療: 0.1293 | 電子科技與半導體: 0.1161 | 其他產業或綜合新聞: 0.1119 | 再生能源與永續發展: 0.1066 | 營建與房地產: 0.093 | 大盤指數、期貨與總體經濟: 0.0894 | 民生消費與零售: 0.0812 | 通訊網路與軟體服務: 0.0808 | 航運與物流: 0.0769 | 金融與保險業: 0.0744 | 傳統製造與原物料: 0.0404</t>
         </is>
       </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
@@ -35205,6 +37660,11 @@
       <c r="M492" t="inlineStr">
         <is>
           <t>電子科技與半導體: 0.1858 | 再生能源與永續發展: 0.1167 | 民生消費與零售: 0.1032 | 其他產業或綜合新聞: 0.1002 | 大盤指數、期貨與總體經濟: 0.0905 | 航運與物流: 0.0812 | 營建與房地產: 0.0685 | 傳統製造與原物料: 0.0652 | 金融與保險業: 0.0639 | 生技與醫療: 0.0632 | 通訊網路與軟體服務: 0.0616</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
         </is>
       </c>
     </row>
@@ -35278,6 +37738,11 @@
           <t>電子科技與半導體: 0.7412 | 通訊網路與軟體服務: 0.0638 | 再生能源與永續發展: 0.0377 | 大盤指數、期貨與總體經濟: 0.0346 | 金融與保險業: 0.0287 | 其他產業或綜合新聞: 0.0193 | 航運與物流: 0.0191 | 傳統製造與原物料: 0.018 | 民生消費與零售: 0.0152 | 營建與房地產: 0.0116 | 生技與醫療: 0.0107</t>
         </is>
       </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
@@ -35347,6 +37812,11 @@
           <t>通訊網路與軟體服務: 0.3738 | 電子科技與半導體: 0.2688 | 再生能源與永續發展: 0.0953 | 其他產業或綜合新聞: 0.0485 | 民生消費與零售: 0.0444 | 大盤指數、期貨與總體經濟: 0.0349 | 生技與醫療: 0.0323 | 營建與房地產: 0.0304 | 航運與物流: 0.0287 | 金融與保險業: 0.0263 | 傳統製造與原物料: 0.0165</t>
         </is>
       </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
@@ -35406,6 +37876,11 @@
       <c r="M495" t="inlineStr">
         <is>
           <t>金融與保險業: 0.2847 | 民生消費與零售: 0.2428 | 大盤指數、期貨與總體經濟: 0.0814 | 其他產業或綜合新聞: 0.0766 | 營建與房地產: 0.0683 | 再生能源與永續發展: 0.0635 | 傳統製造與原物料: 0.0442 | 航運與物流: 0.0416 | 生技與醫療: 0.0364 | 電子科技與半導體: 0.0316 | 通訊網路與軟體服務: 0.0289</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>籌碼與股價動態</t>
         </is>
       </c>
     </row>
@@ -35485,6 +37960,11 @@
           <t>電子科技與半導體: 0.3304 | 再生能源與永續發展: 0.1183 | 營建與房地產: 0.1135 | 金融與保險業: 0.0713 | 大盤指數、期貨與總體經濟: 0.071 | 其他產業或綜合新聞: 0.0673 | 生技與醫療: 0.0514 | 通訊網路與軟體服務: 0.0495 | 航運與物流: 0.0452 | 民生消費與零售: 0.0418 | 傳統製造與原物料: 0.0405</t>
         </is>
       </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
@@ -35554,6 +38034,11 @@
           <t>生技與醫療: 0.32 | 其他產業或綜合新聞: 0.16 | 金融與保險業: 0.0801 | 通訊網路與軟體服務: 0.0783 | 電子科技與半導體: 0.0631 | 民生消費與零售: 0.0528 | 航運與物流: 0.0525 | 傳統製造與原物料: 0.0511 | 大盤指數、期貨與總體經濟: 0.0507 | 營建與房地產: 0.0467 | 再生能源與永續發展: 0.0446</t>
         </is>
       </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>業務與產品</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
@@ -35613,6 +38098,11 @@
       <c r="M498" t="inlineStr">
         <is>
           <t>金融與保險業: 0.4266 | 大盤指數、期貨與總體經濟: 0.4259 | 航運與物流: 0.0318 | 其他產業或綜合新聞: 0.0295 | 民生消費與零售: 0.0164 | 營建與房地產: 0.0145 | 傳統製造與原物料: 0.0143 | 生技與醫療: 0.0115 | 電子科技與半導體: 0.0113 | 通訊網路與軟體服務: 0.01 | 再生能源與永續發展: 0.0082</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
         </is>
       </c>
     </row>
@@ -35686,6 +38176,11 @@
           <t>電子科技與半導體: 0.2956 | 通訊網路與軟體服務: 0.1256 | 大盤指數、期貨與總體經濟: 0.1242 | 金融與保險業: 0.0961 | 其他產業或綜合新聞: 0.0917 | 民生消費與零售: 0.0849 | 再生能源與永續發展: 0.0489 | 傳統製造與原物料: 0.0474 | 航運與物流: 0.0313 | 生技與醫療: 0.0291 | 營建與房地產: 0.0251</t>
         </is>
       </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>法說與股東會</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
@@ -35751,6 +38246,11 @@
           <t>電子科技與半導體: 0.1647 | 金融與保險業: 0.1572 | 航運與物流: 0.1074 | 大盤指數、期貨與總體經濟: 0.097 | 民生消費與零售: 0.0896 | 營建與房地產: 0.075 | 其他產業或綜合新聞: 0.0713 | 生技與醫療: 0.0658 | 通訊網路與軟體服務: 0.0656 | 再生能源與永續發展: 0.065 | 傳統製造與原物料: 0.0415</t>
         </is>
       </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>財報與營收</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
